--- a/JsonConverter/ExcelFiles/PetStatData.xlsx
+++ b/JsonConverter/ExcelFiles/PetStatData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>아이디</t>
   </si>
@@ -114,12 +114,15 @@
   <si>
     <t>pet_air_004</t>
   </si>
+  <si>
+    <t>바람의 축복 펫</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -145,6 +148,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -181,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -192,23 +200,38 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -436,8 +459,8 @@
     <col customWidth="1" min="4" max="4" width="7.13"/>
     <col customWidth="1" min="5" max="5" width="11.88"/>
     <col customWidth="1" min="6" max="6" width="12.38"/>
-    <col customWidth="1" min="7" max="7" width="11.88"/>
-    <col customWidth="1" min="8" max="8" width="12.5"/>
+    <col customWidth="1" min="7" max="7" width="14.5"/>
+    <col customWidth="1" min="8" max="8" width="13.63"/>
     <col customWidth="1" min="9" max="9" width="10.0"/>
     <col customWidth="1" min="10" max="10" width="16.25"/>
     <col customWidth="1" min="11" max="11" width="16.38"/>
@@ -462,37 +485,37 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -513,10 +536,10 @@
       <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -528,22 +551,22 @@
       <c r="K2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -564,4185 +587,6174 @@
       <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>50.0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <v>0.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>0.0</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>0.0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>0.0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="10">
         <v>0.0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="10">
         <v>0.0</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <v>4.0</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <v>1.0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <v>0.0</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="11">
         <v>10.0</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="11">
         <v>1.5</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="9">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>60.0</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>0.0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>0.0</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>0.0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>0.0</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="10">
         <v>0.0</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="10">
         <v>0.0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>4.0</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>1.0</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>0.0</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="11">
         <v>10.0</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="11">
         <v>1.5</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="9">
         <v>0.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>100.0</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <v>0.0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>0.0</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>0.0</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>0.0</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="10">
         <v>0.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="10">
         <v>0.0</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>4.0</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>1.0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <v>0.0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="11">
         <v>10.0</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="11">
         <v>1.5</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="9">
         <v>0.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>50.0</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="9">
         <v>0.0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>0.0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>0.0</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>0.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="10">
         <v>0.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="10">
         <v>0.0</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>4.0</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>1.0</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>0.0</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="11">
         <v>10.0</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="11">
         <v>1.5</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="9">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="A8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
     </row>
     <row r="9">
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
     </row>
     <row r="10">
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
     </row>
     <row r="11">
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
     </row>
     <row r="12">
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
     </row>
     <row r="13">
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
     </row>
     <row r="14">
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
     </row>
     <row r="15">
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16">
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17">
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18">
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19">
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
     </row>
     <row r="20">
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
     </row>
     <row r="21">
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
     </row>
     <row r="22">
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
     </row>
     <row r="23">
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
     </row>
     <row r="24">
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25">
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
     </row>
     <row r="26">
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
     </row>
     <row r="27">
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
     </row>
     <row r="28">
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
     </row>
     <row r="29">
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
     </row>
     <row r="30">
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
     </row>
     <row r="31">
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
     </row>
     <row r="32">
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
     </row>
     <row r="33">
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
     </row>
     <row r="34">
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
     </row>
     <row r="35">
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
     </row>
     <row r="36">
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
     </row>
     <row r="37">
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
     </row>
     <row r="38">
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
     </row>
     <row r="39">
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
     </row>
     <row r="40">
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
     </row>
     <row r="41">
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
     </row>
     <row r="42">
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
     </row>
     <row r="43">
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
     </row>
     <row r="44">
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
     </row>
     <row r="45">
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
     </row>
     <row r="46">
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
     </row>
     <row r="47">
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
     </row>
     <row r="48">
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
     </row>
     <row r="49">
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
     </row>
     <row r="50">
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
     </row>
     <row r="51">
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
     </row>
     <row r="52">
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
     </row>
     <row r="53">
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
     </row>
     <row r="54">
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
     </row>
     <row r="55">
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
     </row>
     <row r="56">
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
     </row>
     <row r="57">
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
     </row>
     <row r="58">
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
     </row>
     <row r="59">
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
     </row>
     <row r="60">
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
     </row>
     <row r="61">
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
     </row>
     <row r="62">
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
     </row>
     <row r="63">
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
     </row>
     <row r="64">
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
     </row>
     <row r="65">
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
     </row>
     <row r="66">
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
     </row>
     <row r="67">
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
     </row>
     <row r="68">
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
     </row>
     <row r="69">
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
     </row>
     <row r="70">
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
     </row>
     <row r="71">
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
     </row>
     <row r="72">
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
     </row>
     <row r="73">
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
     </row>
     <row r="74">
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
     </row>
     <row r="75">
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
     </row>
     <row r="76">
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
     </row>
     <row r="77">
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="L77" s="15"/>
+      <c r="M77" s="15"/>
     </row>
     <row r="78">
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="L78" s="15"/>
+      <c r="M78" s="15"/>
     </row>
     <row r="79">
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="L79" s="15"/>
+      <c r="M79" s="15"/>
     </row>
     <row r="80">
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="L80" s="15"/>
+      <c r="M80" s="15"/>
     </row>
     <row r="81">
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="L81" s="15"/>
+      <c r="M81" s="15"/>
     </row>
     <row r="82">
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
     </row>
     <row r="83">
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
     </row>
     <row r="84">
-      <c r="L84" s="10"/>
-      <c r="M84" s="10"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="L84" s="15"/>
+      <c r="M84" s="15"/>
     </row>
     <row r="85">
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="L85" s="15"/>
+      <c r="M85" s="15"/>
     </row>
     <row r="86">
-      <c r="L86" s="10"/>
-      <c r="M86" s="10"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="L86" s="15"/>
+      <c r="M86" s="15"/>
     </row>
     <row r="87">
-      <c r="L87" s="10"/>
-      <c r="M87" s="10"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="L87" s="15"/>
+      <c r="M87" s="15"/>
     </row>
     <row r="88">
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="L88" s="15"/>
+      <c r="M88" s="15"/>
     </row>
     <row r="89">
-      <c r="L89" s="10"/>
-      <c r="M89" s="10"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="L89" s="15"/>
+      <c r="M89" s="15"/>
     </row>
     <row r="90">
-      <c r="L90" s="10"/>
-      <c r="M90" s="10"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="L90" s="15"/>
+      <c r="M90" s="15"/>
     </row>
     <row r="91">
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="L91" s="15"/>
+      <c r="M91" s="15"/>
     </row>
     <row r="92">
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
+      <c r="L92" s="15"/>
+      <c r="M92" s="15"/>
     </row>
     <row r="93">
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="L93" s="15"/>
+      <c r="M93" s="15"/>
     </row>
     <row r="94">
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
+      <c r="L94" s="15"/>
+      <c r="M94" s="15"/>
     </row>
     <row r="95">
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="14"/>
+      <c r="L95" s="15"/>
+      <c r="M95" s="15"/>
     </row>
     <row r="96">
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="L96" s="15"/>
+      <c r="M96" s="15"/>
     </row>
     <row r="97">
-      <c r="L97" s="10"/>
-      <c r="M97" s="10"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="L97" s="15"/>
+      <c r="M97" s="15"/>
     </row>
     <row r="98">
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14"/>
+      <c r="L98" s="15"/>
+      <c r="M98" s="15"/>
     </row>
     <row r="99">
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
+      <c r="L99" s="15"/>
+      <c r="M99" s="15"/>
     </row>
     <row r="100">
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14"/>
+      <c r="L100" s="15"/>
+      <c r="M100" s="15"/>
     </row>
     <row r="101">
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="L101" s="15"/>
+      <c r="M101" s="15"/>
     </row>
     <row r="102">
-      <c r="L102" s="10"/>
-      <c r="M102" s="10"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14"/>
+      <c r="L102" s="15"/>
+      <c r="M102" s="15"/>
     </row>
     <row r="103">
-      <c r="L103" s="10"/>
-      <c r="M103" s="10"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="L103" s="15"/>
+      <c r="M103" s="15"/>
     </row>
     <row r="104">
-      <c r="L104" s="10"/>
-      <c r="M104" s="10"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="14"/>
+      <c r="L104" s="15"/>
+      <c r="M104" s="15"/>
     </row>
     <row r="105">
-      <c r="L105" s="10"/>
-      <c r="M105" s="10"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14"/>
+      <c r="L105" s="15"/>
+      <c r="M105" s="15"/>
     </row>
     <row r="106">
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
+      <c r="L106" s="15"/>
+      <c r="M106" s="15"/>
     </row>
     <row r="107">
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="14"/>
+      <c r="L107" s="15"/>
+      <c r="M107" s="15"/>
     </row>
     <row r="108">
-      <c r="L108" s="10"/>
-      <c r="M108" s="10"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14"/>
+      <c r="L108" s="15"/>
+      <c r="M108" s="15"/>
     </row>
     <row r="109">
-      <c r="L109" s="10"/>
-      <c r="M109" s="10"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="L109" s="15"/>
+      <c r="M109" s="15"/>
     </row>
     <row r="110">
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
+      <c r="L110" s="15"/>
+      <c r="M110" s="15"/>
     </row>
     <row r="111">
-      <c r="L111" s="10"/>
-      <c r="M111" s="10"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="L111" s="15"/>
+      <c r="M111" s="15"/>
     </row>
     <row r="112">
-      <c r="L112" s="10"/>
-      <c r="M112" s="10"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="14"/>
+      <c r="L112" s="15"/>
+      <c r="M112" s="15"/>
     </row>
     <row r="113">
-      <c r="L113" s="10"/>
-      <c r="M113" s="10"/>
+      <c r="G113" s="14"/>
+      <c r="H113" s="14"/>
+      <c r="L113" s="15"/>
+      <c r="M113" s="15"/>
     </row>
     <row r="114">
-      <c r="L114" s="10"/>
-      <c r="M114" s="10"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="14"/>
+      <c r="L114" s="15"/>
+      <c r="M114" s="15"/>
     </row>
     <row r="115">
-      <c r="L115" s="10"/>
-      <c r="M115" s="10"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="14"/>
+      <c r="L115" s="15"/>
+      <c r="M115" s="15"/>
     </row>
     <row r="116">
-      <c r="L116" s="10"/>
-      <c r="M116" s="10"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14"/>
+      <c r="L116" s="15"/>
+      <c r="M116" s="15"/>
     </row>
     <row r="117">
-      <c r="L117" s="10"/>
-      <c r="M117" s="10"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="14"/>
+      <c r="L117" s="15"/>
+      <c r="M117" s="15"/>
     </row>
     <row r="118">
-      <c r="L118" s="10"/>
-      <c r="M118" s="10"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="14"/>
+      <c r="L118" s="15"/>
+      <c r="M118" s="15"/>
     </row>
     <row r="119">
-      <c r="L119" s="10"/>
-      <c r="M119" s="10"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="L119" s="15"/>
+      <c r="M119" s="15"/>
     </row>
     <row r="120">
-      <c r="L120" s="10"/>
-      <c r="M120" s="10"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14"/>
+      <c r="L120" s="15"/>
+      <c r="M120" s="15"/>
     </row>
     <row r="121">
-      <c r="L121" s="10"/>
-      <c r="M121" s="10"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="L121" s="15"/>
+      <c r="M121" s="15"/>
     </row>
     <row r="122">
-      <c r="L122" s="10"/>
-      <c r="M122" s="10"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="14"/>
+      <c r="L122" s="15"/>
+      <c r="M122" s="15"/>
     </row>
     <row r="123">
-      <c r="L123" s="10"/>
-      <c r="M123" s="10"/>
+      <c r="G123" s="14"/>
+      <c r="H123" s="14"/>
+      <c r="L123" s="15"/>
+      <c r="M123" s="15"/>
     </row>
     <row r="124">
-      <c r="L124" s="10"/>
-      <c r="M124" s="10"/>
+      <c r="G124" s="14"/>
+      <c r="H124" s="14"/>
+      <c r="L124" s="15"/>
+      <c r="M124" s="15"/>
     </row>
     <row r="125">
-      <c r="L125" s="10"/>
-      <c r="M125" s="10"/>
+      <c r="G125" s="14"/>
+      <c r="H125" s="14"/>
+      <c r="L125" s="15"/>
+      <c r="M125" s="15"/>
     </row>
     <row r="126">
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
+      <c r="G126" s="14"/>
+      <c r="H126" s="14"/>
+      <c r="L126" s="15"/>
+      <c r="M126" s="15"/>
     </row>
     <row r="127">
-      <c r="L127" s="10"/>
-      <c r="M127" s="10"/>
+      <c r="G127" s="14"/>
+      <c r="H127" s="14"/>
+      <c r="L127" s="15"/>
+      <c r="M127" s="15"/>
     </row>
     <row r="128">
-      <c r="L128" s="10"/>
-      <c r="M128" s="10"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="14"/>
+      <c r="L128" s="15"/>
+      <c r="M128" s="15"/>
     </row>
     <row r="129">
-      <c r="L129" s="10"/>
-      <c r="M129" s="10"/>
+      <c r="G129" s="14"/>
+      <c r="H129" s="14"/>
+      <c r="L129" s="15"/>
+      <c r="M129" s="15"/>
     </row>
     <row r="130">
-      <c r="L130" s="10"/>
-      <c r="M130" s="10"/>
+      <c r="G130" s="14"/>
+      <c r="H130" s="14"/>
+      <c r="L130" s="15"/>
+      <c r="M130" s="15"/>
     </row>
     <row r="131">
-      <c r="L131" s="10"/>
-      <c r="M131" s="10"/>
+      <c r="G131" s="14"/>
+      <c r="H131" s="14"/>
+      <c r="L131" s="15"/>
+      <c r="M131" s="15"/>
     </row>
     <row r="132">
-      <c r="L132" s="10"/>
-      <c r="M132" s="10"/>
+      <c r="G132" s="14"/>
+      <c r="H132" s="14"/>
+      <c r="L132" s="15"/>
+      <c r="M132" s="15"/>
     </row>
     <row r="133">
-      <c r="L133" s="10"/>
-      <c r="M133" s="10"/>
+      <c r="G133" s="14"/>
+      <c r="H133" s="14"/>
+      <c r="L133" s="15"/>
+      <c r="M133" s="15"/>
     </row>
     <row r="134">
-      <c r="L134" s="10"/>
-      <c r="M134" s="10"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="14"/>
+      <c r="L134" s="15"/>
+      <c r="M134" s="15"/>
     </row>
     <row r="135">
-      <c r="L135" s="10"/>
-      <c r="M135" s="10"/>
+      <c r="G135" s="14"/>
+      <c r="H135" s="14"/>
+      <c r="L135" s="15"/>
+      <c r="M135" s="15"/>
     </row>
     <row r="136">
-      <c r="L136" s="10"/>
-      <c r="M136" s="10"/>
+      <c r="G136" s="14"/>
+      <c r="H136" s="14"/>
+      <c r="L136" s="15"/>
+      <c r="M136" s="15"/>
     </row>
     <row r="137">
-      <c r="L137" s="10"/>
-      <c r="M137" s="10"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="14"/>
+      <c r="L137" s="15"/>
+      <c r="M137" s="15"/>
     </row>
     <row r="138">
-      <c r="L138" s="10"/>
-      <c r="M138" s="10"/>
+      <c r="G138" s="14"/>
+      <c r="H138" s="14"/>
+      <c r="L138" s="15"/>
+      <c r="M138" s="15"/>
     </row>
     <row r="139">
-      <c r="L139" s="10"/>
-      <c r="M139" s="10"/>
+      <c r="G139" s="14"/>
+      <c r="H139" s="14"/>
+      <c r="L139" s="15"/>
+      <c r="M139" s="15"/>
     </row>
     <row r="140">
-      <c r="L140" s="10"/>
-      <c r="M140" s="10"/>
+      <c r="G140" s="14"/>
+      <c r="H140" s="14"/>
+      <c r="L140" s="15"/>
+      <c r="M140" s="15"/>
     </row>
     <row r="141">
-      <c r="L141" s="10"/>
-      <c r="M141" s="10"/>
+      <c r="G141" s="14"/>
+      <c r="H141" s="14"/>
+      <c r="L141" s="15"/>
+      <c r="M141" s="15"/>
     </row>
     <row r="142">
-      <c r="L142" s="10"/>
-      <c r="M142" s="10"/>
+      <c r="G142" s="14"/>
+      <c r="H142" s="14"/>
+      <c r="L142" s="15"/>
+      <c r="M142" s="15"/>
     </row>
     <row r="143">
-      <c r="L143" s="10"/>
-      <c r="M143" s="10"/>
+      <c r="G143" s="14"/>
+      <c r="H143" s="14"/>
+      <c r="L143" s="15"/>
+      <c r="M143" s="15"/>
     </row>
     <row r="144">
-      <c r="L144" s="10"/>
-      <c r="M144" s="10"/>
+      <c r="G144" s="14"/>
+      <c r="H144" s="14"/>
+      <c r="L144" s="15"/>
+      <c r="M144" s="15"/>
     </row>
     <row r="145">
-      <c r="L145" s="10"/>
-      <c r="M145" s="10"/>
+      <c r="G145" s="14"/>
+      <c r="H145" s="14"/>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
     </row>
     <row r="146">
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
+      <c r="G146" s="14"/>
+      <c r="H146" s="14"/>
+      <c r="L146" s="15"/>
+      <c r="M146" s="15"/>
     </row>
     <row r="147">
-      <c r="L147" s="10"/>
-      <c r="M147" s="10"/>
+      <c r="G147" s="14"/>
+      <c r="H147" s="14"/>
+      <c r="L147" s="15"/>
+      <c r="M147" s="15"/>
     </row>
     <row r="148">
-      <c r="L148" s="10"/>
-      <c r="M148" s="10"/>
+      <c r="G148" s="14"/>
+      <c r="H148" s="14"/>
+      <c r="L148" s="15"/>
+      <c r="M148" s="15"/>
     </row>
     <row r="149">
-      <c r="L149" s="10"/>
-      <c r="M149" s="10"/>
+      <c r="G149" s="14"/>
+      <c r="H149" s="14"/>
+      <c r="L149" s="15"/>
+      <c r="M149" s="15"/>
     </row>
     <row r="150">
-      <c r="L150" s="10"/>
-      <c r="M150" s="10"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="14"/>
+      <c r="L150" s="15"/>
+      <c r="M150" s="15"/>
     </row>
     <row r="151">
-      <c r="L151" s="10"/>
-      <c r="M151" s="10"/>
+      <c r="G151" s="14"/>
+      <c r="H151" s="14"/>
+      <c r="L151" s="15"/>
+      <c r="M151" s="15"/>
     </row>
     <row r="152">
-      <c r="L152" s="10"/>
-      <c r="M152" s="10"/>
+      <c r="G152" s="14"/>
+      <c r="H152" s="14"/>
+      <c r="L152" s="15"/>
+      <c r="M152" s="15"/>
     </row>
     <row r="153">
-      <c r="L153" s="10"/>
-      <c r="M153" s="10"/>
+      <c r="G153" s="14"/>
+      <c r="H153" s="14"/>
+      <c r="L153" s="15"/>
+      <c r="M153" s="15"/>
     </row>
     <row r="154">
-      <c r="L154" s="10"/>
-      <c r="M154" s="10"/>
+      <c r="G154" s="14"/>
+      <c r="H154" s="14"/>
+      <c r="L154" s="15"/>
+      <c r="M154" s="15"/>
     </row>
     <row r="155">
-      <c r="L155" s="10"/>
-      <c r="M155" s="10"/>
+      <c r="G155" s="14"/>
+      <c r="H155" s="14"/>
+      <c r="L155" s="15"/>
+      <c r="M155" s="15"/>
     </row>
     <row r="156">
-      <c r="L156" s="10"/>
-      <c r="M156" s="10"/>
+      <c r="G156" s="14"/>
+      <c r="H156" s="14"/>
+      <c r="L156" s="15"/>
+      <c r="M156" s="15"/>
     </row>
     <row r="157">
-      <c r="L157" s="10"/>
-      <c r="M157" s="10"/>
+      <c r="G157" s="14"/>
+      <c r="H157" s="14"/>
+      <c r="L157" s="15"/>
+      <c r="M157" s="15"/>
     </row>
     <row r="158">
-      <c r="L158" s="10"/>
-      <c r="M158" s="10"/>
+      <c r="G158" s="14"/>
+      <c r="H158" s="14"/>
+      <c r="L158" s="15"/>
+      <c r="M158" s="15"/>
     </row>
     <row r="159">
-      <c r="L159" s="10"/>
-      <c r="M159" s="10"/>
+      <c r="G159" s="14"/>
+      <c r="H159" s="14"/>
+      <c r="L159" s="15"/>
+      <c r="M159" s="15"/>
     </row>
     <row r="160">
-      <c r="L160" s="10"/>
-      <c r="M160" s="10"/>
+      <c r="G160" s="14"/>
+      <c r="H160" s="14"/>
+      <c r="L160" s="15"/>
+      <c r="M160" s="15"/>
     </row>
     <row r="161">
-      <c r="L161" s="10"/>
-      <c r="M161" s="10"/>
+      <c r="G161" s="14"/>
+      <c r="H161" s="14"/>
+      <c r="L161" s="15"/>
+      <c r="M161" s="15"/>
     </row>
     <row r="162">
-      <c r="L162" s="10"/>
-      <c r="M162" s="10"/>
+      <c r="G162" s="14"/>
+      <c r="H162" s="14"/>
+      <c r="L162" s="15"/>
+      <c r="M162" s="15"/>
     </row>
     <row r="163">
-      <c r="L163" s="10"/>
-      <c r="M163" s="10"/>
+      <c r="G163" s="14"/>
+      <c r="H163" s="14"/>
+      <c r="L163" s="15"/>
+      <c r="M163" s="15"/>
     </row>
     <row r="164">
-      <c r="L164" s="10"/>
-      <c r="M164" s="10"/>
+      <c r="G164" s="14"/>
+      <c r="H164" s="14"/>
+      <c r="L164" s="15"/>
+      <c r="M164" s="15"/>
     </row>
     <row r="165">
-      <c r="L165" s="10"/>
-      <c r="M165" s="10"/>
+      <c r="G165" s="14"/>
+      <c r="H165" s="14"/>
+      <c r="L165" s="15"/>
+      <c r="M165" s="15"/>
     </row>
     <row r="166">
-      <c r="L166" s="10"/>
-      <c r="M166" s="10"/>
+      <c r="G166" s="14"/>
+      <c r="H166" s="14"/>
+      <c r="L166" s="15"/>
+      <c r="M166" s="15"/>
     </row>
     <row r="167">
-      <c r="L167" s="10"/>
-      <c r="M167" s="10"/>
+      <c r="G167" s="14"/>
+      <c r="H167" s="14"/>
+      <c r="L167" s="15"/>
+      <c r="M167" s="15"/>
     </row>
     <row r="168">
-      <c r="L168" s="10"/>
-      <c r="M168" s="10"/>
+      <c r="G168" s="14"/>
+      <c r="H168" s="14"/>
+      <c r="L168" s="15"/>
+      <c r="M168" s="15"/>
     </row>
     <row r="169">
-      <c r="L169" s="10"/>
-      <c r="M169" s="10"/>
+      <c r="G169" s="14"/>
+      <c r="H169" s="14"/>
+      <c r="L169" s="15"/>
+      <c r="M169" s="15"/>
     </row>
     <row r="170">
-      <c r="L170" s="10"/>
-      <c r="M170" s="10"/>
+      <c r="G170" s="14"/>
+      <c r="H170" s="14"/>
+      <c r="L170" s="15"/>
+      <c r="M170" s="15"/>
     </row>
     <row r="171">
-      <c r="L171" s="10"/>
-      <c r="M171" s="10"/>
+      <c r="G171" s="14"/>
+      <c r="H171" s="14"/>
+      <c r="L171" s="15"/>
+      <c r="M171" s="15"/>
     </row>
     <row r="172">
-      <c r="L172" s="10"/>
-      <c r="M172" s="10"/>
+      <c r="G172" s="14"/>
+      <c r="H172" s="14"/>
+      <c r="L172" s="15"/>
+      <c r="M172" s="15"/>
     </row>
     <row r="173">
-      <c r="L173" s="10"/>
-      <c r="M173" s="10"/>
+      <c r="G173" s="14"/>
+      <c r="H173" s="14"/>
+      <c r="L173" s="15"/>
+      <c r="M173" s="15"/>
     </row>
     <row r="174">
-      <c r="L174" s="10"/>
-      <c r="M174" s="10"/>
+      <c r="G174" s="14"/>
+      <c r="H174" s="14"/>
+      <c r="L174" s="15"/>
+      <c r="M174" s="15"/>
     </row>
     <row r="175">
-      <c r="L175" s="10"/>
-      <c r="M175" s="10"/>
+      <c r="G175" s="14"/>
+      <c r="H175" s="14"/>
+      <c r="L175" s="15"/>
+      <c r="M175" s="15"/>
     </row>
     <row r="176">
-      <c r="L176" s="10"/>
-      <c r="M176" s="10"/>
+      <c r="G176" s="14"/>
+      <c r="H176" s="14"/>
+      <c r="L176" s="15"/>
+      <c r="M176" s="15"/>
     </row>
     <row r="177">
-      <c r="L177" s="10"/>
-      <c r="M177" s="10"/>
+      <c r="G177" s="14"/>
+      <c r="H177" s="14"/>
+      <c r="L177" s="15"/>
+      <c r="M177" s="15"/>
     </row>
     <row r="178">
-      <c r="L178" s="10"/>
-      <c r="M178" s="10"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="14"/>
+      <c r="L178" s="15"/>
+      <c r="M178" s="15"/>
     </row>
     <row r="179">
-      <c r="L179" s="10"/>
-      <c r="M179" s="10"/>
+      <c r="G179" s="14"/>
+      <c r="H179" s="14"/>
+      <c r="L179" s="15"/>
+      <c r="M179" s="15"/>
     </row>
     <row r="180">
-      <c r="L180" s="10"/>
-      <c r="M180" s="10"/>
+      <c r="G180" s="14"/>
+      <c r="H180" s="14"/>
+      <c r="L180" s="15"/>
+      <c r="M180" s="15"/>
     </row>
     <row r="181">
-      <c r="L181" s="10"/>
-      <c r="M181" s="10"/>
+      <c r="G181" s="14"/>
+      <c r="H181" s="14"/>
+      <c r="L181" s="15"/>
+      <c r="M181" s="15"/>
     </row>
     <row r="182">
-      <c r="L182" s="10"/>
-      <c r="M182" s="10"/>
+      <c r="G182" s="14"/>
+      <c r="H182" s="14"/>
+      <c r="L182" s="15"/>
+      <c r="M182" s="15"/>
     </row>
     <row r="183">
-      <c r="L183" s="10"/>
-      <c r="M183" s="10"/>
+      <c r="G183" s="14"/>
+      <c r="H183" s="14"/>
+      <c r="L183" s="15"/>
+      <c r="M183" s="15"/>
     </row>
     <row r="184">
-      <c r="L184" s="10"/>
-      <c r="M184" s="10"/>
+      <c r="G184" s="14"/>
+      <c r="H184" s="14"/>
+      <c r="L184" s="15"/>
+      <c r="M184" s="15"/>
     </row>
     <row r="185">
-      <c r="L185" s="10"/>
-      <c r="M185" s="10"/>
+      <c r="G185" s="14"/>
+      <c r="H185" s="14"/>
+      <c r="L185" s="15"/>
+      <c r="M185" s="15"/>
     </row>
     <row r="186">
-      <c r="L186" s="10"/>
-      <c r="M186" s="10"/>
+      <c r="G186" s="14"/>
+      <c r="H186" s="14"/>
+      <c r="L186" s="15"/>
+      <c r="M186" s="15"/>
     </row>
     <row r="187">
-      <c r="L187" s="10"/>
-      <c r="M187" s="10"/>
+      <c r="G187" s="14"/>
+      <c r="H187" s="14"/>
+      <c r="L187" s="15"/>
+      <c r="M187" s="15"/>
     </row>
     <row r="188">
-      <c r="L188" s="10"/>
-      <c r="M188" s="10"/>
+      <c r="G188" s="14"/>
+      <c r="H188" s="14"/>
+      <c r="L188" s="15"/>
+      <c r="M188" s="15"/>
     </row>
     <row r="189">
-      <c r="L189" s="10"/>
-      <c r="M189" s="10"/>
+      <c r="G189" s="14"/>
+      <c r="H189" s="14"/>
+      <c r="L189" s="15"/>
+      <c r="M189" s="15"/>
     </row>
     <row r="190">
-      <c r="L190" s="10"/>
-      <c r="M190" s="10"/>
+      <c r="G190" s="14"/>
+      <c r="H190" s="14"/>
+      <c r="L190" s="15"/>
+      <c r="M190" s="15"/>
     </row>
     <row r="191">
-      <c r="L191" s="10"/>
-      <c r="M191" s="10"/>
+      <c r="G191" s="14"/>
+      <c r="H191" s="14"/>
+      <c r="L191" s="15"/>
+      <c r="M191" s="15"/>
     </row>
     <row r="192">
-      <c r="L192" s="10"/>
-      <c r="M192" s="10"/>
+      <c r="G192" s="14"/>
+      <c r="H192" s="14"/>
+      <c r="L192" s="15"/>
+      <c r="M192" s="15"/>
     </row>
     <row r="193">
-      <c r="L193" s="10"/>
-      <c r="M193" s="10"/>
+      <c r="G193" s="14"/>
+      <c r="H193" s="14"/>
+      <c r="L193" s="15"/>
+      <c r="M193" s="15"/>
     </row>
     <row r="194">
-      <c r="L194" s="10"/>
-      <c r="M194" s="10"/>
+      <c r="G194" s="14"/>
+      <c r="H194" s="14"/>
+      <c r="L194" s="15"/>
+      <c r="M194" s="15"/>
     </row>
     <row r="195">
-      <c r="L195" s="10"/>
-      <c r="M195" s="10"/>
+      <c r="G195" s="14"/>
+      <c r="H195" s="14"/>
+      <c r="L195" s="15"/>
+      <c r="M195" s="15"/>
     </row>
     <row r="196">
-      <c r="L196" s="10"/>
-      <c r="M196" s="10"/>
+      <c r="G196" s="14"/>
+      <c r="H196" s="14"/>
+      <c r="L196" s="15"/>
+      <c r="M196" s="15"/>
     </row>
     <row r="197">
-      <c r="L197" s="10"/>
-      <c r="M197" s="10"/>
+      <c r="G197" s="14"/>
+      <c r="H197" s="14"/>
+      <c r="L197" s="15"/>
+      <c r="M197" s="15"/>
     </row>
     <row r="198">
-      <c r="L198" s="10"/>
-      <c r="M198" s="10"/>
+      <c r="G198" s="14"/>
+      <c r="H198" s="14"/>
+      <c r="L198" s="15"/>
+      <c r="M198" s="15"/>
     </row>
     <row r="199">
-      <c r="L199" s="10"/>
-      <c r="M199" s="10"/>
+      <c r="G199" s="14"/>
+      <c r="H199" s="14"/>
+      <c r="L199" s="15"/>
+      <c r="M199" s="15"/>
     </row>
     <row r="200">
-      <c r="L200" s="10"/>
-      <c r="M200" s="10"/>
+      <c r="G200" s="14"/>
+      <c r="H200" s="14"/>
+      <c r="L200" s="15"/>
+      <c r="M200" s="15"/>
     </row>
     <row r="201">
-      <c r="L201" s="10"/>
-      <c r="M201" s="10"/>
+      <c r="G201" s="14"/>
+      <c r="H201" s="14"/>
+      <c r="L201" s="15"/>
+      <c r="M201" s="15"/>
     </row>
     <row r="202">
-      <c r="L202" s="10"/>
-      <c r="M202" s="10"/>
+      <c r="G202" s="14"/>
+      <c r="H202" s="14"/>
+      <c r="L202" s="15"/>
+      <c r="M202" s="15"/>
     </row>
     <row r="203">
-      <c r="L203" s="10"/>
-      <c r="M203" s="10"/>
+      <c r="G203" s="14"/>
+      <c r="H203" s="14"/>
+      <c r="L203" s="15"/>
+      <c r="M203" s="15"/>
     </row>
     <row r="204">
-      <c r="L204" s="10"/>
-      <c r="M204" s="10"/>
+      <c r="G204" s="14"/>
+      <c r="H204" s="14"/>
+      <c r="L204" s="15"/>
+      <c r="M204" s="15"/>
     </row>
     <row r="205">
-      <c r="L205" s="10"/>
-      <c r="M205" s="10"/>
+      <c r="G205" s="14"/>
+      <c r="H205" s="14"/>
+      <c r="L205" s="15"/>
+      <c r="M205" s="15"/>
     </row>
     <row r="206">
-      <c r="L206" s="10"/>
-      <c r="M206" s="10"/>
+      <c r="G206" s="14"/>
+      <c r="H206" s="14"/>
+      <c r="L206" s="15"/>
+      <c r="M206" s="15"/>
     </row>
     <row r="207">
-      <c r="L207" s="10"/>
-      <c r="M207" s="10"/>
+      <c r="G207" s="14"/>
+      <c r="H207" s="14"/>
+      <c r="L207" s="15"/>
+      <c r="M207" s="15"/>
     </row>
     <row r="208">
-      <c r="L208" s="10"/>
-      <c r="M208" s="10"/>
+      <c r="G208" s="14"/>
+      <c r="H208" s="14"/>
+      <c r="L208" s="15"/>
+      <c r="M208" s="15"/>
     </row>
     <row r="209">
-      <c r="L209" s="10"/>
-      <c r="M209" s="10"/>
+      <c r="G209" s="14"/>
+      <c r="H209" s="14"/>
+      <c r="L209" s="15"/>
+      <c r="M209" s="15"/>
     </row>
     <row r="210">
-      <c r="L210" s="10"/>
-      <c r="M210" s="10"/>
+      <c r="G210" s="14"/>
+      <c r="H210" s="14"/>
+      <c r="L210" s="15"/>
+      <c r="M210" s="15"/>
     </row>
     <row r="211">
-      <c r="L211" s="10"/>
-      <c r="M211" s="10"/>
+      <c r="G211" s="14"/>
+      <c r="H211" s="14"/>
+      <c r="L211" s="15"/>
+      <c r="M211" s="15"/>
     </row>
     <row r="212">
-      <c r="L212" s="10"/>
-      <c r="M212" s="10"/>
+      <c r="G212" s="14"/>
+      <c r="H212" s="14"/>
+      <c r="L212" s="15"/>
+      <c r="M212" s="15"/>
     </row>
     <row r="213">
-      <c r="L213" s="10"/>
-      <c r="M213" s="10"/>
+      <c r="G213" s="14"/>
+      <c r="H213" s="14"/>
+      <c r="L213" s="15"/>
+      <c r="M213" s="15"/>
     </row>
     <row r="214">
-      <c r="L214" s="10"/>
-      <c r="M214" s="10"/>
+      <c r="G214" s="14"/>
+      <c r="H214" s="14"/>
+      <c r="L214" s="15"/>
+      <c r="M214" s="15"/>
     </row>
     <row r="215">
-      <c r="L215" s="10"/>
-      <c r="M215" s="10"/>
+      <c r="G215" s="14"/>
+      <c r="H215" s="14"/>
+      <c r="L215" s="15"/>
+      <c r="M215" s="15"/>
     </row>
     <row r="216">
-      <c r="L216" s="10"/>
-      <c r="M216" s="10"/>
+      <c r="G216" s="14"/>
+      <c r="H216" s="14"/>
+      <c r="L216" s="15"/>
+      <c r="M216" s="15"/>
     </row>
     <row r="217">
-      <c r="L217" s="10"/>
-      <c r="M217" s="10"/>
+      <c r="G217" s="14"/>
+      <c r="H217" s="14"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
     </row>
     <row r="218">
-      <c r="L218" s="10"/>
-      <c r="M218" s="10"/>
+      <c r="G218" s="14"/>
+      <c r="H218" s="14"/>
+      <c r="L218" s="15"/>
+      <c r="M218" s="15"/>
     </row>
     <row r="219">
-      <c r="L219" s="10"/>
-      <c r="M219" s="10"/>
+      <c r="G219" s="14"/>
+      <c r="H219" s="14"/>
+      <c r="L219" s="15"/>
+      <c r="M219" s="15"/>
     </row>
     <row r="220">
-      <c r="L220" s="10"/>
-      <c r="M220" s="10"/>
+      <c r="G220" s="14"/>
+      <c r="H220" s="14"/>
+      <c r="L220" s="15"/>
+      <c r="M220" s="15"/>
     </row>
     <row r="221">
-      <c r="L221" s="10"/>
-      <c r="M221" s="10"/>
+      <c r="G221" s="14"/>
+      <c r="H221" s="14"/>
+      <c r="L221" s="15"/>
+      <c r="M221" s="15"/>
     </row>
     <row r="222">
-      <c r="L222" s="10"/>
-      <c r="M222" s="10"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="14"/>
+      <c r="L222" s="15"/>
+      <c r="M222" s="15"/>
     </row>
     <row r="223">
-      <c r="L223" s="10"/>
-      <c r="M223" s="10"/>
+      <c r="G223" s="14"/>
+      <c r="H223" s="14"/>
+      <c r="L223" s="15"/>
+      <c r="M223" s="15"/>
     </row>
     <row r="224">
-      <c r="L224" s="10"/>
-      <c r="M224" s="10"/>
+      <c r="G224" s="14"/>
+      <c r="H224" s="14"/>
+      <c r="L224" s="15"/>
+      <c r="M224" s="15"/>
     </row>
     <row r="225">
-      <c r="L225" s="10"/>
-      <c r="M225" s="10"/>
+      <c r="G225" s="14"/>
+      <c r="H225" s="14"/>
+      <c r="L225" s="15"/>
+      <c r="M225" s="15"/>
     </row>
     <row r="226">
-      <c r="L226" s="10"/>
-      <c r="M226" s="10"/>
+      <c r="G226" s="14"/>
+      <c r="H226" s="14"/>
+      <c r="L226" s="15"/>
+      <c r="M226" s="15"/>
     </row>
     <row r="227">
-      <c r="L227" s="10"/>
-      <c r="M227" s="10"/>
+      <c r="G227" s="14"/>
+      <c r="H227" s="14"/>
+      <c r="L227" s="15"/>
+      <c r="M227" s="15"/>
     </row>
     <row r="228">
-      <c r="L228" s="10"/>
-      <c r="M228" s="10"/>
+      <c r="G228" s="14"/>
+      <c r="H228" s="14"/>
+      <c r="L228" s="15"/>
+      <c r="M228" s="15"/>
     </row>
     <row r="229">
-      <c r="L229" s="10"/>
-      <c r="M229" s="10"/>
+      <c r="G229" s="14"/>
+      <c r="H229" s="14"/>
+      <c r="L229" s="15"/>
+      <c r="M229" s="15"/>
     </row>
     <row r="230">
-      <c r="L230" s="10"/>
-      <c r="M230" s="10"/>
+      <c r="G230" s="14"/>
+      <c r="H230" s="14"/>
+      <c r="L230" s="15"/>
+      <c r="M230" s="15"/>
     </row>
     <row r="231">
-      <c r="L231" s="10"/>
-      <c r="M231" s="10"/>
+      <c r="G231" s="14"/>
+      <c r="H231" s="14"/>
+      <c r="L231" s="15"/>
+      <c r="M231" s="15"/>
     </row>
     <row r="232">
-      <c r="L232" s="10"/>
-      <c r="M232" s="10"/>
+      <c r="G232" s="14"/>
+      <c r="H232" s="14"/>
+      <c r="L232" s="15"/>
+      <c r="M232" s="15"/>
     </row>
     <row r="233">
-      <c r="L233" s="10"/>
-      <c r="M233" s="10"/>
+      <c r="G233" s="14"/>
+      <c r="H233" s="14"/>
+      <c r="L233" s="15"/>
+      <c r="M233" s="15"/>
     </row>
     <row r="234">
-      <c r="L234" s="10"/>
-      <c r="M234" s="10"/>
+      <c r="G234" s="14"/>
+      <c r="H234" s="14"/>
+      <c r="L234" s="15"/>
+      <c r="M234" s="15"/>
     </row>
     <row r="235">
-      <c r="L235" s="10"/>
-      <c r="M235" s="10"/>
+      <c r="G235" s="14"/>
+      <c r="H235" s="14"/>
+      <c r="L235" s="15"/>
+      <c r="M235" s="15"/>
     </row>
     <row r="236">
-      <c r="L236" s="10"/>
-      <c r="M236" s="10"/>
+      <c r="G236" s="14"/>
+      <c r="H236" s="14"/>
+      <c r="L236" s="15"/>
+      <c r="M236" s="15"/>
     </row>
     <row r="237">
-      <c r="L237" s="10"/>
-      <c r="M237" s="10"/>
+      <c r="G237" s="14"/>
+      <c r="H237" s="14"/>
+      <c r="L237" s="15"/>
+      <c r="M237" s="15"/>
     </row>
     <row r="238">
-      <c r="L238" s="10"/>
-      <c r="M238" s="10"/>
+      <c r="G238" s="14"/>
+      <c r="H238" s="14"/>
+      <c r="L238" s="15"/>
+      <c r="M238" s="15"/>
     </row>
     <row r="239">
-      <c r="L239" s="10"/>
-      <c r="M239" s="10"/>
+      <c r="G239" s="14"/>
+      <c r="H239" s="14"/>
+      <c r="L239" s="15"/>
+      <c r="M239" s="15"/>
     </row>
     <row r="240">
-      <c r="L240" s="10"/>
-      <c r="M240" s="10"/>
+      <c r="G240" s="14"/>
+      <c r="H240" s="14"/>
+      <c r="L240" s="15"/>
+      <c r="M240" s="15"/>
     </row>
     <row r="241">
-      <c r="L241" s="10"/>
-      <c r="M241" s="10"/>
+      <c r="G241" s="14"/>
+      <c r="H241" s="14"/>
+      <c r="L241" s="15"/>
+      <c r="M241" s="15"/>
     </row>
     <row r="242">
-      <c r="L242" s="10"/>
-      <c r="M242" s="10"/>
+      <c r="G242" s="14"/>
+      <c r="H242" s="14"/>
+      <c r="L242" s="15"/>
+      <c r="M242" s="15"/>
     </row>
     <row r="243">
-      <c r="L243" s="10"/>
-      <c r="M243" s="10"/>
+      <c r="G243" s="14"/>
+      <c r="H243" s="14"/>
+      <c r="L243" s="15"/>
+      <c r="M243" s="15"/>
     </row>
     <row r="244">
-      <c r="L244" s="10"/>
-      <c r="M244" s="10"/>
+      <c r="G244" s="14"/>
+      <c r="H244" s="14"/>
+      <c r="L244" s="15"/>
+      <c r="M244" s="15"/>
     </row>
     <row r="245">
-      <c r="L245" s="10"/>
-      <c r="M245" s="10"/>
+      <c r="G245" s="14"/>
+      <c r="H245" s="14"/>
+      <c r="L245" s="15"/>
+      <c r="M245" s="15"/>
     </row>
     <row r="246">
-      <c r="L246" s="10"/>
-      <c r="M246" s="10"/>
+      <c r="G246" s="14"/>
+      <c r="H246" s="14"/>
+      <c r="L246" s="15"/>
+      <c r="M246" s="15"/>
     </row>
     <row r="247">
-      <c r="L247" s="10"/>
-      <c r="M247" s="10"/>
+      <c r="G247" s="14"/>
+      <c r="H247" s="14"/>
+      <c r="L247" s="15"/>
+      <c r="M247" s="15"/>
     </row>
     <row r="248">
-      <c r="L248" s="10"/>
-      <c r="M248" s="10"/>
+      <c r="G248" s="14"/>
+      <c r="H248" s="14"/>
+      <c r="L248" s="15"/>
+      <c r="M248" s="15"/>
     </row>
     <row r="249">
-      <c r="L249" s="10"/>
-      <c r="M249" s="10"/>
+      <c r="G249" s="14"/>
+      <c r="H249" s="14"/>
+      <c r="L249" s="15"/>
+      <c r="M249" s="15"/>
     </row>
     <row r="250">
-      <c r="L250" s="10"/>
-      <c r="M250" s="10"/>
+      <c r="G250" s="14"/>
+      <c r="H250" s="14"/>
+      <c r="L250" s="15"/>
+      <c r="M250" s="15"/>
     </row>
     <row r="251">
-      <c r="L251" s="10"/>
-      <c r="M251" s="10"/>
+      <c r="G251" s="14"/>
+      <c r="H251" s="14"/>
+      <c r="L251" s="15"/>
+      <c r="M251" s="15"/>
     </row>
     <row r="252">
-      <c r="L252" s="10"/>
-      <c r="M252" s="10"/>
+      <c r="G252" s="14"/>
+      <c r="H252" s="14"/>
+      <c r="L252" s="15"/>
+      <c r="M252" s="15"/>
     </row>
     <row r="253">
-      <c r="L253" s="10"/>
-      <c r="M253" s="10"/>
+      <c r="G253" s="14"/>
+      <c r="H253" s="14"/>
+      <c r="L253" s="15"/>
+      <c r="M253" s="15"/>
     </row>
     <row r="254">
-      <c r="L254" s="10"/>
-      <c r="M254" s="10"/>
+      <c r="G254" s="14"/>
+      <c r="H254" s="14"/>
+      <c r="L254" s="15"/>
+      <c r="M254" s="15"/>
     </row>
     <row r="255">
-      <c r="L255" s="10"/>
-      <c r="M255" s="10"/>
+      <c r="G255" s="14"/>
+      <c r="H255" s="14"/>
+      <c r="L255" s="15"/>
+      <c r="M255" s="15"/>
     </row>
     <row r="256">
-      <c r="L256" s="10"/>
-      <c r="M256" s="10"/>
+      <c r="G256" s="14"/>
+      <c r="H256" s="14"/>
+      <c r="L256" s="15"/>
+      <c r="M256" s="15"/>
     </row>
     <row r="257">
-      <c r="L257" s="10"/>
-      <c r="M257" s="10"/>
+      <c r="G257" s="14"/>
+      <c r="H257" s="14"/>
+      <c r="L257" s="15"/>
+      <c r="M257" s="15"/>
     </row>
     <row r="258">
-      <c r="L258" s="10"/>
-      <c r="M258" s="10"/>
+      <c r="G258" s="14"/>
+      <c r="H258" s="14"/>
+      <c r="L258" s="15"/>
+      <c r="M258" s="15"/>
     </row>
     <row r="259">
-      <c r="L259" s="10"/>
-      <c r="M259" s="10"/>
+      <c r="G259" s="14"/>
+      <c r="H259" s="14"/>
+      <c r="L259" s="15"/>
+      <c r="M259" s="15"/>
     </row>
     <row r="260">
-      <c r="L260" s="10"/>
-      <c r="M260" s="10"/>
+      <c r="G260" s="14"/>
+      <c r="H260" s="14"/>
+      <c r="L260" s="15"/>
+      <c r="M260" s="15"/>
     </row>
     <row r="261">
-      <c r="L261" s="10"/>
-      <c r="M261" s="10"/>
+      <c r="G261" s="14"/>
+      <c r="H261" s="14"/>
+      <c r="L261" s="15"/>
+      <c r="M261" s="15"/>
     </row>
     <row r="262">
-      <c r="L262" s="10"/>
-      <c r="M262" s="10"/>
+      <c r="G262" s="14"/>
+      <c r="H262" s="14"/>
+      <c r="L262" s="15"/>
+      <c r="M262" s="15"/>
     </row>
     <row r="263">
-      <c r="L263" s="10"/>
-      <c r="M263" s="10"/>
+      <c r="G263" s="14"/>
+      <c r="H263" s="14"/>
+      <c r="L263" s="15"/>
+      <c r="M263" s="15"/>
     </row>
     <row r="264">
-      <c r="L264" s="10"/>
-      <c r="M264" s="10"/>
+      <c r="G264" s="14"/>
+      <c r="H264" s="14"/>
+      <c r="L264" s="15"/>
+      <c r="M264" s="15"/>
     </row>
     <row r="265">
-      <c r="L265" s="10"/>
-      <c r="M265" s="10"/>
+      <c r="G265" s="14"/>
+      <c r="H265" s="14"/>
+      <c r="L265" s="15"/>
+      <c r="M265" s="15"/>
     </row>
     <row r="266">
-      <c r="L266" s="10"/>
-      <c r="M266" s="10"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="14"/>
+      <c r="L266" s="15"/>
+      <c r="M266" s="15"/>
     </row>
     <row r="267">
-      <c r="L267" s="10"/>
-      <c r="M267" s="10"/>
+      <c r="G267" s="14"/>
+      <c r="H267" s="14"/>
+      <c r="L267" s="15"/>
+      <c r="M267" s="15"/>
     </row>
     <row r="268">
-      <c r="L268" s="10"/>
-      <c r="M268" s="10"/>
+      <c r="G268" s="14"/>
+      <c r="H268" s="14"/>
+      <c r="L268" s="15"/>
+      <c r="M268" s="15"/>
     </row>
     <row r="269">
-      <c r="L269" s="10"/>
-      <c r="M269" s="10"/>
+      <c r="G269" s="14"/>
+      <c r="H269" s="14"/>
+      <c r="L269" s="15"/>
+      <c r="M269" s="15"/>
     </row>
     <row r="270">
-      <c r="L270" s="10"/>
-      <c r="M270" s="10"/>
+      <c r="G270" s="14"/>
+      <c r="H270" s="14"/>
+      <c r="L270" s="15"/>
+      <c r="M270" s="15"/>
     </row>
     <row r="271">
-      <c r="L271" s="10"/>
-      <c r="M271" s="10"/>
+      <c r="G271" s="14"/>
+      <c r="H271" s="14"/>
+      <c r="L271" s="15"/>
+      <c r="M271" s="15"/>
     </row>
     <row r="272">
-      <c r="L272" s="10"/>
-      <c r="M272" s="10"/>
+      <c r="G272" s="14"/>
+      <c r="H272" s="14"/>
+      <c r="L272" s="15"/>
+      <c r="M272" s="15"/>
     </row>
     <row r="273">
-      <c r="L273" s="10"/>
-      <c r="M273" s="10"/>
+      <c r="G273" s="14"/>
+      <c r="H273" s="14"/>
+      <c r="L273" s="15"/>
+      <c r="M273" s="15"/>
     </row>
     <row r="274">
-      <c r="L274" s="10"/>
-      <c r="M274" s="10"/>
+      <c r="G274" s="14"/>
+      <c r="H274" s="14"/>
+      <c r="L274" s="15"/>
+      <c r="M274" s="15"/>
     </row>
     <row r="275">
-      <c r="L275" s="10"/>
-      <c r="M275" s="10"/>
+      <c r="G275" s="14"/>
+      <c r="H275" s="14"/>
+      <c r="L275" s="15"/>
+      <c r="M275" s="15"/>
     </row>
     <row r="276">
-      <c r="L276" s="10"/>
-      <c r="M276" s="10"/>
+      <c r="G276" s="14"/>
+      <c r="H276" s="14"/>
+      <c r="L276" s="15"/>
+      <c r="M276" s="15"/>
     </row>
     <row r="277">
-      <c r="L277" s="10"/>
-      <c r="M277" s="10"/>
+      <c r="G277" s="14"/>
+      <c r="H277" s="14"/>
+      <c r="L277" s="15"/>
+      <c r="M277" s="15"/>
     </row>
     <row r="278">
-      <c r="L278" s="10"/>
-      <c r="M278" s="10"/>
+      <c r="G278" s="14"/>
+      <c r="H278" s="14"/>
+      <c r="L278" s="15"/>
+      <c r="M278" s="15"/>
     </row>
     <row r="279">
-      <c r="L279" s="10"/>
-      <c r="M279" s="10"/>
+      <c r="G279" s="14"/>
+      <c r="H279" s="14"/>
+      <c r="L279" s="15"/>
+      <c r="M279" s="15"/>
     </row>
     <row r="280">
-      <c r="L280" s="10"/>
-      <c r="M280" s="10"/>
+      <c r="G280" s="14"/>
+      <c r="H280" s="14"/>
+      <c r="L280" s="15"/>
+      <c r="M280" s="15"/>
     </row>
     <row r="281">
-      <c r="L281" s="10"/>
-      <c r="M281" s="10"/>
+      <c r="G281" s="14"/>
+      <c r="H281" s="14"/>
+      <c r="L281" s="15"/>
+      <c r="M281" s="15"/>
     </row>
     <row r="282">
-      <c r="L282" s="10"/>
-      <c r="M282" s="10"/>
+      <c r="G282" s="14"/>
+      <c r="H282" s="14"/>
+      <c r="L282" s="15"/>
+      <c r="M282" s="15"/>
     </row>
     <row r="283">
-      <c r="L283" s="10"/>
-      <c r="M283" s="10"/>
+      <c r="G283" s="14"/>
+      <c r="H283" s="14"/>
+      <c r="L283" s="15"/>
+      <c r="M283" s="15"/>
     </row>
     <row r="284">
-      <c r="L284" s="10"/>
-      <c r="M284" s="10"/>
+      <c r="G284" s="14"/>
+      <c r="H284" s="14"/>
+      <c r="L284" s="15"/>
+      <c r="M284" s="15"/>
     </row>
     <row r="285">
-      <c r="L285" s="10"/>
-      <c r="M285" s="10"/>
+      <c r="G285" s="14"/>
+      <c r="H285" s="14"/>
+      <c r="L285" s="15"/>
+      <c r="M285" s="15"/>
     </row>
     <row r="286">
-      <c r="L286" s="10"/>
-      <c r="M286" s="10"/>
+      <c r="G286" s="14"/>
+      <c r="H286" s="14"/>
+      <c r="L286" s="15"/>
+      <c r="M286" s="15"/>
     </row>
     <row r="287">
-      <c r="L287" s="10"/>
-      <c r="M287" s="10"/>
+      <c r="G287" s="14"/>
+      <c r="H287" s="14"/>
+      <c r="L287" s="15"/>
+      <c r="M287" s="15"/>
     </row>
     <row r="288">
-      <c r="L288" s="10"/>
-      <c r="M288" s="10"/>
+      <c r="G288" s="14"/>
+      <c r="H288" s="14"/>
+      <c r="L288" s="15"/>
+      <c r="M288" s="15"/>
     </row>
     <row r="289">
-      <c r="L289" s="10"/>
-      <c r="M289" s="10"/>
+      <c r="G289" s="14"/>
+      <c r="H289" s="14"/>
+      <c r="L289" s="15"/>
+      <c r="M289" s="15"/>
     </row>
     <row r="290">
-      <c r="L290" s="10"/>
-      <c r="M290" s="10"/>
+      <c r="G290" s="14"/>
+      <c r="H290" s="14"/>
+      <c r="L290" s="15"/>
+      <c r="M290" s="15"/>
     </row>
     <row r="291">
-      <c r="L291" s="10"/>
-      <c r="M291" s="10"/>
+      <c r="G291" s="14"/>
+      <c r="H291" s="14"/>
+      <c r="L291" s="15"/>
+      <c r="M291" s="15"/>
     </row>
     <row r="292">
-      <c r="L292" s="10"/>
-      <c r="M292" s="10"/>
+      <c r="G292" s="14"/>
+      <c r="H292" s="14"/>
+      <c r="L292" s="15"/>
+      <c r="M292" s="15"/>
     </row>
     <row r="293">
-      <c r="L293" s="10"/>
-      <c r="M293" s="10"/>
+      <c r="G293" s="14"/>
+      <c r="H293" s="14"/>
+      <c r="L293" s="15"/>
+      <c r="M293" s="15"/>
     </row>
     <row r="294">
-      <c r="L294" s="10"/>
-      <c r="M294" s="10"/>
+      <c r="G294" s="14"/>
+      <c r="H294" s="14"/>
+      <c r="L294" s="15"/>
+      <c r="M294" s="15"/>
     </row>
     <row r="295">
-      <c r="L295" s="10"/>
-      <c r="M295" s="10"/>
+      <c r="G295" s="14"/>
+      <c r="H295" s="14"/>
+      <c r="L295" s="15"/>
+      <c r="M295" s="15"/>
     </row>
     <row r="296">
-      <c r="L296" s="10"/>
-      <c r="M296" s="10"/>
+      <c r="G296" s="14"/>
+      <c r="H296" s="14"/>
+      <c r="L296" s="15"/>
+      <c r="M296" s="15"/>
     </row>
     <row r="297">
-      <c r="L297" s="10"/>
-      <c r="M297" s="10"/>
+      <c r="G297" s="14"/>
+      <c r="H297" s="14"/>
+      <c r="L297" s="15"/>
+      <c r="M297" s="15"/>
     </row>
     <row r="298">
-      <c r="L298" s="10"/>
-      <c r="M298" s="10"/>
+      <c r="G298" s="14"/>
+      <c r="H298" s="14"/>
+      <c r="L298" s="15"/>
+      <c r="M298" s="15"/>
     </row>
     <row r="299">
-      <c r="L299" s="10"/>
-      <c r="M299" s="10"/>
+      <c r="G299" s="14"/>
+      <c r="H299" s="14"/>
+      <c r="L299" s="15"/>
+      <c r="M299" s="15"/>
     </row>
     <row r="300">
-      <c r="L300" s="10"/>
-      <c r="M300" s="10"/>
+      <c r="G300" s="14"/>
+      <c r="H300" s="14"/>
+      <c r="L300" s="15"/>
+      <c r="M300" s="15"/>
     </row>
     <row r="301">
-      <c r="L301" s="10"/>
-      <c r="M301" s="10"/>
+      <c r="G301" s="14"/>
+      <c r="H301" s="14"/>
+      <c r="L301" s="15"/>
+      <c r="M301" s="15"/>
     </row>
     <row r="302">
-      <c r="L302" s="10"/>
-      <c r="M302" s="10"/>
+      <c r="G302" s="14"/>
+      <c r="H302" s="14"/>
+      <c r="L302" s="15"/>
+      <c r="M302" s="15"/>
     </row>
     <row r="303">
-      <c r="L303" s="10"/>
-      <c r="M303" s="10"/>
+      <c r="G303" s="14"/>
+      <c r="H303" s="14"/>
+      <c r="L303" s="15"/>
+      <c r="M303" s="15"/>
     </row>
     <row r="304">
-      <c r="L304" s="10"/>
-      <c r="M304" s="10"/>
+      <c r="G304" s="14"/>
+      <c r="H304" s="14"/>
+      <c r="L304" s="15"/>
+      <c r="M304" s="15"/>
     </row>
     <row r="305">
-      <c r="L305" s="10"/>
-      <c r="M305" s="10"/>
+      <c r="G305" s="14"/>
+      <c r="H305" s="14"/>
+      <c r="L305" s="15"/>
+      <c r="M305" s="15"/>
     </row>
     <row r="306">
-      <c r="L306" s="10"/>
-      <c r="M306" s="10"/>
+      <c r="G306" s="14"/>
+      <c r="H306" s="14"/>
+      <c r="L306" s="15"/>
+      <c r="M306" s="15"/>
     </row>
     <row r="307">
-      <c r="L307" s="10"/>
-      <c r="M307" s="10"/>
+      <c r="G307" s="14"/>
+      <c r="H307" s="14"/>
+      <c r="L307" s="15"/>
+      <c r="M307" s="15"/>
     </row>
     <row r="308">
-      <c r="L308" s="10"/>
-      <c r="M308" s="10"/>
+      <c r="G308" s="14"/>
+      <c r="H308" s="14"/>
+      <c r="L308" s="15"/>
+      <c r="M308" s="15"/>
     </row>
     <row r="309">
-      <c r="L309" s="10"/>
-      <c r="M309" s="10"/>
+      <c r="G309" s="14"/>
+      <c r="H309" s="14"/>
+      <c r="L309" s="15"/>
+      <c r="M309" s="15"/>
     </row>
     <row r="310">
-      <c r="L310" s="10"/>
-      <c r="M310" s="10"/>
+      <c r="G310" s="14"/>
+      <c r="H310" s="14"/>
+      <c r="L310" s="15"/>
+      <c r="M310" s="15"/>
     </row>
     <row r="311">
-      <c r="L311" s="10"/>
-      <c r="M311" s="10"/>
+      <c r="G311" s="14"/>
+      <c r="H311" s="14"/>
+      <c r="L311" s="15"/>
+      <c r="M311" s="15"/>
     </row>
     <row r="312">
-      <c r="L312" s="10"/>
-      <c r="M312" s="10"/>
+      <c r="G312" s="14"/>
+      <c r="H312" s="14"/>
+      <c r="L312" s="15"/>
+      <c r="M312" s="15"/>
     </row>
     <row r="313">
-      <c r="L313" s="10"/>
-      <c r="M313" s="10"/>
+      <c r="G313" s="14"/>
+      <c r="H313" s="14"/>
+      <c r="L313" s="15"/>
+      <c r="M313" s="15"/>
     </row>
     <row r="314">
-      <c r="L314" s="10"/>
-      <c r="M314" s="10"/>
+      <c r="G314" s="14"/>
+      <c r="H314" s="14"/>
+      <c r="L314" s="15"/>
+      <c r="M314" s="15"/>
     </row>
     <row r="315">
-      <c r="L315" s="10"/>
-      <c r="M315" s="10"/>
+      <c r="G315" s="14"/>
+      <c r="H315" s="14"/>
+      <c r="L315" s="15"/>
+      <c r="M315" s="15"/>
     </row>
     <row r="316">
-      <c r="L316" s="10"/>
-      <c r="M316" s="10"/>
+      <c r="G316" s="14"/>
+      <c r="H316" s="14"/>
+      <c r="L316" s="15"/>
+      <c r="M316" s="15"/>
     </row>
     <row r="317">
-      <c r="L317" s="10"/>
-      <c r="M317" s="10"/>
+      <c r="G317" s="14"/>
+      <c r="H317" s="14"/>
+      <c r="L317" s="15"/>
+      <c r="M317" s="15"/>
     </row>
     <row r="318">
-      <c r="L318" s="10"/>
-      <c r="M318" s="10"/>
+      <c r="G318" s="14"/>
+      <c r="H318" s="14"/>
+      <c r="L318" s="15"/>
+      <c r="M318" s="15"/>
     </row>
     <row r="319">
-      <c r="L319" s="10"/>
-      <c r="M319" s="10"/>
+      <c r="G319" s="14"/>
+      <c r="H319" s="14"/>
+      <c r="L319" s="15"/>
+      <c r="M319" s="15"/>
     </row>
     <row r="320">
-      <c r="L320" s="10"/>
-      <c r="M320" s="10"/>
+      <c r="G320" s="14"/>
+      <c r="H320" s="14"/>
+      <c r="L320" s="15"/>
+      <c r="M320" s="15"/>
     </row>
     <row r="321">
-      <c r="L321" s="10"/>
-      <c r="M321" s="10"/>
+      <c r="G321" s="14"/>
+      <c r="H321" s="14"/>
+      <c r="L321" s="15"/>
+      <c r="M321" s="15"/>
     </row>
     <row r="322">
-      <c r="L322" s="10"/>
-      <c r="M322" s="10"/>
+      <c r="G322" s="14"/>
+      <c r="H322" s="14"/>
+      <c r="L322" s="15"/>
+      <c r="M322" s="15"/>
     </row>
     <row r="323">
-      <c r="L323" s="10"/>
-      <c r="M323" s="10"/>
+      <c r="G323" s="14"/>
+      <c r="H323" s="14"/>
+      <c r="L323" s="15"/>
+      <c r="M323" s="15"/>
     </row>
     <row r="324">
-      <c r="L324" s="10"/>
-      <c r="M324" s="10"/>
+      <c r="G324" s="14"/>
+      <c r="H324" s="14"/>
+      <c r="L324" s="15"/>
+      <c r="M324" s="15"/>
     </row>
     <row r="325">
-      <c r="L325" s="10"/>
-      <c r="M325" s="10"/>
+      <c r="G325" s="14"/>
+      <c r="H325" s="14"/>
+      <c r="L325" s="15"/>
+      <c r="M325" s="15"/>
     </row>
     <row r="326">
-      <c r="L326" s="10"/>
-      <c r="M326" s="10"/>
+      <c r="G326" s="14"/>
+      <c r="H326" s="14"/>
+      <c r="L326" s="15"/>
+      <c r="M326" s="15"/>
     </row>
     <row r="327">
-      <c r="L327" s="10"/>
-      <c r="M327" s="10"/>
+      <c r="G327" s="14"/>
+      <c r="H327" s="14"/>
+      <c r="L327" s="15"/>
+      <c r="M327" s="15"/>
     </row>
     <row r="328">
-      <c r="L328" s="10"/>
-      <c r="M328" s="10"/>
+      <c r="G328" s="14"/>
+      <c r="H328" s="14"/>
+      <c r="L328" s="15"/>
+      <c r="M328" s="15"/>
     </row>
     <row r="329">
-      <c r="L329" s="10"/>
-      <c r="M329" s="10"/>
+      <c r="G329" s="14"/>
+      <c r="H329" s="14"/>
+      <c r="L329" s="15"/>
+      <c r="M329" s="15"/>
     </row>
     <row r="330">
-      <c r="L330" s="10"/>
-      <c r="M330" s="10"/>
+      <c r="G330" s="14"/>
+      <c r="H330" s="14"/>
+      <c r="L330" s="15"/>
+      <c r="M330" s="15"/>
     </row>
     <row r="331">
-      <c r="L331" s="10"/>
-      <c r="M331" s="10"/>
+      <c r="G331" s="14"/>
+      <c r="H331" s="14"/>
+      <c r="L331" s="15"/>
+      <c r="M331" s="15"/>
     </row>
     <row r="332">
-      <c r="L332" s="10"/>
-      <c r="M332" s="10"/>
+      <c r="G332" s="14"/>
+      <c r="H332" s="14"/>
+      <c r="L332" s="15"/>
+      <c r="M332" s="15"/>
     </row>
     <row r="333">
-      <c r="L333" s="10"/>
-      <c r="M333" s="10"/>
+      <c r="G333" s="14"/>
+      <c r="H333" s="14"/>
+      <c r="L333" s="15"/>
+      <c r="M333" s="15"/>
     </row>
     <row r="334">
-      <c r="L334" s="10"/>
-      <c r="M334" s="10"/>
+      <c r="G334" s="14"/>
+      <c r="H334" s="14"/>
+      <c r="L334" s="15"/>
+      <c r="M334" s="15"/>
     </row>
     <row r="335">
-      <c r="L335" s="10"/>
-      <c r="M335" s="10"/>
+      <c r="G335" s="14"/>
+      <c r="H335" s="14"/>
+      <c r="L335" s="15"/>
+      <c r="M335" s="15"/>
     </row>
     <row r="336">
-      <c r="L336" s="10"/>
-      <c r="M336" s="10"/>
+      <c r="G336" s="14"/>
+      <c r="H336" s="14"/>
+      <c r="L336" s="15"/>
+      <c r="M336" s="15"/>
     </row>
     <row r="337">
-      <c r="L337" s="10"/>
-      <c r="M337" s="10"/>
+      <c r="G337" s="14"/>
+      <c r="H337" s="14"/>
+      <c r="L337" s="15"/>
+      <c r="M337" s="15"/>
     </row>
     <row r="338">
-      <c r="L338" s="10"/>
-      <c r="M338" s="10"/>
+      <c r="G338" s="14"/>
+      <c r="H338" s="14"/>
+      <c r="L338" s="15"/>
+      <c r="M338" s="15"/>
     </row>
     <row r="339">
-      <c r="L339" s="10"/>
-      <c r="M339" s="10"/>
+      <c r="G339" s="14"/>
+      <c r="H339" s="14"/>
+      <c r="L339" s="15"/>
+      <c r="M339" s="15"/>
     </row>
     <row r="340">
-      <c r="L340" s="10"/>
-      <c r="M340" s="10"/>
+      <c r="G340" s="14"/>
+      <c r="H340" s="14"/>
+      <c r="L340" s="15"/>
+      <c r="M340" s="15"/>
     </row>
     <row r="341">
-      <c r="L341" s="10"/>
-      <c r="M341" s="10"/>
+      <c r="G341" s="14"/>
+      <c r="H341" s="14"/>
+      <c r="L341" s="15"/>
+      <c r="M341" s="15"/>
     </row>
     <row r="342">
-      <c r="L342" s="10"/>
-      <c r="M342" s="10"/>
+      <c r="G342" s="14"/>
+      <c r="H342" s="14"/>
+      <c r="L342" s="15"/>
+      <c r="M342" s="15"/>
     </row>
     <row r="343">
-      <c r="L343" s="10"/>
-      <c r="M343" s="10"/>
+      <c r="G343" s="14"/>
+      <c r="H343" s="14"/>
+      <c r="L343" s="15"/>
+      <c r="M343" s="15"/>
     </row>
     <row r="344">
-      <c r="L344" s="10"/>
-      <c r="M344" s="10"/>
+      <c r="G344" s="14"/>
+      <c r="H344" s="14"/>
+      <c r="L344" s="15"/>
+      <c r="M344" s="15"/>
     </row>
     <row r="345">
-      <c r="L345" s="10"/>
-      <c r="M345" s="10"/>
+      <c r="G345" s="14"/>
+      <c r="H345" s="14"/>
+      <c r="L345" s="15"/>
+      <c r="M345" s="15"/>
     </row>
     <row r="346">
-      <c r="L346" s="10"/>
-      <c r="M346" s="10"/>
+      <c r="G346" s="14"/>
+      <c r="H346" s="14"/>
+      <c r="L346" s="15"/>
+      <c r="M346" s="15"/>
     </row>
     <row r="347">
-      <c r="L347" s="10"/>
-      <c r="M347" s="10"/>
+      <c r="G347" s="14"/>
+      <c r="H347" s="14"/>
+      <c r="L347" s="15"/>
+      <c r="M347" s="15"/>
     </row>
     <row r="348">
-      <c r="L348" s="10"/>
-      <c r="M348" s="10"/>
+      <c r="G348" s="14"/>
+      <c r="H348" s="14"/>
+      <c r="L348" s="15"/>
+      <c r="M348" s="15"/>
     </row>
     <row r="349">
-      <c r="L349" s="10"/>
-      <c r="M349" s="10"/>
+      <c r="G349" s="14"/>
+      <c r="H349" s="14"/>
+      <c r="L349" s="15"/>
+      <c r="M349" s="15"/>
     </row>
     <row r="350">
-      <c r="L350" s="10"/>
-      <c r="M350" s="10"/>
+      <c r="G350" s="14"/>
+      <c r="H350" s="14"/>
+      <c r="L350" s="15"/>
+      <c r="M350" s="15"/>
     </row>
     <row r="351">
-      <c r="L351" s="10"/>
-      <c r="M351" s="10"/>
+      <c r="G351" s="14"/>
+      <c r="H351" s="14"/>
+      <c r="L351" s="15"/>
+      <c r="M351" s="15"/>
     </row>
     <row r="352">
-      <c r="L352" s="10"/>
-      <c r="M352" s="10"/>
+      <c r="G352" s="14"/>
+      <c r="H352" s="14"/>
+      <c r="L352" s="15"/>
+      <c r="M352" s="15"/>
     </row>
     <row r="353">
-      <c r="L353" s="10"/>
-      <c r="M353" s="10"/>
+      <c r="G353" s="14"/>
+      <c r="H353" s="14"/>
+      <c r="L353" s="15"/>
+      <c r="M353" s="15"/>
     </row>
     <row r="354">
-      <c r="L354" s="10"/>
-      <c r="M354" s="10"/>
+      <c r="G354" s="14"/>
+      <c r="H354" s="14"/>
+      <c r="L354" s="15"/>
+      <c r="M354" s="15"/>
     </row>
     <row r="355">
-      <c r="L355" s="10"/>
-      <c r="M355" s="10"/>
+      <c r="G355" s="14"/>
+      <c r="H355" s="14"/>
+      <c r="L355" s="15"/>
+      <c r="M355" s="15"/>
     </row>
     <row r="356">
-      <c r="L356" s="10"/>
-      <c r="M356" s="10"/>
+      <c r="G356" s="14"/>
+      <c r="H356" s="14"/>
+      <c r="L356" s="15"/>
+      <c r="M356" s="15"/>
     </row>
     <row r="357">
-      <c r="L357" s="10"/>
-      <c r="M357" s="10"/>
+      <c r="G357" s="14"/>
+      <c r="H357" s="14"/>
+      <c r="L357" s="15"/>
+      <c r="M357" s="15"/>
     </row>
     <row r="358">
-      <c r="L358" s="10"/>
-      <c r="M358" s="10"/>
+      <c r="G358" s="14"/>
+      <c r="H358" s="14"/>
+      <c r="L358" s="15"/>
+      <c r="M358" s="15"/>
     </row>
     <row r="359">
-      <c r="L359" s="10"/>
-      <c r="M359" s="10"/>
+      <c r="G359" s="14"/>
+      <c r="H359" s="14"/>
+      <c r="L359" s="15"/>
+      <c r="M359" s="15"/>
     </row>
     <row r="360">
-      <c r="L360" s="10"/>
-      <c r="M360" s="10"/>
+      <c r="G360" s="14"/>
+      <c r="H360" s="14"/>
+      <c r="L360" s="15"/>
+      <c r="M360" s="15"/>
     </row>
     <row r="361">
-      <c r="L361" s="10"/>
-      <c r="M361" s="10"/>
+      <c r="G361" s="14"/>
+      <c r="H361" s="14"/>
+      <c r="L361" s="15"/>
+      <c r="M361" s="15"/>
     </row>
     <row r="362">
-      <c r="L362" s="10"/>
-      <c r="M362" s="10"/>
+      <c r="G362" s="14"/>
+      <c r="H362" s="14"/>
+      <c r="L362" s="15"/>
+      <c r="M362" s="15"/>
     </row>
     <row r="363">
-      <c r="L363" s="10"/>
-      <c r="M363" s="10"/>
+      <c r="G363" s="14"/>
+      <c r="H363" s="14"/>
+      <c r="L363" s="15"/>
+      <c r="M363" s="15"/>
     </row>
     <row r="364">
-      <c r="L364" s="10"/>
-      <c r="M364" s="10"/>
+      <c r="G364" s="14"/>
+      <c r="H364" s="14"/>
+      <c r="L364" s="15"/>
+      <c r="M364" s="15"/>
     </row>
     <row r="365">
-      <c r="L365" s="10"/>
-      <c r="M365" s="10"/>
+      <c r="G365" s="14"/>
+      <c r="H365" s="14"/>
+      <c r="L365" s="15"/>
+      <c r="M365" s="15"/>
     </row>
     <row r="366">
-      <c r="L366" s="10"/>
-      <c r="M366" s="10"/>
+      <c r="G366" s="14"/>
+      <c r="H366" s="14"/>
+      <c r="L366" s="15"/>
+      <c r="M366" s="15"/>
     </row>
     <row r="367">
-      <c r="L367" s="10"/>
-      <c r="M367" s="10"/>
+      <c r="G367" s="14"/>
+      <c r="H367" s="14"/>
+      <c r="L367" s="15"/>
+      <c r="M367" s="15"/>
     </row>
     <row r="368">
-      <c r="L368" s="10"/>
-      <c r="M368" s="10"/>
+      <c r="G368" s="14"/>
+      <c r="H368" s="14"/>
+      <c r="L368" s="15"/>
+      <c r="M368" s="15"/>
     </row>
     <row r="369">
-      <c r="L369" s="10"/>
-      <c r="M369" s="10"/>
+      <c r="G369" s="14"/>
+      <c r="H369" s="14"/>
+      <c r="L369" s="15"/>
+      <c r="M369" s="15"/>
     </row>
     <row r="370">
-      <c r="L370" s="10"/>
-      <c r="M370" s="10"/>
+      <c r="G370" s="14"/>
+      <c r="H370" s="14"/>
+      <c r="L370" s="15"/>
+      <c r="M370" s="15"/>
     </row>
     <row r="371">
-      <c r="L371" s="10"/>
-      <c r="M371" s="10"/>
+      <c r="G371" s="14"/>
+      <c r="H371" s="14"/>
+      <c r="L371" s="15"/>
+      <c r="M371" s="15"/>
     </row>
     <row r="372">
-      <c r="L372" s="10"/>
-      <c r="M372" s="10"/>
+      <c r="G372" s="14"/>
+      <c r="H372" s="14"/>
+      <c r="L372" s="15"/>
+      <c r="M372" s="15"/>
     </row>
     <row r="373">
-      <c r="L373" s="10"/>
-      <c r="M373" s="10"/>
+      <c r="G373" s="14"/>
+      <c r="H373" s="14"/>
+      <c r="L373" s="15"/>
+      <c r="M373" s="15"/>
     </row>
     <row r="374">
-      <c r="L374" s="10"/>
-      <c r="M374" s="10"/>
+      <c r="G374" s="14"/>
+      <c r="H374" s="14"/>
+      <c r="L374" s="15"/>
+      <c r="M374" s="15"/>
     </row>
     <row r="375">
-      <c r="L375" s="10"/>
-      <c r="M375" s="10"/>
+      <c r="G375" s="14"/>
+      <c r="H375" s="14"/>
+      <c r="L375" s="15"/>
+      <c r="M375" s="15"/>
     </row>
     <row r="376">
-      <c r="L376" s="10"/>
-      <c r="M376" s="10"/>
+      <c r="G376" s="14"/>
+      <c r="H376" s="14"/>
+      <c r="L376" s="15"/>
+      <c r="M376" s="15"/>
     </row>
     <row r="377">
-      <c r="L377" s="10"/>
-      <c r="M377" s="10"/>
+      <c r="G377" s="14"/>
+      <c r="H377" s="14"/>
+      <c r="L377" s="15"/>
+      <c r="M377" s="15"/>
     </row>
     <row r="378">
-      <c r="L378" s="10"/>
-      <c r="M378" s="10"/>
+      <c r="G378" s="14"/>
+      <c r="H378" s="14"/>
+      <c r="L378" s="15"/>
+      <c r="M378" s="15"/>
     </row>
     <row r="379">
-      <c r="L379" s="10"/>
-      <c r="M379" s="10"/>
+      <c r="G379" s="14"/>
+      <c r="H379" s="14"/>
+      <c r="L379" s="15"/>
+      <c r="M379" s="15"/>
     </row>
     <row r="380">
-      <c r="L380" s="10"/>
-      <c r="M380" s="10"/>
+      <c r="G380" s="14"/>
+      <c r="H380" s="14"/>
+      <c r="L380" s="15"/>
+      <c r="M380" s="15"/>
     </row>
     <row r="381">
-      <c r="L381" s="10"/>
-      <c r="M381" s="10"/>
+      <c r="G381" s="14"/>
+      <c r="H381" s="14"/>
+      <c r="L381" s="15"/>
+      <c r="M381" s="15"/>
     </row>
     <row r="382">
-      <c r="L382" s="10"/>
-      <c r="M382" s="10"/>
+      <c r="G382" s="14"/>
+      <c r="H382" s="14"/>
+      <c r="L382" s="15"/>
+      <c r="M382" s="15"/>
     </row>
     <row r="383">
-      <c r="L383" s="10"/>
-      <c r="M383" s="10"/>
+      <c r="G383" s="14"/>
+      <c r="H383" s="14"/>
+      <c r="L383" s="15"/>
+      <c r="M383" s="15"/>
     </row>
     <row r="384">
-      <c r="L384" s="10"/>
-      <c r="M384" s="10"/>
+      <c r="G384" s="14"/>
+      <c r="H384" s="14"/>
+      <c r="L384" s="15"/>
+      <c r="M384" s="15"/>
     </row>
     <row r="385">
-      <c r="L385" s="10"/>
-      <c r="M385" s="10"/>
+      <c r="G385" s="14"/>
+      <c r="H385" s="14"/>
+      <c r="L385" s="15"/>
+      <c r="M385" s="15"/>
     </row>
     <row r="386">
-      <c r="L386" s="10"/>
-      <c r="M386" s="10"/>
+      <c r="G386" s="14"/>
+      <c r="H386" s="14"/>
+      <c r="L386" s="15"/>
+      <c r="M386" s="15"/>
     </row>
     <row r="387">
-      <c r="L387" s="10"/>
-      <c r="M387" s="10"/>
+      <c r="G387" s="14"/>
+      <c r="H387" s="14"/>
+      <c r="L387" s="15"/>
+      <c r="M387" s="15"/>
     </row>
     <row r="388">
-      <c r="L388" s="10"/>
-      <c r="M388" s="10"/>
+      <c r="G388" s="14"/>
+      <c r="H388" s="14"/>
+      <c r="L388" s="15"/>
+      <c r="M388" s="15"/>
     </row>
     <row r="389">
-      <c r="L389" s="10"/>
-      <c r="M389" s="10"/>
+      <c r="G389" s="14"/>
+      <c r="H389" s="14"/>
+      <c r="L389" s="15"/>
+      <c r="M389" s="15"/>
     </row>
     <row r="390">
-      <c r="L390" s="10"/>
-      <c r="M390" s="10"/>
+      <c r="G390" s="14"/>
+      <c r="H390" s="14"/>
+      <c r="L390" s="15"/>
+      <c r="M390" s="15"/>
     </row>
     <row r="391">
-      <c r="L391" s="10"/>
-      <c r="M391" s="10"/>
+      <c r="G391" s="14"/>
+      <c r="H391" s="14"/>
+      <c r="L391" s="15"/>
+      <c r="M391" s="15"/>
     </row>
     <row r="392">
-      <c r="L392" s="10"/>
-      <c r="M392" s="10"/>
+      <c r="G392" s="14"/>
+      <c r="H392" s="14"/>
+      <c r="L392" s="15"/>
+      <c r="M392" s="15"/>
     </row>
     <row r="393">
-      <c r="L393" s="10"/>
-      <c r="M393" s="10"/>
+      <c r="G393" s="14"/>
+      <c r="H393" s="14"/>
+      <c r="L393" s="15"/>
+      <c r="M393" s="15"/>
     </row>
     <row r="394">
-      <c r="L394" s="10"/>
-      <c r="M394" s="10"/>
+      <c r="G394" s="14"/>
+      <c r="H394" s="14"/>
+      <c r="L394" s="15"/>
+      <c r="M394" s="15"/>
     </row>
     <row r="395">
-      <c r="L395" s="10"/>
-      <c r="M395" s="10"/>
+      <c r="G395" s="14"/>
+      <c r="H395" s="14"/>
+      <c r="L395" s="15"/>
+      <c r="M395" s="15"/>
     </row>
     <row r="396">
-      <c r="L396" s="10"/>
-      <c r="M396" s="10"/>
+      <c r="G396" s="14"/>
+      <c r="H396" s="14"/>
+      <c r="L396" s="15"/>
+      <c r="M396" s="15"/>
     </row>
     <row r="397">
-      <c r="L397" s="10"/>
-      <c r="M397" s="10"/>
+      <c r="G397" s="14"/>
+      <c r="H397" s="14"/>
+      <c r="L397" s="15"/>
+      <c r="M397" s="15"/>
     </row>
     <row r="398">
-      <c r="L398" s="10"/>
-      <c r="M398" s="10"/>
+      <c r="G398" s="14"/>
+      <c r="H398" s="14"/>
+      <c r="L398" s="15"/>
+      <c r="M398" s="15"/>
     </row>
     <row r="399">
-      <c r="L399" s="10"/>
-      <c r="M399" s="10"/>
+      <c r="G399" s="14"/>
+      <c r="H399" s="14"/>
+      <c r="L399" s="15"/>
+      <c r="M399" s="15"/>
     </row>
     <row r="400">
-      <c r="L400" s="10"/>
-      <c r="M400" s="10"/>
+      <c r="G400" s="14"/>
+      <c r="H400" s="14"/>
+      <c r="L400" s="15"/>
+      <c r="M400" s="15"/>
     </row>
     <row r="401">
-      <c r="L401" s="10"/>
-      <c r="M401" s="10"/>
+      <c r="G401" s="14"/>
+      <c r="H401" s="14"/>
+      <c r="L401" s="15"/>
+      <c r="M401" s="15"/>
     </row>
     <row r="402">
-      <c r="L402" s="10"/>
-      <c r="M402" s="10"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="L402" s="15"/>
+      <c r="M402" s="15"/>
     </row>
     <row r="403">
-      <c r="L403" s="10"/>
-      <c r="M403" s="10"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="L403" s="15"/>
+      <c r="M403" s="15"/>
     </row>
     <row r="404">
-      <c r="L404" s="10"/>
-      <c r="M404" s="10"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="L404" s="15"/>
+      <c r="M404" s="15"/>
     </row>
     <row r="405">
-      <c r="L405" s="10"/>
-      <c r="M405" s="10"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="L405" s="15"/>
+      <c r="M405" s="15"/>
     </row>
     <row r="406">
-      <c r="L406" s="10"/>
-      <c r="M406" s="10"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="L406" s="15"/>
+      <c r="M406" s="15"/>
     </row>
     <row r="407">
-      <c r="L407" s="10"/>
-      <c r="M407" s="10"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="L407" s="15"/>
+      <c r="M407" s="15"/>
     </row>
     <row r="408">
-      <c r="L408" s="10"/>
-      <c r="M408" s="10"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="L408" s="15"/>
+      <c r="M408" s="15"/>
     </row>
     <row r="409">
-      <c r="L409" s="10"/>
-      <c r="M409" s="10"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="L409" s="15"/>
+      <c r="M409" s="15"/>
     </row>
     <row r="410">
-      <c r="L410" s="10"/>
-      <c r="M410" s="10"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="L410" s="15"/>
+      <c r="M410" s="15"/>
     </row>
     <row r="411">
-      <c r="L411" s="10"/>
-      <c r="M411" s="10"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="L411" s="15"/>
+      <c r="M411" s="15"/>
     </row>
     <row r="412">
-      <c r="L412" s="10"/>
-      <c r="M412" s="10"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="L412" s="15"/>
+      <c r="M412" s="15"/>
     </row>
     <row r="413">
-      <c r="L413" s="10"/>
-      <c r="M413" s="10"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="L413" s="15"/>
+      <c r="M413" s="15"/>
     </row>
     <row r="414">
-      <c r="L414" s="10"/>
-      <c r="M414" s="10"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="L414" s="15"/>
+      <c r="M414" s="15"/>
     </row>
     <row r="415">
-      <c r="L415" s="10"/>
-      <c r="M415" s="10"/>
+      <c r="G415" s="14"/>
+      <c r="H415" s="14"/>
+      <c r="L415" s="15"/>
+      <c r="M415" s="15"/>
     </row>
     <row r="416">
-      <c r="L416" s="10"/>
-      <c r="M416" s="10"/>
+      <c r="G416" s="14"/>
+      <c r="H416" s="14"/>
+      <c r="L416" s="15"/>
+      <c r="M416" s="15"/>
     </row>
     <row r="417">
-      <c r="L417" s="10"/>
-      <c r="M417" s="10"/>
+      <c r="G417" s="14"/>
+      <c r="H417" s="14"/>
+      <c r="L417" s="15"/>
+      <c r="M417" s="15"/>
     </row>
     <row r="418">
-      <c r="L418" s="10"/>
-      <c r="M418" s="10"/>
+      <c r="G418" s="14"/>
+      <c r="H418" s="14"/>
+      <c r="L418" s="15"/>
+      <c r="M418" s="15"/>
     </row>
     <row r="419">
-      <c r="L419" s="10"/>
-      <c r="M419" s="10"/>
+      <c r="G419" s="14"/>
+      <c r="H419" s="14"/>
+      <c r="L419" s="15"/>
+      <c r="M419" s="15"/>
     </row>
     <row r="420">
-      <c r="L420" s="10"/>
-      <c r="M420" s="10"/>
+      <c r="G420" s="14"/>
+      <c r="H420" s="14"/>
+      <c r="L420" s="15"/>
+      <c r="M420" s="15"/>
     </row>
     <row r="421">
-      <c r="L421" s="10"/>
-      <c r="M421" s="10"/>
+      <c r="G421" s="14"/>
+      <c r="H421" s="14"/>
+      <c r="L421" s="15"/>
+      <c r="M421" s="15"/>
     </row>
     <row r="422">
-      <c r="L422" s="10"/>
-      <c r="M422" s="10"/>
+      <c r="G422" s="14"/>
+      <c r="H422" s="14"/>
+      <c r="L422" s="15"/>
+      <c r="M422" s="15"/>
     </row>
     <row r="423">
-      <c r="L423" s="10"/>
-      <c r="M423" s="10"/>
+      <c r="G423" s="14"/>
+      <c r="H423" s="14"/>
+      <c r="L423" s="15"/>
+      <c r="M423" s="15"/>
     </row>
     <row r="424">
-      <c r="L424" s="10"/>
-      <c r="M424" s="10"/>
+      <c r="G424" s="14"/>
+      <c r="H424" s="14"/>
+      <c r="L424" s="15"/>
+      <c r="M424" s="15"/>
     </row>
     <row r="425">
-      <c r="L425" s="10"/>
-      <c r="M425" s="10"/>
+      <c r="G425" s="14"/>
+      <c r="H425" s="14"/>
+      <c r="L425" s="15"/>
+      <c r="M425" s="15"/>
     </row>
     <row r="426">
-      <c r="L426" s="10"/>
-      <c r="M426" s="10"/>
+      <c r="G426" s="14"/>
+      <c r="H426" s="14"/>
+      <c r="L426" s="15"/>
+      <c r="M426" s="15"/>
     </row>
     <row r="427">
-      <c r="L427" s="10"/>
-      <c r="M427" s="10"/>
+      <c r="G427" s="14"/>
+      <c r="H427" s="14"/>
+      <c r="L427" s="15"/>
+      <c r="M427" s="15"/>
     </row>
     <row r="428">
-      <c r="L428" s="10"/>
-      <c r="M428" s="10"/>
+      <c r="G428" s="14"/>
+      <c r="H428" s="14"/>
+      <c r="L428" s="15"/>
+      <c r="M428" s="15"/>
     </row>
     <row r="429">
-      <c r="L429" s="10"/>
-      <c r="M429" s="10"/>
+      <c r="G429" s="14"/>
+      <c r="H429" s="14"/>
+      <c r="L429" s="15"/>
+      <c r="M429" s="15"/>
     </row>
     <row r="430">
-      <c r="L430" s="10"/>
-      <c r="M430" s="10"/>
+      <c r="G430" s="14"/>
+      <c r="H430" s="14"/>
+      <c r="L430" s="15"/>
+      <c r="M430" s="15"/>
     </row>
     <row r="431">
-      <c r="L431" s="10"/>
-      <c r="M431" s="10"/>
+      <c r="G431" s="14"/>
+      <c r="H431" s="14"/>
+      <c r="L431" s="15"/>
+      <c r="M431" s="15"/>
     </row>
     <row r="432">
-      <c r="L432" s="10"/>
-      <c r="M432" s="10"/>
+      <c r="G432" s="14"/>
+      <c r="H432" s="14"/>
+      <c r="L432" s="15"/>
+      <c r="M432" s="15"/>
     </row>
     <row r="433">
-      <c r="L433" s="10"/>
-      <c r="M433" s="10"/>
+      <c r="G433" s="14"/>
+      <c r="H433" s="14"/>
+      <c r="L433" s="15"/>
+      <c r="M433" s="15"/>
     </row>
     <row r="434">
-      <c r="L434" s="10"/>
-      <c r="M434" s="10"/>
+      <c r="G434" s="14"/>
+      <c r="H434" s="14"/>
+      <c r="L434" s="15"/>
+      <c r="M434" s="15"/>
     </row>
     <row r="435">
-      <c r="L435" s="10"/>
-      <c r="M435" s="10"/>
+      <c r="G435" s="14"/>
+      <c r="H435" s="14"/>
+      <c r="L435" s="15"/>
+      <c r="M435" s="15"/>
     </row>
     <row r="436">
-      <c r="L436" s="10"/>
-      <c r="M436" s="10"/>
+      <c r="G436" s="14"/>
+      <c r="H436" s="14"/>
+      <c r="L436" s="15"/>
+      <c r="M436" s="15"/>
     </row>
     <row r="437">
-      <c r="L437" s="10"/>
-      <c r="M437" s="10"/>
+      <c r="G437" s="14"/>
+      <c r="H437" s="14"/>
+      <c r="L437" s="15"/>
+      <c r="M437" s="15"/>
     </row>
     <row r="438">
-      <c r="L438" s="10"/>
-      <c r="M438" s="10"/>
+      <c r="G438" s="14"/>
+      <c r="H438" s="14"/>
+      <c r="L438" s="15"/>
+      <c r="M438" s="15"/>
     </row>
     <row r="439">
-      <c r="L439" s="10"/>
-      <c r="M439" s="10"/>
+      <c r="G439" s="14"/>
+      <c r="H439" s="14"/>
+      <c r="L439" s="15"/>
+      <c r="M439" s="15"/>
     </row>
     <row r="440">
-      <c r="L440" s="10"/>
-      <c r="M440" s="10"/>
+      <c r="G440" s="14"/>
+      <c r="H440" s="14"/>
+      <c r="L440" s="15"/>
+      <c r="M440" s="15"/>
     </row>
     <row r="441">
-      <c r="L441" s="10"/>
-      <c r="M441" s="10"/>
+      <c r="G441" s="14"/>
+      <c r="H441" s="14"/>
+      <c r="L441" s="15"/>
+      <c r="M441" s="15"/>
     </row>
     <row r="442">
-      <c r="L442" s="10"/>
-      <c r="M442" s="10"/>
+      <c r="G442" s="14"/>
+      <c r="H442" s="14"/>
+      <c r="L442" s="15"/>
+      <c r="M442" s="15"/>
     </row>
     <row r="443">
-      <c r="L443" s="10"/>
-      <c r="M443" s="10"/>
+      <c r="G443" s="14"/>
+      <c r="H443" s="14"/>
+      <c r="L443" s="15"/>
+      <c r="M443" s="15"/>
     </row>
     <row r="444">
-      <c r="L444" s="10"/>
-      <c r="M444" s="10"/>
+      <c r="G444" s="14"/>
+      <c r="H444" s="14"/>
+      <c r="L444" s="15"/>
+      <c r="M444" s="15"/>
     </row>
     <row r="445">
-      <c r="L445" s="10"/>
-      <c r="M445" s="10"/>
+      <c r="G445" s="14"/>
+      <c r="H445" s="14"/>
+      <c r="L445" s="15"/>
+      <c r="M445" s="15"/>
     </row>
     <row r="446">
-      <c r="L446" s="10"/>
-      <c r="M446" s="10"/>
+      <c r="G446" s="14"/>
+      <c r="H446" s="14"/>
+      <c r="L446" s="15"/>
+      <c r="M446" s="15"/>
     </row>
     <row r="447">
-      <c r="L447" s="10"/>
-      <c r="M447" s="10"/>
+      <c r="G447" s="14"/>
+      <c r="H447" s="14"/>
+      <c r="L447" s="15"/>
+      <c r="M447" s="15"/>
     </row>
     <row r="448">
-      <c r="L448" s="10"/>
-      <c r="M448" s="10"/>
+      <c r="G448" s="14"/>
+      <c r="H448" s="14"/>
+      <c r="L448" s="15"/>
+      <c r="M448" s="15"/>
     </row>
     <row r="449">
-      <c r="L449" s="10"/>
-      <c r="M449" s="10"/>
+      <c r="G449" s="14"/>
+      <c r="H449" s="14"/>
+      <c r="L449" s="15"/>
+      <c r="M449" s="15"/>
     </row>
     <row r="450">
-      <c r="L450" s="10"/>
-      <c r="M450" s="10"/>
+      <c r="G450" s="14"/>
+      <c r="H450" s="14"/>
+      <c r="L450" s="15"/>
+      <c r="M450" s="15"/>
     </row>
     <row r="451">
-      <c r="L451" s="10"/>
-      <c r="M451" s="10"/>
+      <c r="G451" s="14"/>
+      <c r="H451" s="14"/>
+      <c r="L451" s="15"/>
+      <c r="M451" s="15"/>
     </row>
     <row r="452">
-      <c r="L452" s="10"/>
-      <c r="M452" s="10"/>
+      <c r="G452" s="14"/>
+      <c r="H452" s="14"/>
+      <c r="L452" s="15"/>
+      <c r="M452" s="15"/>
     </row>
     <row r="453">
-      <c r="L453" s="10"/>
-      <c r="M453" s="10"/>
+      <c r="G453" s="14"/>
+      <c r="H453" s="14"/>
+      <c r="L453" s="15"/>
+      <c r="M453" s="15"/>
     </row>
     <row r="454">
-      <c r="L454" s="10"/>
-      <c r="M454" s="10"/>
+      <c r="G454" s="14"/>
+      <c r="H454" s="14"/>
+      <c r="L454" s="15"/>
+      <c r="M454" s="15"/>
     </row>
     <row r="455">
-      <c r="L455" s="10"/>
-      <c r="M455" s="10"/>
+      <c r="G455" s="14"/>
+      <c r="H455" s="14"/>
+      <c r="L455" s="15"/>
+      <c r="M455" s="15"/>
     </row>
     <row r="456">
-      <c r="L456" s="10"/>
-      <c r="M456" s="10"/>
+      <c r="G456" s="14"/>
+      <c r="H456" s="14"/>
+      <c r="L456" s="15"/>
+      <c r="M456" s="15"/>
     </row>
     <row r="457">
-      <c r="L457" s="10"/>
-      <c r="M457" s="10"/>
+      <c r="G457" s="14"/>
+      <c r="H457" s="14"/>
+      <c r="L457" s="15"/>
+      <c r="M457" s="15"/>
     </row>
     <row r="458">
-      <c r="L458" s="10"/>
-      <c r="M458" s="10"/>
+      <c r="G458" s="14"/>
+      <c r="H458" s="14"/>
+      <c r="L458" s="15"/>
+      <c r="M458" s="15"/>
     </row>
     <row r="459">
-      <c r="L459" s="10"/>
-      <c r="M459" s="10"/>
+      <c r="G459" s="14"/>
+      <c r="H459" s="14"/>
+      <c r="L459" s="15"/>
+      <c r="M459" s="15"/>
     </row>
     <row r="460">
-      <c r="L460" s="10"/>
-      <c r="M460" s="10"/>
+      <c r="G460" s="14"/>
+      <c r="H460" s="14"/>
+      <c r="L460" s="15"/>
+      <c r="M460" s="15"/>
     </row>
     <row r="461">
-      <c r="L461" s="10"/>
-      <c r="M461" s="10"/>
+      <c r="G461" s="14"/>
+      <c r="H461" s="14"/>
+      <c r="L461" s="15"/>
+      <c r="M461" s="15"/>
     </row>
     <row r="462">
-      <c r="L462" s="10"/>
-      <c r="M462" s="10"/>
+      <c r="G462" s="14"/>
+      <c r="H462" s="14"/>
+      <c r="L462" s="15"/>
+      <c r="M462" s="15"/>
     </row>
     <row r="463">
-      <c r="L463" s="10"/>
-      <c r="M463" s="10"/>
+      <c r="G463" s="14"/>
+      <c r="H463" s="14"/>
+      <c r="L463" s="15"/>
+      <c r="M463" s="15"/>
     </row>
     <row r="464">
-      <c r="L464" s="10"/>
-      <c r="M464" s="10"/>
+      <c r="G464" s="14"/>
+      <c r="H464" s="14"/>
+      <c r="L464" s="15"/>
+      <c r="M464" s="15"/>
     </row>
     <row r="465">
-      <c r="L465" s="10"/>
-      <c r="M465" s="10"/>
+      <c r="G465" s="14"/>
+      <c r="H465" s="14"/>
+      <c r="L465" s="15"/>
+      <c r="M465" s="15"/>
     </row>
     <row r="466">
-      <c r="L466" s="10"/>
-      <c r="M466" s="10"/>
+      <c r="G466" s="14"/>
+      <c r="H466" s="14"/>
+      <c r="L466" s="15"/>
+      <c r="M466" s="15"/>
     </row>
     <row r="467">
-      <c r="L467" s="10"/>
-      <c r="M467" s="10"/>
+      <c r="G467" s="14"/>
+      <c r="H467" s="14"/>
+      <c r="L467" s="15"/>
+      <c r="M467" s="15"/>
     </row>
     <row r="468">
-      <c r="L468" s="10"/>
-      <c r="M468" s="10"/>
+      <c r="G468" s="14"/>
+      <c r="H468" s="14"/>
+      <c r="L468" s="15"/>
+      <c r="M468" s="15"/>
     </row>
     <row r="469">
-      <c r="L469" s="10"/>
-      <c r="M469" s="10"/>
+      <c r="G469" s="14"/>
+      <c r="H469" s="14"/>
+      <c r="L469" s="15"/>
+      <c r="M469" s="15"/>
     </row>
     <row r="470">
-      <c r="L470" s="10"/>
-      <c r="M470" s="10"/>
+      <c r="G470" s="14"/>
+      <c r="H470" s="14"/>
+      <c r="L470" s="15"/>
+      <c r="M470" s="15"/>
     </row>
     <row r="471">
-      <c r="L471" s="10"/>
-      <c r="M471" s="10"/>
+      <c r="G471" s="14"/>
+      <c r="H471" s="14"/>
+      <c r="L471" s="15"/>
+      <c r="M471" s="15"/>
     </row>
     <row r="472">
-      <c r="L472" s="10"/>
-      <c r="M472" s="10"/>
+      <c r="G472" s="14"/>
+      <c r="H472" s="14"/>
+      <c r="L472" s="15"/>
+      <c r="M472" s="15"/>
     </row>
     <row r="473">
-      <c r="L473" s="10"/>
-      <c r="M473" s="10"/>
+      <c r="G473" s="14"/>
+      <c r="H473" s="14"/>
+      <c r="L473" s="15"/>
+      <c r="M473" s="15"/>
     </row>
     <row r="474">
-      <c r="L474" s="10"/>
-      <c r="M474" s="10"/>
+      <c r="G474" s="14"/>
+      <c r="H474" s="14"/>
+      <c r="L474" s="15"/>
+      <c r="M474" s="15"/>
     </row>
     <row r="475">
-      <c r="L475" s="10"/>
-      <c r="M475" s="10"/>
+      <c r="G475" s="14"/>
+      <c r="H475" s="14"/>
+      <c r="L475" s="15"/>
+      <c r="M475" s="15"/>
     </row>
     <row r="476">
-      <c r="L476" s="10"/>
-      <c r="M476" s="10"/>
+      <c r="G476" s="14"/>
+      <c r="H476" s="14"/>
+      <c r="L476" s="15"/>
+      <c r="M476" s="15"/>
     </row>
     <row r="477">
-      <c r="L477" s="10"/>
-      <c r="M477" s="10"/>
+      <c r="G477" s="14"/>
+      <c r="H477" s="14"/>
+      <c r="L477" s="15"/>
+      <c r="M477" s="15"/>
     </row>
     <row r="478">
-      <c r="L478" s="10"/>
-      <c r="M478" s="10"/>
+      <c r="G478" s="14"/>
+      <c r="H478" s="14"/>
+      <c r="L478" s="15"/>
+      <c r="M478" s="15"/>
     </row>
     <row r="479">
-      <c r="L479" s="10"/>
-      <c r="M479" s="10"/>
+      <c r="G479" s="14"/>
+      <c r="H479" s="14"/>
+      <c r="L479" s="15"/>
+      <c r="M479" s="15"/>
     </row>
     <row r="480">
-      <c r="L480" s="10"/>
-      <c r="M480" s="10"/>
+      <c r="G480" s="14"/>
+      <c r="H480" s="14"/>
+      <c r="L480" s="15"/>
+      <c r="M480" s="15"/>
     </row>
     <row r="481">
-      <c r="L481" s="10"/>
-      <c r="M481" s="10"/>
+      <c r="G481" s="14"/>
+      <c r="H481" s="14"/>
+      <c r="L481" s="15"/>
+      <c r="M481" s="15"/>
     </row>
     <row r="482">
-      <c r="L482" s="10"/>
-      <c r="M482" s="10"/>
+      <c r="G482" s="14"/>
+      <c r="H482" s="14"/>
+      <c r="L482" s="15"/>
+      <c r="M482" s="15"/>
     </row>
     <row r="483">
-      <c r="L483" s="10"/>
-      <c r="M483" s="10"/>
+      <c r="G483" s="14"/>
+      <c r="H483" s="14"/>
+      <c r="L483" s="15"/>
+      <c r="M483" s="15"/>
     </row>
     <row r="484">
-      <c r="L484" s="10"/>
-      <c r="M484" s="10"/>
+      <c r="G484" s="14"/>
+      <c r="H484" s="14"/>
+      <c r="L484" s="15"/>
+      <c r="M484" s="15"/>
     </row>
     <row r="485">
-      <c r="L485" s="10"/>
-      <c r="M485" s="10"/>
+      <c r="G485" s="14"/>
+      <c r="H485" s="14"/>
+      <c r="L485" s="15"/>
+      <c r="M485" s="15"/>
     </row>
     <row r="486">
-      <c r="L486" s="10"/>
-      <c r="M486" s="10"/>
+      <c r="G486" s="14"/>
+      <c r="H486" s="14"/>
+      <c r="L486" s="15"/>
+      <c r="M486" s="15"/>
     </row>
     <row r="487">
-      <c r="L487" s="10"/>
-      <c r="M487" s="10"/>
+      <c r="G487" s="14"/>
+      <c r="H487" s="14"/>
+      <c r="L487" s="15"/>
+      <c r="M487" s="15"/>
     </row>
     <row r="488">
-      <c r="L488" s="10"/>
-      <c r="M488" s="10"/>
+      <c r="G488" s="14"/>
+      <c r="H488" s="14"/>
+      <c r="L488" s="15"/>
+      <c r="M488" s="15"/>
     </row>
     <row r="489">
-      <c r="L489" s="10"/>
-      <c r="M489" s="10"/>
+      <c r="G489" s="14"/>
+      <c r="H489" s="14"/>
+      <c r="L489" s="15"/>
+      <c r="M489" s="15"/>
     </row>
     <row r="490">
-      <c r="L490" s="10"/>
-      <c r="M490" s="10"/>
+      <c r="G490" s="14"/>
+      <c r="H490" s="14"/>
+      <c r="L490" s="15"/>
+      <c r="M490" s="15"/>
     </row>
     <row r="491">
-      <c r="L491" s="10"/>
-      <c r="M491" s="10"/>
+      <c r="G491" s="14"/>
+      <c r="H491" s="14"/>
+      <c r="L491" s="15"/>
+      <c r="M491" s="15"/>
     </row>
     <row r="492">
-      <c r="L492" s="10"/>
-      <c r="M492" s="10"/>
+      <c r="G492" s="14"/>
+      <c r="H492" s="14"/>
+      <c r="L492" s="15"/>
+      <c r="M492" s="15"/>
     </row>
     <row r="493">
-      <c r="L493" s="10"/>
-      <c r="M493" s="10"/>
+      <c r="G493" s="14"/>
+      <c r="H493" s="14"/>
+      <c r="L493" s="15"/>
+      <c r="M493" s="15"/>
     </row>
     <row r="494">
-      <c r="L494" s="10"/>
-      <c r="M494" s="10"/>
+      <c r="G494" s="14"/>
+      <c r="H494" s="14"/>
+      <c r="L494" s="15"/>
+      <c r="M494" s="15"/>
     </row>
     <row r="495">
-      <c r="L495" s="10"/>
-      <c r="M495" s="10"/>
+      <c r="G495" s="14"/>
+      <c r="H495" s="14"/>
+      <c r="L495" s="15"/>
+      <c r="M495" s="15"/>
     </row>
     <row r="496">
-      <c r="L496" s="10"/>
-      <c r="M496" s="10"/>
+      <c r="G496" s="14"/>
+      <c r="H496" s="14"/>
+      <c r="L496" s="15"/>
+      <c r="M496" s="15"/>
     </row>
     <row r="497">
-      <c r="L497" s="10"/>
-      <c r="M497" s="10"/>
+      <c r="G497" s="14"/>
+      <c r="H497" s="14"/>
+      <c r="L497" s="15"/>
+      <c r="M497" s="15"/>
     </row>
     <row r="498">
-      <c r="L498" s="10"/>
-      <c r="M498" s="10"/>
+      <c r="G498" s="14"/>
+      <c r="H498" s="14"/>
+      <c r="L498" s="15"/>
+      <c r="M498" s="15"/>
     </row>
     <row r="499">
-      <c r="L499" s="10"/>
-      <c r="M499" s="10"/>
+      <c r="G499" s="14"/>
+      <c r="H499" s="14"/>
+      <c r="L499" s="15"/>
+      <c r="M499" s="15"/>
     </row>
     <row r="500">
-      <c r="L500" s="10"/>
-      <c r="M500" s="10"/>
+      <c r="G500" s="14"/>
+      <c r="H500" s="14"/>
+      <c r="L500" s="15"/>
+      <c r="M500" s="15"/>
     </row>
     <row r="501">
-      <c r="L501" s="10"/>
-      <c r="M501" s="10"/>
+      <c r="G501" s="14"/>
+      <c r="H501" s="14"/>
+      <c r="L501" s="15"/>
+      <c r="M501" s="15"/>
     </row>
     <row r="502">
-      <c r="L502" s="10"/>
-      <c r="M502" s="10"/>
+      <c r="G502" s="14"/>
+      <c r="H502" s="14"/>
+      <c r="L502" s="15"/>
+      <c r="M502" s="15"/>
     </row>
     <row r="503">
-      <c r="L503" s="10"/>
-      <c r="M503" s="10"/>
+      <c r="G503" s="14"/>
+      <c r="H503" s="14"/>
+      <c r="L503" s="15"/>
+      <c r="M503" s="15"/>
     </row>
     <row r="504">
-      <c r="L504" s="10"/>
-      <c r="M504" s="10"/>
+      <c r="G504" s="14"/>
+      <c r="H504" s="14"/>
+      <c r="L504" s="15"/>
+      <c r="M504" s="15"/>
     </row>
     <row r="505">
-      <c r="L505" s="10"/>
-      <c r="M505" s="10"/>
+      <c r="G505" s="14"/>
+      <c r="H505" s="14"/>
+      <c r="L505" s="15"/>
+      <c r="M505" s="15"/>
     </row>
     <row r="506">
-      <c r="L506" s="10"/>
-      <c r="M506" s="10"/>
+      <c r="G506" s="14"/>
+      <c r="H506" s="14"/>
+      <c r="L506" s="15"/>
+      <c r="M506" s="15"/>
     </row>
     <row r="507">
-      <c r="L507" s="10"/>
-      <c r="M507" s="10"/>
+      <c r="G507" s="14"/>
+      <c r="H507" s="14"/>
+      <c r="L507" s="15"/>
+      <c r="M507" s="15"/>
     </row>
     <row r="508">
-      <c r="L508" s="10"/>
-      <c r="M508" s="10"/>
+      <c r="G508" s="14"/>
+      <c r="H508" s="14"/>
+      <c r="L508" s="15"/>
+      <c r="M508" s="15"/>
     </row>
     <row r="509">
-      <c r="L509" s="10"/>
-      <c r="M509" s="10"/>
+      <c r="G509" s="14"/>
+      <c r="H509" s="14"/>
+      <c r="L509" s="15"/>
+      <c r="M509" s="15"/>
     </row>
     <row r="510">
-      <c r="L510" s="10"/>
-      <c r="M510" s="10"/>
+      <c r="G510" s="14"/>
+      <c r="H510" s="14"/>
+      <c r="L510" s="15"/>
+      <c r="M510" s="15"/>
     </row>
     <row r="511">
-      <c r="L511" s="10"/>
-      <c r="M511" s="10"/>
+      <c r="G511" s="14"/>
+      <c r="H511" s="14"/>
+      <c r="L511" s="15"/>
+      <c r="M511" s="15"/>
     </row>
     <row r="512">
-      <c r="L512" s="10"/>
-      <c r="M512" s="10"/>
+      <c r="G512" s="14"/>
+      <c r="H512" s="14"/>
+      <c r="L512" s="15"/>
+      <c r="M512" s="15"/>
     </row>
     <row r="513">
-      <c r="L513" s="10"/>
-      <c r="M513" s="10"/>
+      <c r="G513" s="14"/>
+      <c r="H513" s="14"/>
+      <c r="L513" s="15"/>
+      <c r="M513" s="15"/>
     </row>
     <row r="514">
-      <c r="L514" s="10"/>
-      <c r="M514" s="10"/>
+      <c r="G514" s="14"/>
+      <c r="H514" s="14"/>
+      <c r="L514" s="15"/>
+      <c r="M514" s="15"/>
     </row>
     <row r="515">
-      <c r="L515" s="10"/>
-      <c r="M515" s="10"/>
+      <c r="G515" s="14"/>
+      <c r="H515" s="14"/>
+      <c r="L515" s="15"/>
+      <c r="M515" s="15"/>
     </row>
     <row r="516">
-      <c r="L516" s="10"/>
-      <c r="M516" s="10"/>
+      <c r="G516" s="14"/>
+      <c r="H516" s="14"/>
+      <c r="L516" s="15"/>
+      <c r="M516" s="15"/>
     </row>
     <row r="517">
-      <c r="L517" s="10"/>
-      <c r="M517" s="10"/>
+      <c r="G517" s="14"/>
+      <c r="H517" s="14"/>
+      <c r="L517" s="15"/>
+      <c r="M517" s="15"/>
     </row>
     <row r="518">
-      <c r="L518" s="10"/>
-      <c r="M518" s="10"/>
+      <c r="G518" s="14"/>
+      <c r="H518" s="14"/>
+      <c r="L518" s="15"/>
+      <c r="M518" s="15"/>
     </row>
     <row r="519">
-      <c r="L519" s="10"/>
-      <c r="M519" s="10"/>
+      <c r="G519" s="14"/>
+      <c r="H519" s="14"/>
+      <c r="L519" s="15"/>
+      <c r="M519" s="15"/>
     </row>
     <row r="520">
-      <c r="L520" s="10"/>
-      <c r="M520" s="10"/>
+      <c r="G520" s="14"/>
+      <c r="H520" s="14"/>
+      <c r="L520" s="15"/>
+      <c r="M520" s="15"/>
     </row>
     <row r="521">
-      <c r="L521" s="10"/>
-      <c r="M521" s="10"/>
+      <c r="G521" s="14"/>
+      <c r="H521" s="14"/>
+      <c r="L521" s="15"/>
+      <c r="M521" s="15"/>
     </row>
     <row r="522">
-      <c r="L522" s="10"/>
-      <c r="M522" s="10"/>
+      <c r="G522" s="14"/>
+      <c r="H522" s="14"/>
+      <c r="L522" s="15"/>
+      <c r="M522" s="15"/>
     </row>
     <row r="523">
-      <c r="L523" s="10"/>
-      <c r="M523" s="10"/>
+      <c r="G523" s="14"/>
+      <c r="H523" s="14"/>
+      <c r="L523" s="15"/>
+      <c r="M523" s="15"/>
     </row>
     <row r="524">
-      <c r="L524" s="10"/>
-      <c r="M524" s="10"/>
+      <c r="G524" s="14"/>
+      <c r="H524" s="14"/>
+      <c r="L524" s="15"/>
+      <c r="M524" s="15"/>
     </row>
     <row r="525">
-      <c r="L525" s="10"/>
-      <c r="M525" s="10"/>
+      <c r="G525" s="14"/>
+      <c r="H525" s="14"/>
+      <c r="L525" s="15"/>
+      <c r="M525" s="15"/>
     </row>
     <row r="526">
-      <c r="L526" s="10"/>
-      <c r="M526" s="10"/>
+      <c r="G526" s="14"/>
+      <c r="H526" s="14"/>
+      <c r="L526" s="15"/>
+      <c r="M526" s="15"/>
     </row>
     <row r="527">
-      <c r="L527" s="10"/>
-      <c r="M527" s="10"/>
+      <c r="G527" s="14"/>
+      <c r="H527" s="14"/>
+      <c r="L527" s="15"/>
+      <c r="M527" s="15"/>
     </row>
     <row r="528">
-      <c r="L528" s="10"/>
-      <c r="M528" s="10"/>
+      <c r="G528" s="14"/>
+      <c r="H528" s="14"/>
+      <c r="L528" s="15"/>
+      <c r="M528" s="15"/>
     </row>
     <row r="529">
-      <c r="L529" s="10"/>
-      <c r="M529" s="10"/>
+      <c r="G529" s="14"/>
+      <c r="H529" s="14"/>
+      <c r="L529" s="15"/>
+      <c r="M529" s="15"/>
     </row>
     <row r="530">
-      <c r="L530" s="10"/>
-      <c r="M530" s="10"/>
+      <c r="G530" s="14"/>
+      <c r="H530" s="14"/>
+      <c r="L530" s="15"/>
+      <c r="M530" s="15"/>
     </row>
     <row r="531">
-      <c r="L531" s="10"/>
-      <c r="M531" s="10"/>
+      <c r="G531" s="14"/>
+      <c r="H531" s="14"/>
+      <c r="L531" s="15"/>
+      <c r="M531" s="15"/>
     </row>
     <row r="532">
-      <c r="L532" s="10"/>
-      <c r="M532" s="10"/>
+      <c r="G532" s="14"/>
+      <c r="H532" s="14"/>
+      <c r="L532" s="15"/>
+      <c r="M532" s="15"/>
     </row>
     <row r="533">
-      <c r="L533" s="10"/>
-      <c r="M533" s="10"/>
+      <c r="G533" s="14"/>
+      <c r="H533" s="14"/>
+      <c r="L533" s="15"/>
+      <c r="M533" s="15"/>
     </row>
     <row r="534">
-      <c r="L534" s="10"/>
-      <c r="M534" s="10"/>
+      <c r="G534" s="14"/>
+      <c r="H534" s="14"/>
+      <c r="L534" s="15"/>
+      <c r="M534" s="15"/>
     </row>
     <row r="535">
-      <c r="L535" s="10"/>
-      <c r="M535" s="10"/>
+      <c r="G535" s="14"/>
+      <c r="H535" s="14"/>
+      <c r="L535" s="15"/>
+      <c r="M535" s="15"/>
     </row>
     <row r="536">
-      <c r="L536" s="10"/>
-      <c r="M536" s="10"/>
+      <c r="G536" s="14"/>
+      <c r="H536" s="14"/>
+      <c r="L536" s="15"/>
+      <c r="M536" s="15"/>
     </row>
     <row r="537">
-      <c r="L537" s="10"/>
-      <c r="M537" s="10"/>
+      <c r="G537" s="14"/>
+      <c r="H537" s="14"/>
+      <c r="L537" s="15"/>
+      <c r="M537" s="15"/>
     </row>
     <row r="538">
-      <c r="L538" s="10"/>
-      <c r="M538" s="10"/>
+      <c r="G538" s="14"/>
+      <c r="H538" s="14"/>
+      <c r="L538" s="15"/>
+      <c r="M538" s="15"/>
     </row>
     <row r="539">
-      <c r="L539" s="10"/>
-      <c r="M539" s="10"/>
+      <c r="G539" s="14"/>
+      <c r="H539" s="14"/>
+      <c r="L539" s="15"/>
+      <c r="M539" s="15"/>
     </row>
     <row r="540">
-      <c r="L540" s="10"/>
-      <c r="M540" s="10"/>
+      <c r="G540" s="14"/>
+      <c r="H540" s="14"/>
+      <c r="L540" s="15"/>
+      <c r="M540" s="15"/>
     </row>
     <row r="541">
-      <c r="L541" s="10"/>
-      <c r="M541" s="10"/>
+      <c r="G541" s="14"/>
+      <c r="H541" s="14"/>
+      <c r="L541" s="15"/>
+      <c r="M541" s="15"/>
     </row>
     <row r="542">
-      <c r="L542" s="10"/>
-      <c r="M542" s="10"/>
+      <c r="G542" s="14"/>
+      <c r="H542" s="14"/>
+      <c r="L542" s="15"/>
+      <c r="M542" s="15"/>
     </row>
     <row r="543">
-      <c r="L543" s="10"/>
-      <c r="M543" s="10"/>
+      <c r="G543" s="14"/>
+      <c r="H543" s="14"/>
+      <c r="L543" s="15"/>
+      <c r="M543" s="15"/>
     </row>
     <row r="544">
-      <c r="L544" s="10"/>
-      <c r="M544" s="10"/>
+      <c r="G544" s="14"/>
+      <c r="H544" s="14"/>
+      <c r="L544" s="15"/>
+      <c r="M544" s="15"/>
     </row>
     <row r="545">
-      <c r="L545" s="10"/>
-      <c r="M545" s="10"/>
+      <c r="G545" s="14"/>
+      <c r="H545" s="14"/>
+      <c r="L545" s="15"/>
+      <c r="M545" s="15"/>
     </row>
     <row r="546">
-      <c r="L546" s="10"/>
-      <c r="M546" s="10"/>
+      <c r="G546" s="14"/>
+      <c r="H546" s="14"/>
+      <c r="L546" s="15"/>
+      <c r="M546" s="15"/>
     </row>
     <row r="547">
-      <c r="L547" s="10"/>
-      <c r="M547" s="10"/>
+      <c r="G547" s="14"/>
+      <c r="H547" s="14"/>
+      <c r="L547" s="15"/>
+      <c r="M547" s="15"/>
     </row>
     <row r="548">
-      <c r="L548" s="10"/>
-      <c r="M548" s="10"/>
+      <c r="G548" s="14"/>
+      <c r="H548" s="14"/>
+      <c r="L548" s="15"/>
+      <c r="M548" s="15"/>
     </row>
     <row r="549">
-      <c r="L549" s="10"/>
-      <c r="M549" s="10"/>
+      <c r="G549" s="14"/>
+      <c r="H549" s="14"/>
+      <c r="L549" s="15"/>
+      <c r="M549" s="15"/>
     </row>
     <row r="550">
-      <c r="L550" s="10"/>
-      <c r="M550" s="10"/>
+      <c r="G550" s="14"/>
+      <c r="H550" s="14"/>
+      <c r="L550" s="15"/>
+      <c r="M550" s="15"/>
     </row>
     <row r="551">
-      <c r="L551" s="10"/>
-      <c r="M551" s="10"/>
+      <c r="G551" s="14"/>
+      <c r="H551" s="14"/>
+      <c r="L551" s="15"/>
+      <c r="M551" s="15"/>
     </row>
     <row r="552">
-      <c r="L552" s="10"/>
-      <c r="M552" s="10"/>
+      <c r="G552" s="14"/>
+      <c r="H552" s="14"/>
+      <c r="L552" s="15"/>
+      <c r="M552" s="15"/>
     </row>
     <row r="553">
-      <c r="L553" s="10"/>
-      <c r="M553" s="10"/>
+      <c r="G553" s="14"/>
+      <c r="H553" s="14"/>
+      <c r="L553" s="15"/>
+      <c r="M553" s="15"/>
     </row>
     <row r="554">
-      <c r="L554" s="10"/>
-      <c r="M554" s="10"/>
+      <c r="G554" s="14"/>
+      <c r="H554" s="14"/>
+      <c r="L554" s="15"/>
+      <c r="M554" s="15"/>
     </row>
     <row r="555">
-      <c r="L555" s="10"/>
-      <c r="M555" s="10"/>
+      <c r="G555" s="14"/>
+      <c r="H555" s="14"/>
+      <c r="L555" s="15"/>
+      <c r="M555" s="15"/>
     </row>
     <row r="556">
-      <c r="L556" s="10"/>
-      <c r="M556" s="10"/>
+      <c r="G556" s="14"/>
+      <c r="H556" s="14"/>
+      <c r="L556" s="15"/>
+      <c r="M556" s="15"/>
     </row>
     <row r="557">
-      <c r="L557" s="10"/>
-      <c r="M557" s="10"/>
+      <c r="G557" s="14"/>
+      <c r="H557" s="14"/>
+      <c r="L557" s="15"/>
+      <c r="M557" s="15"/>
     </row>
     <row r="558">
-      <c r="L558" s="10"/>
-      <c r="M558" s="10"/>
+      <c r="G558" s="14"/>
+      <c r="H558" s="14"/>
+      <c r="L558" s="15"/>
+      <c r="M558" s="15"/>
     </row>
     <row r="559">
-      <c r="L559" s="10"/>
-      <c r="M559" s="10"/>
+      <c r="G559" s="14"/>
+      <c r="H559" s="14"/>
+      <c r="L559" s="15"/>
+      <c r="M559" s="15"/>
     </row>
     <row r="560">
-      <c r="L560" s="10"/>
-      <c r="M560" s="10"/>
+      <c r="G560" s="14"/>
+      <c r="H560" s="14"/>
+      <c r="L560" s="15"/>
+      <c r="M560" s="15"/>
     </row>
     <row r="561">
-      <c r="L561" s="10"/>
-      <c r="M561" s="10"/>
+      <c r="G561" s="14"/>
+      <c r="H561" s="14"/>
+      <c r="L561" s="15"/>
+      <c r="M561" s="15"/>
     </row>
     <row r="562">
-      <c r="L562" s="10"/>
-      <c r="M562" s="10"/>
+      <c r="G562" s="14"/>
+      <c r="H562" s="14"/>
+      <c r="L562" s="15"/>
+      <c r="M562" s="15"/>
     </row>
     <row r="563">
-      <c r="L563" s="10"/>
-      <c r="M563" s="10"/>
+      <c r="G563" s="14"/>
+      <c r="H563" s="14"/>
+      <c r="L563" s="15"/>
+      <c r="M563" s="15"/>
     </row>
     <row r="564">
-      <c r="L564" s="10"/>
-      <c r="M564" s="10"/>
+      <c r="G564" s="14"/>
+      <c r="H564" s="14"/>
+      <c r="L564" s="15"/>
+      <c r="M564" s="15"/>
     </row>
     <row r="565">
-      <c r="L565" s="10"/>
-      <c r="M565" s="10"/>
+      <c r="G565" s="14"/>
+      <c r="H565" s="14"/>
+      <c r="L565" s="15"/>
+      <c r="M565" s="15"/>
     </row>
     <row r="566">
-      <c r="L566" s="10"/>
-      <c r="M566" s="10"/>
+      <c r="G566" s="14"/>
+      <c r="H566" s="14"/>
+      <c r="L566" s="15"/>
+      <c r="M566" s="15"/>
     </row>
     <row r="567">
-      <c r="L567" s="10"/>
-      <c r="M567" s="10"/>
+      <c r="G567" s="14"/>
+      <c r="H567" s="14"/>
+      <c r="L567" s="15"/>
+      <c r="M567" s="15"/>
     </row>
     <row r="568">
-      <c r="L568" s="10"/>
-      <c r="M568" s="10"/>
+      <c r="G568" s="14"/>
+      <c r="H568" s="14"/>
+      <c r="L568" s="15"/>
+      <c r="M568" s="15"/>
     </row>
     <row r="569">
-      <c r="L569" s="10"/>
-      <c r="M569" s="10"/>
+      <c r="G569" s="14"/>
+      <c r="H569" s="14"/>
+      <c r="L569" s="15"/>
+      <c r="M569" s="15"/>
     </row>
     <row r="570">
-      <c r="L570" s="10"/>
-      <c r="M570" s="10"/>
+      <c r="G570" s="14"/>
+      <c r="H570" s="14"/>
+      <c r="L570" s="15"/>
+      <c r="M570" s="15"/>
     </row>
     <row r="571">
-      <c r="L571" s="10"/>
-      <c r="M571" s="10"/>
+      <c r="G571" s="14"/>
+      <c r="H571" s="14"/>
+      <c r="L571" s="15"/>
+      <c r="M571" s="15"/>
     </row>
     <row r="572">
-      <c r="L572" s="10"/>
-      <c r="M572" s="10"/>
+      <c r="G572" s="14"/>
+      <c r="H572" s="14"/>
+      <c r="L572" s="15"/>
+      <c r="M572" s="15"/>
     </row>
     <row r="573">
-      <c r="L573" s="10"/>
-      <c r="M573" s="10"/>
+      <c r="G573" s="14"/>
+      <c r="H573" s="14"/>
+      <c r="L573" s="15"/>
+      <c r="M573" s="15"/>
     </row>
     <row r="574">
-      <c r="L574" s="10"/>
-      <c r="M574" s="10"/>
+      <c r="G574" s="14"/>
+      <c r="H574" s="14"/>
+      <c r="L574" s="15"/>
+      <c r="M574" s="15"/>
     </row>
     <row r="575">
-      <c r="L575" s="10"/>
-      <c r="M575" s="10"/>
+      <c r="G575" s="14"/>
+      <c r="H575" s="14"/>
+      <c r="L575" s="15"/>
+      <c r="M575" s="15"/>
     </row>
     <row r="576">
-      <c r="L576" s="10"/>
-      <c r="M576" s="10"/>
+      <c r="G576" s="14"/>
+      <c r="H576" s="14"/>
+      <c r="L576" s="15"/>
+      <c r="M576" s="15"/>
     </row>
     <row r="577">
-      <c r="L577" s="10"/>
-      <c r="M577" s="10"/>
+      <c r="G577" s="14"/>
+      <c r="H577" s="14"/>
+      <c r="L577" s="15"/>
+      <c r="M577" s="15"/>
     </row>
     <row r="578">
-      <c r="L578" s="10"/>
-      <c r="M578" s="10"/>
+      <c r="G578" s="14"/>
+      <c r="H578" s="14"/>
+      <c r="L578" s="15"/>
+      <c r="M578" s="15"/>
     </row>
     <row r="579">
-      <c r="L579" s="10"/>
-      <c r="M579" s="10"/>
+      <c r="G579" s="14"/>
+      <c r="H579" s="14"/>
+      <c r="L579" s="15"/>
+      <c r="M579" s="15"/>
     </row>
     <row r="580">
-      <c r="L580" s="10"/>
-      <c r="M580" s="10"/>
+      <c r="G580" s="14"/>
+      <c r="H580" s="14"/>
+      <c r="L580" s="15"/>
+      <c r="M580" s="15"/>
     </row>
     <row r="581">
-      <c r="L581" s="10"/>
-      <c r="M581" s="10"/>
+      <c r="G581" s="14"/>
+      <c r="H581" s="14"/>
+      <c r="L581" s="15"/>
+      <c r="M581" s="15"/>
     </row>
     <row r="582">
-      <c r="L582" s="10"/>
-      <c r="M582" s="10"/>
+      <c r="G582" s="14"/>
+      <c r="H582" s="14"/>
+      <c r="L582" s="15"/>
+      <c r="M582" s="15"/>
     </row>
     <row r="583">
-      <c r="L583" s="10"/>
-      <c r="M583" s="10"/>
+      <c r="G583" s="14"/>
+      <c r="H583" s="14"/>
+      <c r="L583" s="15"/>
+      <c r="M583" s="15"/>
     </row>
     <row r="584">
-      <c r="L584" s="10"/>
-      <c r="M584" s="10"/>
+      <c r="G584" s="14"/>
+      <c r="H584" s="14"/>
+      <c r="L584" s="15"/>
+      <c r="M584" s="15"/>
     </row>
     <row r="585">
-      <c r="L585" s="10"/>
-      <c r="M585" s="10"/>
+      <c r="G585" s="14"/>
+      <c r="H585" s="14"/>
+      <c r="L585" s="15"/>
+      <c r="M585" s="15"/>
     </row>
     <row r="586">
-      <c r="L586" s="10"/>
-      <c r="M586" s="10"/>
+      <c r="G586" s="14"/>
+      <c r="H586" s="14"/>
+      <c r="L586" s="15"/>
+      <c r="M586" s="15"/>
     </row>
     <row r="587">
-      <c r="L587" s="10"/>
-      <c r="M587" s="10"/>
+      <c r="G587" s="14"/>
+      <c r="H587" s="14"/>
+      <c r="L587" s="15"/>
+      <c r="M587" s="15"/>
     </row>
     <row r="588">
-      <c r="L588" s="10"/>
-      <c r="M588" s="10"/>
+      <c r="G588" s="14"/>
+      <c r="H588" s="14"/>
+      <c r="L588" s="15"/>
+      <c r="M588" s="15"/>
     </row>
     <row r="589">
-      <c r="L589" s="10"/>
-      <c r="M589" s="10"/>
+      <c r="G589" s="14"/>
+      <c r="H589" s="14"/>
+      <c r="L589" s="15"/>
+      <c r="M589" s="15"/>
     </row>
     <row r="590">
-      <c r="L590" s="10"/>
-      <c r="M590" s="10"/>
+      <c r="G590" s="14"/>
+      <c r="H590" s="14"/>
+      <c r="L590" s="15"/>
+      <c r="M590" s="15"/>
     </row>
     <row r="591">
-      <c r="L591" s="10"/>
-      <c r="M591" s="10"/>
+      <c r="G591" s="14"/>
+      <c r="H591" s="14"/>
+      <c r="L591" s="15"/>
+      <c r="M591" s="15"/>
     </row>
     <row r="592">
-      <c r="L592" s="10"/>
-      <c r="M592" s="10"/>
+      <c r="G592" s="14"/>
+      <c r="H592" s="14"/>
+      <c r="L592" s="15"/>
+      <c r="M592" s="15"/>
     </row>
     <row r="593">
-      <c r="L593" s="10"/>
-      <c r="M593" s="10"/>
+      <c r="G593" s="14"/>
+      <c r="H593" s="14"/>
+      <c r="L593" s="15"/>
+      <c r="M593" s="15"/>
     </row>
     <row r="594">
-      <c r="L594" s="10"/>
-      <c r="M594" s="10"/>
+      <c r="G594" s="14"/>
+      <c r="H594" s="14"/>
+      <c r="L594" s="15"/>
+      <c r="M594" s="15"/>
     </row>
     <row r="595">
-      <c r="L595" s="10"/>
-      <c r="M595" s="10"/>
+      <c r="G595" s="14"/>
+      <c r="H595" s="14"/>
+      <c r="L595" s="15"/>
+      <c r="M595" s="15"/>
     </row>
     <row r="596">
-      <c r="L596" s="10"/>
-      <c r="M596" s="10"/>
+      <c r="G596" s="14"/>
+      <c r="H596" s="14"/>
+      <c r="L596" s="15"/>
+      <c r="M596" s="15"/>
     </row>
     <row r="597">
-      <c r="L597" s="10"/>
-      <c r="M597" s="10"/>
+      <c r="G597" s="14"/>
+      <c r="H597" s="14"/>
+      <c r="L597" s="15"/>
+      <c r="M597" s="15"/>
     </row>
     <row r="598">
-      <c r="L598" s="10"/>
-      <c r="M598" s="10"/>
+      <c r="G598" s="14"/>
+      <c r="H598" s="14"/>
+      <c r="L598" s="15"/>
+      <c r="M598" s="15"/>
     </row>
     <row r="599">
-      <c r="L599" s="10"/>
-      <c r="M599" s="10"/>
+      <c r="G599" s="14"/>
+      <c r="H599" s="14"/>
+      <c r="L599" s="15"/>
+      <c r="M599" s="15"/>
     </row>
     <row r="600">
-      <c r="L600" s="10"/>
-      <c r="M600" s="10"/>
+      <c r="G600" s="14"/>
+      <c r="H600" s="14"/>
+      <c r="L600" s="15"/>
+      <c r="M600" s="15"/>
     </row>
     <row r="601">
-      <c r="L601" s="10"/>
-      <c r="M601" s="10"/>
+      <c r="G601" s="14"/>
+      <c r="H601" s="14"/>
+      <c r="L601" s="15"/>
+      <c r="M601" s="15"/>
     </row>
     <row r="602">
-      <c r="L602" s="10"/>
-      <c r="M602" s="10"/>
+      <c r="G602" s="14"/>
+      <c r="H602" s="14"/>
+      <c r="L602" s="15"/>
+      <c r="M602" s="15"/>
     </row>
     <row r="603">
-      <c r="L603" s="10"/>
-      <c r="M603" s="10"/>
+      <c r="G603" s="14"/>
+      <c r="H603" s="14"/>
+      <c r="L603" s="15"/>
+      <c r="M603" s="15"/>
     </row>
     <row r="604">
-      <c r="L604" s="10"/>
-      <c r="M604" s="10"/>
+      <c r="G604" s="14"/>
+      <c r="H604" s="14"/>
+      <c r="L604" s="15"/>
+      <c r="M604" s="15"/>
     </row>
     <row r="605">
-      <c r="L605" s="10"/>
-      <c r="M605" s="10"/>
+      <c r="G605" s="14"/>
+      <c r="H605" s="14"/>
+      <c r="L605" s="15"/>
+      <c r="M605" s="15"/>
     </row>
     <row r="606">
-      <c r="L606" s="10"/>
-      <c r="M606" s="10"/>
+      <c r="G606" s="14"/>
+      <c r="H606" s="14"/>
+      <c r="L606" s="15"/>
+      <c r="M606" s="15"/>
     </row>
     <row r="607">
-      <c r="L607" s="10"/>
-      <c r="M607" s="10"/>
+      <c r="G607" s="14"/>
+      <c r="H607" s="14"/>
+      <c r="L607" s="15"/>
+      <c r="M607" s="15"/>
     </row>
     <row r="608">
-      <c r="L608" s="10"/>
-      <c r="M608" s="10"/>
+      <c r="G608" s="14"/>
+      <c r="H608" s="14"/>
+      <c r="L608" s="15"/>
+      <c r="M608" s="15"/>
     </row>
     <row r="609">
-      <c r="L609" s="10"/>
-      <c r="M609" s="10"/>
+      <c r="G609" s="14"/>
+      <c r="H609" s="14"/>
+      <c r="L609" s="15"/>
+      <c r="M609" s="15"/>
     </row>
     <row r="610">
-      <c r="L610" s="10"/>
-      <c r="M610" s="10"/>
+      <c r="G610" s="14"/>
+      <c r="H610" s="14"/>
+      <c r="L610" s="15"/>
+      <c r="M610" s="15"/>
     </row>
     <row r="611">
-      <c r="L611" s="10"/>
-      <c r="M611" s="10"/>
+      <c r="G611" s="14"/>
+      <c r="H611" s="14"/>
+      <c r="L611" s="15"/>
+      <c r="M611" s="15"/>
     </row>
     <row r="612">
-      <c r="L612" s="10"/>
-      <c r="M612" s="10"/>
+      <c r="G612" s="14"/>
+      <c r="H612" s="14"/>
+      <c r="L612" s="15"/>
+      <c r="M612" s="15"/>
     </row>
     <row r="613">
-      <c r="L613" s="10"/>
-      <c r="M613" s="10"/>
+      <c r="G613" s="14"/>
+      <c r="H613" s="14"/>
+      <c r="L613" s="15"/>
+      <c r="M613" s="15"/>
     </row>
     <row r="614">
-      <c r="L614" s="10"/>
-      <c r="M614" s="10"/>
+      <c r="G614" s="14"/>
+      <c r="H614" s="14"/>
+      <c r="L614" s="15"/>
+      <c r="M614" s="15"/>
     </row>
     <row r="615">
-      <c r="L615" s="10"/>
-      <c r="M615" s="10"/>
+      <c r="G615" s="14"/>
+      <c r="H615" s="14"/>
+      <c r="L615" s="15"/>
+      <c r="M615" s="15"/>
     </row>
     <row r="616">
-      <c r="L616" s="10"/>
-      <c r="M616" s="10"/>
+      <c r="G616" s="14"/>
+      <c r="H616" s="14"/>
+      <c r="L616" s="15"/>
+      <c r="M616" s="15"/>
     </row>
     <row r="617">
-      <c r="L617" s="10"/>
-      <c r="M617" s="10"/>
+      <c r="G617" s="14"/>
+      <c r="H617" s="14"/>
+      <c r="L617" s="15"/>
+      <c r="M617" s="15"/>
     </row>
     <row r="618">
-      <c r="L618" s="10"/>
-      <c r="M618" s="10"/>
+      <c r="G618" s="14"/>
+      <c r="H618" s="14"/>
+      <c r="L618" s="15"/>
+      <c r="M618" s="15"/>
     </row>
     <row r="619">
-      <c r="L619" s="10"/>
-      <c r="M619" s="10"/>
+      <c r="G619" s="14"/>
+      <c r="H619" s="14"/>
+      <c r="L619" s="15"/>
+      <c r="M619" s="15"/>
     </row>
     <row r="620">
-      <c r="L620" s="10"/>
-      <c r="M620" s="10"/>
+      <c r="G620" s="14"/>
+      <c r="H620" s="14"/>
+      <c r="L620" s="15"/>
+      <c r="M620" s="15"/>
     </row>
     <row r="621">
-      <c r="L621" s="10"/>
-      <c r="M621" s="10"/>
+      <c r="G621" s="14"/>
+      <c r="H621" s="14"/>
+      <c r="L621" s="15"/>
+      <c r="M621" s="15"/>
     </row>
     <row r="622">
-      <c r="L622" s="10"/>
-      <c r="M622" s="10"/>
+      <c r="G622" s="14"/>
+      <c r="H622" s="14"/>
+      <c r="L622" s="15"/>
+      <c r="M622" s="15"/>
     </row>
     <row r="623">
-      <c r="L623" s="10"/>
-      <c r="M623" s="10"/>
+      <c r="G623" s="14"/>
+      <c r="H623" s="14"/>
+      <c r="L623" s="15"/>
+      <c r="M623" s="15"/>
     </row>
     <row r="624">
-      <c r="L624" s="10"/>
-      <c r="M624" s="10"/>
+      <c r="G624" s="14"/>
+      <c r="H624" s="14"/>
+      <c r="L624" s="15"/>
+      <c r="M624" s="15"/>
     </row>
     <row r="625">
-      <c r="L625" s="10"/>
-      <c r="M625" s="10"/>
+      <c r="G625" s="14"/>
+      <c r="H625" s="14"/>
+      <c r="L625" s="15"/>
+      <c r="M625" s="15"/>
     </row>
     <row r="626">
-      <c r="L626" s="10"/>
-      <c r="M626" s="10"/>
+      <c r="G626" s="14"/>
+      <c r="H626" s="14"/>
+      <c r="L626" s="15"/>
+      <c r="M626" s="15"/>
     </row>
     <row r="627">
-      <c r="L627" s="10"/>
-      <c r="M627" s="10"/>
+      <c r="G627" s="14"/>
+      <c r="H627" s="14"/>
+      <c r="L627" s="15"/>
+      <c r="M627" s="15"/>
     </row>
     <row r="628">
-      <c r="L628" s="10"/>
-      <c r="M628" s="10"/>
+      <c r="G628" s="14"/>
+      <c r="H628" s="14"/>
+      <c r="L628" s="15"/>
+      <c r="M628" s="15"/>
     </row>
     <row r="629">
-      <c r="L629" s="10"/>
-      <c r="M629" s="10"/>
+      <c r="G629" s="14"/>
+      <c r="H629" s="14"/>
+      <c r="L629" s="15"/>
+      <c r="M629" s="15"/>
     </row>
     <row r="630">
-      <c r="L630" s="10"/>
-      <c r="M630" s="10"/>
+      <c r="G630" s="14"/>
+      <c r="H630" s="14"/>
+      <c r="L630" s="15"/>
+      <c r="M630" s="15"/>
     </row>
     <row r="631">
-      <c r="L631" s="10"/>
-      <c r="M631" s="10"/>
+      <c r="G631" s="14"/>
+      <c r="H631" s="14"/>
+      <c r="L631" s="15"/>
+      <c r="M631" s="15"/>
     </row>
     <row r="632">
-      <c r="L632" s="10"/>
-      <c r="M632" s="10"/>
+      <c r="G632" s="14"/>
+      <c r="H632" s="14"/>
+      <c r="L632" s="15"/>
+      <c r="M632" s="15"/>
     </row>
     <row r="633">
-      <c r="L633" s="10"/>
-      <c r="M633" s="10"/>
+      <c r="G633" s="14"/>
+      <c r="H633" s="14"/>
+      <c r="L633" s="15"/>
+      <c r="M633" s="15"/>
     </row>
     <row r="634">
-      <c r="L634" s="10"/>
-      <c r="M634" s="10"/>
+      <c r="G634" s="14"/>
+      <c r="H634" s="14"/>
+      <c r="L634" s="15"/>
+      <c r="M634" s="15"/>
     </row>
     <row r="635">
-      <c r="L635" s="10"/>
-      <c r="M635" s="10"/>
+      <c r="G635" s="14"/>
+      <c r="H635" s="14"/>
+      <c r="L635" s="15"/>
+      <c r="M635" s="15"/>
     </row>
     <row r="636">
-      <c r="L636" s="10"/>
-      <c r="M636" s="10"/>
+      <c r="G636" s="14"/>
+      <c r="H636" s="14"/>
+      <c r="L636" s="15"/>
+      <c r="M636" s="15"/>
     </row>
     <row r="637">
-      <c r="L637" s="10"/>
-      <c r="M637" s="10"/>
+      <c r="G637" s="14"/>
+      <c r="H637" s="14"/>
+      <c r="L637" s="15"/>
+      <c r="M637" s="15"/>
     </row>
     <row r="638">
-      <c r="L638" s="10"/>
-      <c r="M638" s="10"/>
+      <c r="G638" s="14"/>
+      <c r="H638" s="14"/>
+      <c r="L638" s="15"/>
+      <c r="M638" s="15"/>
     </row>
     <row r="639">
-      <c r="L639" s="10"/>
-      <c r="M639" s="10"/>
+      <c r="G639" s="14"/>
+      <c r="H639" s="14"/>
+      <c r="L639" s="15"/>
+      <c r="M639" s="15"/>
     </row>
     <row r="640">
-      <c r="L640" s="10"/>
-      <c r="M640" s="10"/>
+      <c r="G640" s="14"/>
+      <c r="H640" s="14"/>
+      <c r="L640" s="15"/>
+      <c r="M640" s="15"/>
     </row>
     <row r="641">
-      <c r="L641" s="10"/>
-      <c r="M641" s="10"/>
+      <c r="G641" s="14"/>
+      <c r="H641" s="14"/>
+      <c r="L641" s="15"/>
+      <c r="M641" s="15"/>
     </row>
     <row r="642">
-      <c r="L642" s="10"/>
-      <c r="M642" s="10"/>
+      <c r="G642" s="14"/>
+      <c r="H642" s="14"/>
+      <c r="L642" s="15"/>
+      <c r="M642" s="15"/>
     </row>
     <row r="643">
-      <c r="L643" s="10"/>
-      <c r="M643" s="10"/>
+      <c r="G643" s="14"/>
+      <c r="H643" s="14"/>
+      <c r="L643" s="15"/>
+      <c r="M643" s="15"/>
     </row>
     <row r="644">
-      <c r="L644" s="10"/>
-      <c r="M644" s="10"/>
+      <c r="G644" s="14"/>
+      <c r="H644" s="14"/>
+      <c r="L644" s="15"/>
+      <c r="M644" s="15"/>
     </row>
     <row r="645">
-      <c r="L645" s="10"/>
-      <c r="M645" s="10"/>
+      <c r="G645" s="14"/>
+      <c r="H645" s="14"/>
+      <c r="L645" s="15"/>
+      <c r="M645" s="15"/>
     </row>
     <row r="646">
-      <c r="L646" s="10"/>
-      <c r="M646" s="10"/>
+      <c r="G646" s="14"/>
+      <c r="H646" s="14"/>
+      <c r="L646" s="15"/>
+      <c r="M646" s="15"/>
     </row>
     <row r="647">
-      <c r="L647" s="10"/>
-      <c r="M647" s="10"/>
+      <c r="G647" s="14"/>
+      <c r="H647" s="14"/>
+      <c r="L647" s="15"/>
+      <c r="M647" s="15"/>
     </row>
     <row r="648">
-      <c r="L648" s="10"/>
-      <c r="M648" s="10"/>
+      <c r="G648" s="14"/>
+      <c r="H648" s="14"/>
+      <c r="L648" s="15"/>
+      <c r="M648" s="15"/>
     </row>
     <row r="649">
-      <c r="L649" s="10"/>
-      <c r="M649" s="10"/>
+      <c r="G649" s="14"/>
+      <c r="H649" s="14"/>
+      <c r="L649" s="15"/>
+      <c r="M649" s="15"/>
     </row>
     <row r="650">
-      <c r="L650" s="10"/>
-      <c r="M650" s="10"/>
+      <c r="G650" s="14"/>
+      <c r="H650" s="14"/>
+      <c r="L650" s="15"/>
+      <c r="M650" s="15"/>
     </row>
     <row r="651">
-      <c r="L651" s="10"/>
-      <c r="M651" s="10"/>
+      <c r="G651" s="14"/>
+      <c r="H651" s="14"/>
+      <c r="L651" s="15"/>
+      <c r="M651" s="15"/>
     </row>
     <row r="652">
-      <c r="L652" s="10"/>
-      <c r="M652" s="10"/>
+      <c r="G652" s="14"/>
+      <c r="H652" s="14"/>
+      <c r="L652" s="15"/>
+      <c r="M652" s="15"/>
     </row>
     <row r="653">
-      <c r="L653" s="10"/>
-      <c r="M653" s="10"/>
+      <c r="G653" s="14"/>
+      <c r="H653" s="14"/>
+      <c r="L653" s="15"/>
+      <c r="M653" s="15"/>
     </row>
     <row r="654">
-      <c r="L654" s="10"/>
-      <c r="M654" s="10"/>
+      <c r="G654" s="14"/>
+      <c r="H654" s="14"/>
+      <c r="L654" s="15"/>
+      <c r="M654" s="15"/>
     </row>
     <row r="655">
-      <c r="L655" s="10"/>
-      <c r="M655" s="10"/>
+      <c r="G655" s="14"/>
+      <c r="H655" s="14"/>
+      <c r="L655" s="15"/>
+      <c r="M655" s="15"/>
     </row>
     <row r="656">
-      <c r="L656" s="10"/>
-      <c r="M656" s="10"/>
+      <c r="G656" s="14"/>
+      <c r="H656" s="14"/>
+      <c r="L656" s="15"/>
+      <c r="M656" s="15"/>
     </row>
     <row r="657">
-      <c r="L657" s="10"/>
-      <c r="M657" s="10"/>
+      <c r="G657" s="14"/>
+      <c r="H657" s="14"/>
+      <c r="L657" s="15"/>
+      <c r="M657" s="15"/>
     </row>
     <row r="658">
-      <c r="L658" s="10"/>
-      <c r="M658" s="10"/>
+      <c r="G658" s="14"/>
+      <c r="H658" s="14"/>
+      <c r="L658" s="15"/>
+      <c r="M658" s="15"/>
     </row>
     <row r="659">
-      <c r="L659" s="10"/>
-      <c r="M659" s="10"/>
+      <c r="G659" s="14"/>
+      <c r="H659" s="14"/>
+      <c r="L659" s="15"/>
+      <c r="M659" s="15"/>
     </row>
     <row r="660">
-      <c r="L660" s="10"/>
-      <c r="M660" s="10"/>
+      <c r="G660" s="14"/>
+      <c r="H660" s="14"/>
+      <c r="L660" s="15"/>
+      <c r="M660" s="15"/>
     </row>
     <row r="661">
-      <c r="L661" s="10"/>
-      <c r="M661" s="10"/>
+      <c r="G661" s="14"/>
+      <c r="H661" s="14"/>
+      <c r="L661" s="15"/>
+      <c r="M661" s="15"/>
     </row>
     <row r="662">
-      <c r="L662" s="10"/>
-      <c r="M662" s="10"/>
+      <c r="G662" s="14"/>
+      <c r="H662" s="14"/>
+      <c r="L662" s="15"/>
+      <c r="M662" s="15"/>
     </row>
     <row r="663">
-      <c r="L663" s="10"/>
-      <c r="M663" s="10"/>
+      <c r="G663" s="14"/>
+      <c r="H663" s="14"/>
+      <c r="L663" s="15"/>
+      <c r="M663" s="15"/>
     </row>
     <row r="664">
-      <c r="L664" s="10"/>
-      <c r="M664" s="10"/>
+      <c r="G664" s="14"/>
+      <c r="H664" s="14"/>
+      <c r="L664" s="15"/>
+      <c r="M664" s="15"/>
     </row>
     <row r="665">
-      <c r="L665" s="10"/>
-      <c r="M665" s="10"/>
+      <c r="G665" s="14"/>
+      <c r="H665" s="14"/>
+      <c r="L665" s="15"/>
+      <c r="M665" s="15"/>
     </row>
     <row r="666">
-      <c r="L666" s="10"/>
-      <c r="M666" s="10"/>
+      <c r="G666" s="14"/>
+      <c r="H666" s="14"/>
+      <c r="L666" s="15"/>
+      <c r="M666" s="15"/>
     </row>
     <row r="667">
-      <c r="L667" s="10"/>
-      <c r="M667" s="10"/>
+      <c r="G667" s="14"/>
+      <c r="H667" s="14"/>
+      <c r="L667" s="15"/>
+      <c r="M667" s="15"/>
     </row>
     <row r="668">
-      <c r="L668" s="10"/>
-      <c r="M668" s="10"/>
+      <c r="G668" s="14"/>
+      <c r="H668" s="14"/>
+      <c r="L668" s="15"/>
+      <c r="M668" s="15"/>
     </row>
     <row r="669">
-      <c r="L669" s="10"/>
-      <c r="M669" s="10"/>
+      <c r="G669" s="14"/>
+      <c r="H669" s="14"/>
+      <c r="L669" s="15"/>
+      <c r="M669" s="15"/>
     </row>
     <row r="670">
-      <c r="L670" s="10"/>
-      <c r="M670" s="10"/>
+      <c r="G670" s="14"/>
+      <c r="H670" s="14"/>
+      <c r="L670" s="15"/>
+      <c r="M670" s="15"/>
     </row>
     <row r="671">
-      <c r="L671" s="10"/>
-      <c r="M671" s="10"/>
+      <c r="G671" s="14"/>
+      <c r="H671" s="14"/>
+      <c r="L671" s="15"/>
+      <c r="M671" s="15"/>
     </row>
     <row r="672">
-      <c r="L672" s="10"/>
-      <c r="M672" s="10"/>
+      <c r="G672" s="14"/>
+      <c r="H672" s="14"/>
+      <c r="L672" s="15"/>
+      <c r="M672" s="15"/>
     </row>
     <row r="673">
-      <c r="L673" s="10"/>
-      <c r="M673" s="10"/>
+      <c r="G673" s="14"/>
+      <c r="H673" s="14"/>
+      <c r="L673" s="15"/>
+      <c r="M673" s="15"/>
     </row>
     <row r="674">
-      <c r="L674" s="10"/>
-      <c r="M674" s="10"/>
+      <c r="G674" s="14"/>
+      <c r="H674" s="14"/>
+      <c r="L674" s="15"/>
+      <c r="M674" s="15"/>
     </row>
     <row r="675">
-      <c r="L675" s="10"/>
-      <c r="M675" s="10"/>
+      <c r="G675" s="14"/>
+      <c r="H675" s="14"/>
+      <c r="L675" s="15"/>
+      <c r="M675" s="15"/>
     </row>
     <row r="676">
-      <c r="L676" s="10"/>
-      <c r="M676" s="10"/>
+      <c r="G676" s="14"/>
+      <c r="H676" s="14"/>
+      <c r="L676" s="15"/>
+      <c r="M676" s="15"/>
     </row>
     <row r="677">
-      <c r="L677" s="10"/>
-      <c r="M677" s="10"/>
+      <c r="G677" s="14"/>
+      <c r="H677" s="14"/>
+      <c r="L677" s="15"/>
+      <c r="M677" s="15"/>
     </row>
     <row r="678">
-      <c r="L678" s="10"/>
-      <c r="M678" s="10"/>
+      <c r="G678" s="14"/>
+      <c r="H678" s="14"/>
+      <c r="L678" s="15"/>
+      <c r="M678" s="15"/>
     </row>
     <row r="679">
-      <c r="L679" s="10"/>
-      <c r="M679" s="10"/>
+      <c r="G679" s="14"/>
+      <c r="H679" s="14"/>
+      <c r="L679" s="15"/>
+      <c r="M679" s="15"/>
     </row>
     <row r="680">
-      <c r="L680" s="10"/>
-      <c r="M680" s="10"/>
+      <c r="G680" s="14"/>
+      <c r="H680" s="14"/>
+      <c r="L680" s="15"/>
+      <c r="M680" s="15"/>
     </row>
     <row r="681">
-      <c r="L681" s="10"/>
-      <c r="M681" s="10"/>
+      <c r="G681" s="14"/>
+      <c r="H681" s="14"/>
+      <c r="L681" s="15"/>
+      <c r="M681" s="15"/>
     </row>
     <row r="682">
-      <c r="L682" s="10"/>
-      <c r="M682" s="10"/>
+      <c r="G682" s="14"/>
+      <c r="H682" s="14"/>
+      <c r="L682" s="15"/>
+      <c r="M682" s="15"/>
     </row>
     <row r="683">
-      <c r="L683" s="10"/>
-      <c r="M683" s="10"/>
+      <c r="G683" s="14"/>
+      <c r="H683" s="14"/>
+      <c r="L683" s="15"/>
+      <c r="M683" s="15"/>
     </row>
     <row r="684">
-      <c r="L684" s="10"/>
-      <c r="M684" s="10"/>
+      <c r="G684" s="14"/>
+      <c r="H684" s="14"/>
+      <c r="L684" s="15"/>
+      <c r="M684" s="15"/>
     </row>
     <row r="685">
-      <c r="L685" s="10"/>
-      <c r="M685" s="10"/>
+      <c r="G685" s="14"/>
+      <c r="H685" s="14"/>
+      <c r="L685" s="15"/>
+      <c r="M685" s="15"/>
     </row>
     <row r="686">
-      <c r="L686" s="10"/>
-      <c r="M686" s="10"/>
+      <c r="G686" s="14"/>
+      <c r="H686" s="14"/>
+      <c r="L686" s="15"/>
+      <c r="M686" s="15"/>
     </row>
     <row r="687">
-      <c r="L687" s="10"/>
-      <c r="M687" s="10"/>
+      <c r="G687" s="14"/>
+      <c r="H687" s="14"/>
+      <c r="L687" s="15"/>
+      <c r="M687" s="15"/>
     </row>
     <row r="688">
-      <c r="L688" s="10"/>
-      <c r="M688" s="10"/>
+      <c r="G688" s="14"/>
+      <c r="H688" s="14"/>
+      <c r="L688" s="15"/>
+      <c r="M688" s="15"/>
     </row>
     <row r="689">
-      <c r="L689" s="10"/>
-      <c r="M689" s="10"/>
+      <c r="G689" s="14"/>
+      <c r="H689" s="14"/>
+      <c r="L689" s="15"/>
+      <c r="M689" s="15"/>
     </row>
     <row r="690">
-      <c r="L690" s="10"/>
-      <c r="M690" s="10"/>
+      <c r="G690" s="14"/>
+      <c r="H690" s="14"/>
+      <c r="L690" s="15"/>
+      <c r="M690" s="15"/>
     </row>
     <row r="691">
-      <c r="L691" s="10"/>
-      <c r="M691" s="10"/>
+      <c r="G691" s="14"/>
+      <c r="H691" s="14"/>
+      <c r="L691" s="15"/>
+      <c r="M691" s="15"/>
     </row>
     <row r="692">
-      <c r="L692" s="10"/>
-      <c r="M692" s="10"/>
+      <c r="G692" s="14"/>
+      <c r="H692" s="14"/>
+      <c r="L692" s="15"/>
+      <c r="M692" s="15"/>
     </row>
     <row r="693">
-      <c r="L693" s="10"/>
-      <c r="M693" s="10"/>
+      <c r="G693" s="14"/>
+      <c r="H693" s="14"/>
+      <c r="L693" s="15"/>
+      <c r="M693" s="15"/>
     </row>
     <row r="694">
-      <c r="L694" s="10"/>
-      <c r="M694" s="10"/>
+      <c r="G694" s="14"/>
+      <c r="H694" s="14"/>
+      <c r="L694" s="15"/>
+      <c r="M694" s="15"/>
     </row>
     <row r="695">
-      <c r="L695" s="10"/>
-      <c r="M695" s="10"/>
+      <c r="G695" s="14"/>
+      <c r="H695" s="14"/>
+      <c r="L695" s="15"/>
+      <c r="M695" s="15"/>
     </row>
     <row r="696">
-      <c r="L696" s="10"/>
-      <c r="M696" s="10"/>
+      <c r="G696" s="14"/>
+      <c r="H696" s="14"/>
+      <c r="L696" s="15"/>
+      <c r="M696" s="15"/>
     </row>
     <row r="697">
-      <c r="L697" s="10"/>
-      <c r="M697" s="10"/>
+      <c r="G697" s="14"/>
+      <c r="H697" s="14"/>
+      <c r="L697" s="15"/>
+      <c r="M697" s="15"/>
     </row>
     <row r="698">
-      <c r="L698" s="10"/>
-      <c r="M698" s="10"/>
+      <c r="G698" s="14"/>
+      <c r="H698" s="14"/>
+      <c r="L698" s="15"/>
+      <c r="M698" s="15"/>
     </row>
     <row r="699">
-      <c r="L699" s="10"/>
-      <c r="M699" s="10"/>
+      <c r="G699" s="14"/>
+      <c r="H699" s="14"/>
+      <c r="L699" s="15"/>
+      <c r="M699" s="15"/>
     </row>
     <row r="700">
-      <c r="L700" s="10"/>
-      <c r="M700" s="10"/>
+      <c r="G700" s="14"/>
+      <c r="H700" s="14"/>
+      <c r="L700" s="15"/>
+      <c r="M700" s="15"/>
     </row>
     <row r="701">
-      <c r="L701" s="10"/>
-      <c r="M701" s="10"/>
+      <c r="G701" s="14"/>
+      <c r="H701" s="14"/>
+      <c r="L701" s="15"/>
+      <c r="M701" s="15"/>
     </row>
     <row r="702">
-      <c r="L702" s="10"/>
-      <c r="M702" s="10"/>
+      <c r="G702" s="14"/>
+      <c r="H702" s="14"/>
+      <c r="L702" s="15"/>
+      <c r="M702" s="15"/>
     </row>
     <row r="703">
-      <c r="L703" s="10"/>
-      <c r="M703" s="10"/>
+      <c r="G703" s="14"/>
+      <c r="H703" s="14"/>
+      <c r="L703" s="15"/>
+      <c r="M703" s="15"/>
     </row>
     <row r="704">
-      <c r="L704" s="10"/>
-      <c r="M704" s="10"/>
+      <c r="G704" s="14"/>
+      <c r="H704" s="14"/>
+      <c r="L704" s="15"/>
+      <c r="M704" s="15"/>
     </row>
     <row r="705">
-      <c r="L705" s="10"/>
-      <c r="M705" s="10"/>
+      <c r="G705" s="14"/>
+      <c r="H705" s="14"/>
+      <c r="L705" s="15"/>
+      <c r="M705" s="15"/>
     </row>
     <row r="706">
-      <c r="L706" s="10"/>
-      <c r="M706" s="10"/>
+      <c r="G706" s="14"/>
+      <c r="H706" s="14"/>
+      <c r="L706" s="15"/>
+      <c r="M706" s="15"/>
     </row>
     <row r="707">
-      <c r="L707" s="10"/>
-      <c r="M707" s="10"/>
+      <c r="G707" s="14"/>
+      <c r="H707" s="14"/>
+      <c r="L707" s="15"/>
+      <c r="M707" s="15"/>
     </row>
     <row r="708">
-      <c r="L708" s="10"/>
-      <c r="M708" s="10"/>
+      <c r="G708" s="14"/>
+      <c r="H708" s="14"/>
+      <c r="L708" s="15"/>
+      <c r="M708" s="15"/>
     </row>
     <row r="709">
-      <c r="L709" s="10"/>
-      <c r="M709" s="10"/>
+      <c r="G709" s="14"/>
+      <c r="H709" s="14"/>
+      <c r="L709" s="15"/>
+      <c r="M709" s="15"/>
     </row>
     <row r="710">
-      <c r="L710" s="10"/>
-      <c r="M710" s="10"/>
+      <c r="G710" s="14"/>
+      <c r="H710" s="14"/>
+      <c r="L710" s="15"/>
+      <c r="M710" s="15"/>
     </row>
     <row r="711">
-      <c r="L711" s="10"/>
-      <c r="M711" s="10"/>
+      <c r="G711" s="14"/>
+      <c r="H711" s="14"/>
+      <c r="L711" s="15"/>
+      <c r="M711" s="15"/>
     </row>
     <row r="712">
-      <c r="L712" s="10"/>
-      <c r="M712" s="10"/>
+      <c r="G712" s="14"/>
+      <c r="H712" s="14"/>
+      <c r="L712" s="15"/>
+      <c r="M712" s="15"/>
     </row>
     <row r="713">
-      <c r="L713" s="10"/>
-      <c r="M713" s="10"/>
+      <c r="G713" s="14"/>
+      <c r="H713" s="14"/>
+      <c r="L713" s="15"/>
+      <c r="M713" s="15"/>
     </row>
     <row r="714">
-      <c r="L714" s="10"/>
-      <c r="M714" s="10"/>
+      <c r="G714" s="14"/>
+      <c r="H714" s="14"/>
+      <c r="L714" s="15"/>
+      <c r="M714" s="15"/>
     </row>
     <row r="715">
-      <c r="L715" s="10"/>
-      <c r="M715" s="10"/>
+      <c r="G715" s="14"/>
+      <c r="H715" s="14"/>
+      <c r="L715" s="15"/>
+      <c r="M715" s="15"/>
     </row>
     <row r="716">
-      <c r="L716" s="10"/>
-      <c r="M716" s="10"/>
+      <c r="G716" s="14"/>
+      <c r="H716" s="14"/>
+      <c r="L716" s="15"/>
+      <c r="M716" s="15"/>
     </row>
     <row r="717">
-      <c r="L717" s="10"/>
-      <c r="M717" s="10"/>
+      <c r="G717" s="14"/>
+      <c r="H717" s="14"/>
+      <c r="L717" s="15"/>
+      <c r="M717" s="15"/>
     </row>
     <row r="718">
-      <c r="L718" s="10"/>
-      <c r="M718" s="10"/>
+      <c r="G718" s="14"/>
+      <c r="H718" s="14"/>
+      <c r="L718" s="15"/>
+      <c r="M718" s="15"/>
     </row>
     <row r="719">
-      <c r="L719" s="10"/>
-      <c r="M719" s="10"/>
+      <c r="G719" s="14"/>
+      <c r="H719" s="14"/>
+      <c r="L719" s="15"/>
+      <c r="M719" s="15"/>
     </row>
     <row r="720">
-      <c r="L720" s="10"/>
-      <c r="M720" s="10"/>
+      <c r="G720" s="14"/>
+      <c r="H720" s="14"/>
+      <c r="L720" s="15"/>
+      <c r="M720" s="15"/>
     </row>
     <row r="721">
-      <c r="L721" s="10"/>
-      <c r="M721" s="10"/>
+      <c r="G721" s="14"/>
+      <c r="H721" s="14"/>
+      <c r="L721" s="15"/>
+      <c r="M721" s="15"/>
     </row>
     <row r="722">
-      <c r="L722" s="10"/>
-      <c r="M722" s="10"/>
+      <c r="G722" s="14"/>
+      <c r="H722" s="14"/>
+      <c r="L722" s="15"/>
+      <c r="M722" s="15"/>
     </row>
     <row r="723">
-      <c r="L723" s="10"/>
-      <c r="M723" s="10"/>
+      <c r="G723" s="14"/>
+      <c r="H723" s="14"/>
+      <c r="L723" s="15"/>
+      <c r="M723" s="15"/>
     </row>
     <row r="724">
-      <c r="L724" s="10"/>
-      <c r="M724" s="10"/>
+      <c r="G724" s="14"/>
+      <c r="H724" s="14"/>
+      <c r="L724" s="15"/>
+      <c r="M724" s="15"/>
     </row>
     <row r="725">
-      <c r="L725" s="10"/>
-      <c r="M725" s="10"/>
+      <c r="G725" s="14"/>
+      <c r="H725" s="14"/>
+      <c r="L725" s="15"/>
+      <c r="M725" s="15"/>
     </row>
     <row r="726">
-      <c r="L726" s="10"/>
-      <c r="M726" s="10"/>
+      <c r="G726" s="14"/>
+      <c r="H726" s="14"/>
+      <c r="L726" s="15"/>
+      <c r="M726" s="15"/>
     </row>
     <row r="727">
-      <c r="L727" s="10"/>
-      <c r="M727" s="10"/>
+      <c r="G727" s="14"/>
+      <c r="H727" s="14"/>
+      <c r="L727" s="15"/>
+      <c r="M727" s="15"/>
     </row>
     <row r="728">
-      <c r="L728" s="10"/>
-      <c r="M728" s="10"/>
+      <c r="G728" s="14"/>
+      <c r="H728" s="14"/>
+      <c r="L728" s="15"/>
+      <c r="M728" s="15"/>
     </row>
     <row r="729">
-      <c r="L729" s="10"/>
-      <c r="M729" s="10"/>
+      <c r="G729" s="14"/>
+      <c r="H729" s="14"/>
+      <c r="L729" s="15"/>
+      <c r="M729" s="15"/>
     </row>
     <row r="730">
-      <c r="L730" s="10"/>
-      <c r="M730" s="10"/>
+      <c r="G730" s="14"/>
+      <c r="H730" s="14"/>
+      <c r="L730" s="15"/>
+      <c r="M730" s="15"/>
     </row>
     <row r="731">
-      <c r="L731" s="10"/>
-      <c r="M731" s="10"/>
+      <c r="G731" s="14"/>
+      <c r="H731" s="14"/>
+      <c r="L731" s="15"/>
+      <c r="M731" s="15"/>
     </row>
     <row r="732">
-      <c r="L732" s="10"/>
-      <c r="M732" s="10"/>
+      <c r="G732" s="14"/>
+      <c r="H732" s="14"/>
+      <c r="L732" s="15"/>
+      <c r="M732" s="15"/>
     </row>
     <row r="733">
-      <c r="L733" s="10"/>
-      <c r="M733" s="10"/>
+      <c r="G733" s="14"/>
+      <c r="H733" s="14"/>
+      <c r="L733" s="15"/>
+      <c r="M733" s="15"/>
     </row>
     <row r="734">
-      <c r="L734" s="10"/>
-      <c r="M734" s="10"/>
+      <c r="G734" s="14"/>
+      <c r="H734" s="14"/>
+      <c r="L734" s="15"/>
+      <c r="M734" s="15"/>
     </row>
     <row r="735">
-      <c r="L735" s="10"/>
-      <c r="M735" s="10"/>
+      <c r="G735" s="14"/>
+      <c r="H735" s="14"/>
+      <c r="L735" s="15"/>
+      <c r="M735" s="15"/>
     </row>
     <row r="736">
-      <c r="L736" s="10"/>
-      <c r="M736" s="10"/>
+      <c r="G736" s="14"/>
+      <c r="H736" s="14"/>
+      <c r="L736" s="15"/>
+      <c r="M736" s="15"/>
     </row>
     <row r="737">
-      <c r="L737" s="10"/>
-      <c r="M737" s="10"/>
+      <c r="G737" s="14"/>
+      <c r="H737" s="14"/>
+      <c r="L737" s="15"/>
+      <c r="M737" s="15"/>
     </row>
     <row r="738">
-      <c r="L738" s="10"/>
-      <c r="M738" s="10"/>
+      <c r="G738" s="14"/>
+      <c r="H738" s="14"/>
+      <c r="L738" s="15"/>
+      <c r="M738" s="15"/>
     </row>
     <row r="739">
-      <c r="L739" s="10"/>
-      <c r="M739" s="10"/>
+      <c r="G739" s="14"/>
+      <c r="H739" s="14"/>
+      <c r="L739" s="15"/>
+      <c r="M739" s="15"/>
     </row>
     <row r="740">
-      <c r="L740" s="10"/>
-      <c r="M740" s="10"/>
+      <c r="G740" s="14"/>
+      <c r="H740" s="14"/>
+      <c r="L740" s="15"/>
+      <c r="M740" s="15"/>
     </row>
     <row r="741">
-      <c r="L741" s="10"/>
-      <c r="M741" s="10"/>
+      <c r="G741" s="14"/>
+      <c r="H741" s="14"/>
+      <c r="L741" s="15"/>
+      <c r="M741" s="15"/>
     </row>
     <row r="742">
-      <c r="L742" s="10"/>
-      <c r="M742" s="10"/>
+      <c r="G742" s="14"/>
+      <c r="H742" s="14"/>
+      <c r="L742" s="15"/>
+      <c r="M742" s="15"/>
     </row>
     <row r="743">
-      <c r="L743" s="10"/>
-      <c r="M743" s="10"/>
+      <c r="G743" s="14"/>
+      <c r="H743" s="14"/>
+      <c r="L743" s="15"/>
+      <c r="M743" s="15"/>
     </row>
     <row r="744">
-      <c r="L744" s="10"/>
-      <c r="M744" s="10"/>
+      <c r="G744" s="14"/>
+      <c r="H744" s="14"/>
+      <c r="L744" s="15"/>
+      <c r="M744" s="15"/>
     </row>
     <row r="745">
-      <c r="L745" s="10"/>
-      <c r="M745" s="10"/>
+      <c r="G745" s="14"/>
+      <c r="H745" s="14"/>
+      <c r="L745" s="15"/>
+      <c r="M745" s="15"/>
     </row>
     <row r="746">
-      <c r="L746" s="10"/>
-      <c r="M746" s="10"/>
+      <c r="G746" s="14"/>
+      <c r="H746" s="14"/>
+      <c r="L746" s="15"/>
+      <c r="M746" s="15"/>
     </row>
     <row r="747">
-      <c r="L747" s="10"/>
-      <c r="M747" s="10"/>
+      <c r="G747" s="14"/>
+      <c r="H747" s="14"/>
+      <c r="L747" s="15"/>
+      <c r="M747" s="15"/>
     </row>
     <row r="748">
-      <c r="L748" s="10"/>
-      <c r="M748" s="10"/>
+      <c r="G748" s="14"/>
+      <c r="H748" s="14"/>
+      <c r="L748" s="15"/>
+      <c r="M748" s="15"/>
     </row>
     <row r="749">
-      <c r="L749" s="10"/>
-      <c r="M749" s="10"/>
+      <c r="G749" s="14"/>
+      <c r="H749" s="14"/>
+      <c r="L749" s="15"/>
+      <c r="M749" s="15"/>
     </row>
     <row r="750">
-      <c r="L750" s="10"/>
-      <c r="M750" s="10"/>
+      <c r="G750" s="14"/>
+      <c r="H750" s="14"/>
+      <c r="L750" s="15"/>
+      <c r="M750" s="15"/>
     </row>
     <row r="751">
-      <c r="L751" s="10"/>
-      <c r="M751" s="10"/>
+      <c r="G751" s="14"/>
+      <c r="H751" s="14"/>
+      <c r="L751" s="15"/>
+      <c r="M751" s="15"/>
     </row>
     <row r="752">
-      <c r="L752" s="10"/>
-      <c r="M752" s="10"/>
+      <c r="G752" s="14"/>
+      <c r="H752" s="14"/>
+      <c r="L752" s="15"/>
+      <c r="M752" s="15"/>
     </row>
     <row r="753">
-      <c r="L753" s="10"/>
-      <c r="M753" s="10"/>
+      <c r="G753" s="14"/>
+      <c r="H753" s="14"/>
+      <c r="L753" s="15"/>
+      <c r="M753" s="15"/>
     </row>
     <row r="754">
-      <c r="L754" s="10"/>
-      <c r="M754" s="10"/>
+      <c r="G754" s="14"/>
+      <c r="H754" s="14"/>
+      <c r="L754" s="15"/>
+      <c r="M754" s="15"/>
     </row>
     <row r="755">
-      <c r="L755" s="10"/>
-      <c r="M755" s="10"/>
+      <c r="G755" s="14"/>
+      <c r="H755" s="14"/>
+      <c r="L755" s="15"/>
+      <c r="M755" s="15"/>
     </row>
     <row r="756">
-      <c r="L756" s="10"/>
-      <c r="M756" s="10"/>
+      <c r="G756" s="14"/>
+      <c r="H756" s="14"/>
+      <c r="L756" s="15"/>
+      <c r="M756" s="15"/>
     </row>
     <row r="757">
-      <c r="L757" s="10"/>
-      <c r="M757" s="10"/>
+      <c r="G757" s="14"/>
+      <c r="H757" s="14"/>
+      <c r="L757" s="15"/>
+      <c r="M757" s="15"/>
     </row>
     <row r="758">
-      <c r="L758" s="10"/>
-      <c r="M758" s="10"/>
+      <c r="G758" s="14"/>
+      <c r="H758" s="14"/>
+      <c r="L758" s="15"/>
+      <c r="M758" s="15"/>
     </row>
     <row r="759">
-      <c r="L759" s="10"/>
-      <c r="M759" s="10"/>
+      <c r="G759" s="14"/>
+      <c r="H759" s="14"/>
+      <c r="L759" s="15"/>
+      <c r="M759" s="15"/>
     </row>
     <row r="760">
-      <c r="L760" s="10"/>
-      <c r="M760" s="10"/>
+      <c r="G760" s="14"/>
+      <c r="H760" s="14"/>
+      <c r="L760" s="15"/>
+      <c r="M760" s="15"/>
     </row>
     <row r="761">
-      <c r="L761" s="10"/>
-      <c r="M761" s="10"/>
+      <c r="G761" s="14"/>
+      <c r="H761" s="14"/>
+      <c r="L761" s="15"/>
+      <c r="M761" s="15"/>
     </row>
     <row r="762">
-      <c r="L762" s="10"/>
-      <c r="M762" s="10"/>
+      <c r="G762" s="14"/>
+      <c r="H762" s="14"/>
+      <c r="L762" s="15"/>
+      <c r="M762" s="15"/>
     </row>
     <row r="763">
-      <c r="L763" s="10"/>
-      <c r="M763" s="10"/>
+      <c r="G763" s="14"/>
+      <c r="H763" s="14"/>
+      <c r="L763" s="15"/>
+      <c r="M763" s="15"/>
     </row>
     <row r="764">
-      <c r="L764" s="10"/>
-      <c r="M764" s="10"/>
+      <c r="G764" s="14"/>
+      <c r="H764" s="14"/>
+      <c r="L764" s="15"/>
+      <c r="M764" s="15"/>
     </row>
     <row r="765">
-      <c r="L765" s="10"/>
-      <c r="M765" s="10"/>
+      <c r="G765" s="14"/>
+      <c r="H765" s="14"/>
+      <c r="L765" s="15"/>
+      <c r="M765" s="15"/>
     </row>
     <row r="766">
-      <c r="L766" s="10"/>
-      <c r="M766" s="10"/>
+      <c r="G766" s="14"/>
+      <c r="H766" s="14"/>
+      <c r="L766" s="15"/>
+      <c r="M766" s="15"/>
     </row>
     <row r="767">
-      <c r="L767" s="10"/>
-      <c r="M767" s="10"/>
+      <c r="G767" s="14"/>
+      <c r="H767" s="14"/>
+      <c r="L767" s="15"/>
+      <c r="M767" s="15"/>
     </row>
     <row r="768">
-      <c r="L768" s="10"/>
-      <c r="M768" s="10"/>
+      <c r="G768" s="14"/>
+      <c r="H768" s="14"/>
+      <c r="L768" s="15"/>
+      <c r="M768" s="15"/>
     </row>
     <row r="769">
-      <c r="L769" s="10"/>
-      <c r="M769" s="10"/>
+      <c r="G769" s="14"/>
+      <c r="H769" s="14"/>
+      <c r="L769" s="15"/>
+      <c r="M769" s="15"/>
     </row>
     <row r="770">
-      <c r="L770" s="10"/>
-      <c r="M770" s="10"/>
+      <c r="G770" s="14"/>
+      <c r="H770" s="14"/>
+      <c r="L770" s="15"/>
+      <c r="M770" s="15"/>
     </row>
     <row r="771">
-      <c r="L771" s="10"/>
-      <c r="M771" s="10"/>
+      <c r="G771" s="14"/>
+      <c r="H771" s="14"/>
+      <c r="L771" s="15"/>
+      <c r="M771" s="15"/>
     </row>
     <row r="772">
-      <c r="L772" s="10"/>
-      <c r="M772" s="10"/>
+      <c r="G772" s="14"/>
+      <c r="H772" s="14"/>
+      <c r="L772" s="15"/>
+      <c r="M772" s="15"/>
     </row>
     <row r="773">
-      <c r="L773" s="10"/>
-      <c r="M773" s="10"/>
+      <c r="G773" s="14"/>
+      <c r="H773" s="14"/>
+      <c r="L773" s="15"/>
+      <c r="M773" s="15"/>
     </row>
     <row r="774">
-      <c r="L774" s="10"/>
-      <c r="M774" s="10"/>
+      <c r="G774" s="14"/>
+      <c r="H774" s="14"/>
+      <c r="L774" s="15"/>
+      <c r="M774" s="15"/>
     </row>
     <row r="775">
-      <c r="L775" s="10"/>
-      <c r="M775" s="10"/>
+      <c r="G775" s="14"/>
+      <c r="H775" s="14"/>
+      <c r="L775" s="15"/>
+      <c r="M775" s="15"/>
     </row>
     <row r="776">
-      <c r="L776" s="10"/>
-      <c r="M776" s="10"/>
+      <c r="G776" s="14"/>
+      <c r="H776" s="14"/>
+      <c r="L776" s="15"/>
+      <c r="M776" s="15"/>
     </row>
     <row r="777">
-      <c r="L777" s="10"/>
-      <c r="M777" s="10"/>
+      <c r="G777" s="14"/>
+      <c r="H777" s="14"/>
+      <c r="L777" s="15"/>
+      <c r="M777" s="15"/>
     </row>
     <row r="778">
-      <c r="L778" s="10"/>
-      <c r="M778" s="10"/>
+      <c r="G778" s="14"/>
+      <c r="H778" s="14"/>
+      <c r="L778" s="15"/>
+      <c r="M778" s="15"/>
     </row>
     <row r="779">
-      <c r="L779" s="10"/>
-      <c r="M779" s="10"/>
+      <c r="G779" s="14"/>
+      <c r="H779" s="14"/>
+      <c r="L779" s="15"/>
+      <c r="M779" s="15"/>
     </row>
     <row r="780">
-      <c r="L780" s="10"/>
-      <c r="M780" s="10"/>
+      <c r="G780" s="14"/>
+      <c r="H780" s="14"/>
+      <c r="L780" s="15"/>
+      <c r="M780" s="15"/>
     </row>
     <row r="781">
-      <c r="L781" s="10"/>
-      <c r="M781" s="10"/>
+      <c r="G781" s="14"/>
+      <c r="H781" s="14"/>
+      <c r="L781" s="15"/>
+      <c r="M781" s="15"/>
     </row>
     <row r="782">
-      <c r="L782" s="10"/>
-      <c r="M782" s="10"/>
+      <c r="G782" s="14"/>
+      <c r="H782" s="14"/>
+      <c r="L782" s="15"/>
+      <c r="M782" s="15"/>
     </row>
     <row r="783">
-      <c r="L783" s="10"/>
-      <c r="M783" s="10"/>
+      <c r="G783" s="14"/>
+      <c r="H783" s="14"/>
+      <c r="L783" s="15"/>
+      <c r="M783" s="15"/>
     </row>
     <row r="784">
-      <c r="L784" s="10"/>
-      <c r="M784" s="10"/>
+      <c r="G784" s="14"/>
+      <c r="H784" s="14"/>
+      <c r="L784" s="15"/>
+      <c r="M784" s="15"/>
     </row>
     <row r="785">
-      <c r="L785" s="10"/>
-      <c r="M785" s="10"/>
+      <c r="G785" s="14"/>
+      <c r="H785" s="14"/>
+      <c r="L785" s="15"/>
+      <c r="M785" s="15"/>
     </row>
     <row r="786">
-      <c r="L786" s="10"/>
-      <c r="M786" s="10"/>
+      <c r="G786" s="14"/>
+      <c r="H786" s="14"/>
+      <c r="L786" s="15"/>
+      <c r="M786" s="15"/>
     </row>
     <row r="787">
-      <c r="L787" s="10"/>
-      <c r="M787" s="10"/>
+      <c r="G787" s="14"/>
+      <c r="H787" s="14"/>
+      <c r="L787" s="15"/>
+      <c r="M787" s="15"/>
     </row>
     <row r="788">
-      <c r="L788" s="10"/>
-      <c r="M788" s="10"/>
+      <c r="G788" s="14"/>
+      <c r="H788" s="14"/>
+      <c r="L788" s="15"/>
+      <c r="M788" s="15"/>
     </row>
     <row r="789">
-      <c r="L789" s="10"/>
-      <c r="M789" s="10"/>
+      <c r="G789" s="14"/>
+      <c r="H789" s="14"/>
+      <c r="L789" s="15"/>
+      <c r="M789" s="15"/>
     </row>
     <row r="790">
-      <c r="L790" s="10"/>
-      <c r="M790" s="10"/>
+      <c r="G790" s="14"/>
+      <c r="H790" s="14"/>
+      <c r="L790" s="15"/>
+      <c r="M790" s="15"/>
     </row>
     <row r="791">
-      <c r="L791" s="10"/>
-      <c r="M791" s="10"/>
+      <c r="G791" s="14"/>
+      <c r="H791" s="14"/>
+      <c r="L791" s="15"/>
+      <c r="M791" s="15"/>
     </row>
     <row r="792">
-      <c r="L792" s="10"/>
-      <c r="M792" s="10"/>
+      <c r="G792" s="14"/>
+      <c r="H792" s="14"/>
+      <c r="L792" s="15"/>
+      <c r="M792" s="15"/>
     </row>
     <row r="793">
-      <c r="L793" s="10"/>
-      <c r="M793" s="10"/>
+      <c r="G793" s="14"/>
+      <c r="H793" s="14"/>
+      <c r="L793" s="15"/>
+      <c r="M793" s="15"/>
     </row>
     <row r="794">
-      <c r="L794" s="10"/>
-      <c r="M794" s="10"/>
+      <c r="G794" s="14"/>
+      <c r="H794" s="14"/>
+      <c r="L794" s="15"/>
+      <c r="M794" s="15"/>
     </row>
     <row r="795">
-      <c r="L795" s="10"/>
-      <c r="M795" s="10"/>
+      <c r="G795" s="14"/>
+      <c r="H795" s="14"/>
+      <c r="L795" s="15"/>
+      <c r="M795" s="15"/>
     </row>
     <row r="796">
-      <c r="L796" s="10"/>
-      <c r="M796" s="10"/>
+      <c r="G796" s="14"/>
+      <c r="H796" s="14"/>
+      <c r="L796" s="15"/>
+      <c r="M796" s="15"/>
     </row>
     <row r="797">
-      <c r="L797" s="10"/>
-      <c r="M797" s="10"/>
+      <c r="G797" s="14"/>
+      <c r="H797" s="14"/>
+      <c r="L797" s="15"/>
+      <c r="M797" s="15"/>
     </row>
     <row r="798">
-      <c r="L798" s="10"/>
-      <c r="M798" s="10"/>
+      <c r="G798" s="14"/>
+      <c r="H798" s="14"/>
+      <c r="L798" s="15"/>
+      <c r="M798" s="15"/>
     </row>
     <row r="799">
-      <c r="L799" s="10"/>
-      <c r="M799" s="10"/>
+      <c r="G799" s="14"/>
+      <c r="H799" s="14"/>
+      <c r="L799" s="15"/>
+      <c r="M799" s="15"/>
     </row>
     <row r="800">
-      <c r="L800" s="10"/>
-      <c r="M800" s="10"/>
+      <c r="G800" s="14"/>
+      <c r="H800" s="14"/>
+      <c r="L800" s="15"/>
+      <c r="M800" s="15"/>
     </row>
     <row r="801">
-      <c r="L801" s="10"/>
-      <c r="M801" s="10"/>
+      <c r="G801" s="14"/>
+      <c r="H801" s="14"/>
+      <c r="L801" s="15"/>
+      <c r="M801" s="15"/>
     </row>
     <row r="802">
-      <c r="L802" s="10"/>
-      <c r="M802" s="10"/>
+      <c r="G802" s="14"/>
+      <c r="H802" s="14"/>
+      <c r="L802" s="15"/>
+      <c r="M802" s="15"/>
     </row>
     <row r="803">
-      <c r="L803" s="10"/>
-      <c r="M803" s="10"/>
+      <c r="G803" s="14"/>
+      <c r="H803" s="14"/>
+      <c r="L803" s="15"/>
+      <c r="M803" s="15"/>
     </row>
     <row r="804">
-      <c r="L804" s="10"/>
-      <c r="M804" s="10"/>
+      <c r="G804" s="14"/>
+      <c r="H804" s="14"/>
+      <c r="L804" s="15"/>
+      <c r="M804" s="15"/>
     </row>
     <row r="805">
-      <c r="L805" s="10"/>
-      <c r="M805" s="10"/>
+      <c r="G805" s="14"/>
+      <c r="H805" s="14"/>
+      <c r="L805" s="15"/>
+      <c r="M805" s="15"/>
     </row>
     <row r="806">
-      <c r="L806" s="10"/>
-      <c r="M806" s="10"/>
+      <c r="G806" s="14"/>
+      <c r="H806" s="14"/>
+      <c r="L806" s="15"/>
+      <c r="M806" s="15"/>
     </row>
     <row r="807">
-      <c r="L807" s="10"/>
-      <c r="M807" s="10"/>
+      <c r="G807" s="14"/>
+      <c r="H807" s="14"/>
+      <c r="L807" s="15"/>
+      <c r="M807" s="15"/>
     </row>
     <row r="808">
-      <c r="L808" s="10"/>
-      <c r="M808" s="10"/>
+      <c r="G808" s="14"/>
+      <c r="H808" s="14"/>
+      <c r="L808" s="15"/>
+      <c r="M808" s="15"/>
     </row>
     <row r="809">
-      <c r="L809" s="10"/>
-      <c r="M809" s="10"/>
+      <c r="G809" s="14"/>
+      <c r="H809" s="14"/>
+      <c r="L809" s="15"/>
+      <c r="M809" s="15"/>
     </row>
     <row r="810">
-      <c r="L810" s="10"/>
-      <c r="M810" s="10"/>
+      <c r="G810" s="14"/>
+      <c r="H810" s="14"/>
+      <c r="L810" s="15"/>
+      <c r="M810" s="15"/>
     </row>
     <row r="811">
-      <c r="L811" s="10"/>
-      <c r="M811" s="10"/>
+      <c r="G811" s="14"/>
+      <c r="H811" s="14"/>
+      <c r="L811" s="15"/>
+      <c r="M811" s="15"/>
     </row>
     <row r="812">
-      <c r="L812" s="10"/>
-      <c r="M812" s="10"/>
+      <c r="G812" s="14"/>
+      <c r="H812" s="14"/>
+      <c r="L812" s="15"/>
+      <c r="M812" s="15"/>
     </row>
     <row r="813">
-      <c r="L813" s="10"/>
-      <c r="M813" s="10"/>
+      <c r="G813" s="14"/>
+      <c r="H813" s="14"/>
+      <c r="L813" s="15"/>
+      <c r="M813" s="15"/>
     </row>
     <row r="814">
-      <c r="L814" s="10"/>
-      <c r="M814" s="10"/>
+      <c r="G814" s="14"/>
+      <c r="H814" s="14"/>
+      <c r="L814" s="15"/>
+      <c r="M814" s="15"/>
     </row>
     <row r="815">
-      <c r="L815" s="10"/>
-      <c r="M815" s="10"/>
+      <c r="G815" s="14"/>
+      <c r="H815" s="14"/>
+      <c r="L815" s="15"/>
+      <c r="M815" s="15"/>
     </row>
     <row r="816">
-      <c r="L816" s="10"/>
-      <c r="M816" s="10"/>
+      <c r="G816" s="14"/>
+      <c r="H816" s="14"/>
+      <c r="L816" s="15"/>
+      <c r="M816" s="15"/>
     </row>
     <row r="817">
-      <c r="L817" s="10"/>
-      <c r="M817" s="10"/>
+      <c r="G817" s="14"/>
+      <c r="H817" s="14"/>
+      <c r="L817" s="15"/>
+      <c r="M817" s="15"/>
     </row>
     <row r="818">
-      <c r="L818" s="10"/>
-      <c r="M818" s="10"/>
+      <c r="G818" s="14"/>
+      <c r="H818" s="14"/>
+      <c r="L818" s="15"/>
+      <c r="M818" s="15"/>
     </row>
     <row r="819">
-      <c r="L819" s="10"/>
-      <c r="M819" s="10"/>
+      <c r="G819" s="14"/>
+      <c r="H819" s="14"/>
+      <c r="L819" s="15"/>
+      <c r="M819" s="15"/>
     </row>
     <row r="820">
-      <c r="L820" s="10"/>
-      <c r="M820" s="10"/>
+      <c r="G820" s="14"/>
+      <c r="H820" s="14"/>
+      <c r="L820" s="15"/>
+      <c r="M820" s="15"/>
     </row>
     <row r="821">
-      <c r="L821" s="10"/>
-      <c r="M821" s="10"/>
+      <c r="G821" s="14"/>
+      <c r="H821" s="14"/>
+      <c r="L821" s="15"/>
+      <c r="M821" s="15"/>
     </row>
     <row r="822">
-      <c r="L822" s="10"/>
-      <c r="M822" s="10"/>
+      <c r="G822" s="14"/>
+      <c r="H822" s="14"/>
+      <c r="L822" s="15"/>
+      <c r="M822" s="15"/>
     </row>
     <row r="823">
-      <c r="L823" s="10"/>
-      <c r="M823" s="10"/>
+      <c r="G823" s="14"/>
+      <c r="H823" s="14"/>
+      <c r="L823" s="15"/>
+      <c r="M823" s="15"/>
     </row>
     <row r="824">
-      <c r="L824" s="10"/>
-      <c r="M824" s="10"/>
+      <c r="G824" s="14"/>
+      <c r="H824" s="14"/>
+      <c r="L824" s="15"/>
+      <c r="M824" s="15"/>
     </row>
     <row r="825">
-      <c r="L825" s="10"/>
-      <c r="M825" s="10"/>
+      <c r="G825" s="14"/>
+      <c r="H825" s="14"/>
+      <c r="L825" s="15"/>
+      <c r="M825" s="15"/>
     </row>
     <row r="826">
-      <c r="L826" s="10"/>
-      <c r="M826" s="10"/>
+      <c r="G826" s="14"/>
+      <c r="H826" s="14"/>
+      <c r="L826" s="15"/>
+      <c r="M826" s="15"/>
     </row>
     <row r="827">
-      <c r="L827" s="10"/>
-      <c r="M827" s="10"/>
+      <c r="G827" s="14"/>
+      <c r="H827" s="14"/>
+      <c r="L827" s="15"/>
+      <c r="M827" s="15"/>
     </row>
     <row r="828">
-      <c r="L828" s="10"/>
-      <c r="M828" s="10"/>
+      <c r="G828" s="14"/>
+      <c r="H828" s="14"/>
+      <c r="L828" s="15"/>
+      <c r="M828" s="15"/>
     </row>
     <row r="829">
-      <c r="L829" s="10"/>
-      <c r="M829" s="10"/>
+      <c r="G829" s="14"/>
+      <c r="H829" s="14"/>
+      <c r="L829" s="15"/>
+      <c r="M829" s="15"/>
     </row>
     <row r="830">
-      <c r="L830" s="10"/>
-      <c r="M830" s="10"/>
+      <c r="G830" s="14"/>
+      <c r="H830" s="14"/>
+      <c r="L830" s="15"/>
+      <c r="M830" s="15"/>
     </row>
     <row r="831">
-      <c r="L831" s="10"/>
-      <c r="M831" s="10"/>
+      <c r="G831" s="14"/>
+      <c r="H831" s="14"/>
+      <c r="L831" s="15"/>
+      <c r="M831" s="15"/>
     </row>
     <row r="832">
-      <c r="L832" s="10"/>
-      <c r="M832" s="10"/>
+      <c r="G832" s="14"/>
+      <c r="H832" s="14"/>
+      <c r="L832" s="15"/>
+      <c r="M832" s="15"/>
     </row>
     <row r="833">
-      <c r="L833" s="10"/>
-      <c r="M833" s="10"/>
+      <c r="G833" s="14"/>
+      <c r="H833" s="14"/>
+      <c r="L833" s="15"/>
+      <c r="M833" s="15"/>
     </row>
     <row r="834">
-      <c r="L834" s="10"/>
-      <c r="M834" s="10"/>
+      <c r="G834" s="14"/>
+      <c r="H834" s="14"/>
+      <c r="L834" s="15"/>
+      <c r="M834" s="15"/>
     </row>
     <row r="835">
-      <c r="L835" s="10"/>
-      <c r="M835" s="10"/>
+      <c r="G835" s="14"/>
+      <c r="H835" s="14"/>
+      <c r="L835" s="15"/>
+      <c r="M835" s="15"/>
     </row>
     <row r="836">
-      <c r="L836" s="10"/>
-      <c r="M836" s="10"/>
+      <c r="G836" s="14"/>
+      <c r="H836" s="14"/>
+      <c r="L836" s="15"/>
+      <c r="M836" s="15"/>
     </row>
     <row r="837">
-      <c r="L837" s="10"/>
-      <c r="M837" s="10"/>
+      <c r="G837" s="14"/>
+      <c r="H837" s="14"/>
+      <c r="L837" s="15"/>
+      <c r="M837" s="15"/>
     </row>
     <row r="838">
-      <c r="L838" s="10"/>
-      <c r="M838" s="10"/>
+      <c r="G838" s="14"/>
+      <c r="H838" s="14"/>
+      <c r="L838" s="15"/>
+      <c r="M838" s="15"/>
     </row>
     <row r="839">
-      <c r="L839" s="10"/>
-      <c r="M839" s="10"/>
+      <c r="G839" s="14"/>
+      <c r="H839" s="14"/>
+      <c r="L839" s="15"/>
+      <c r="M839" s="15"/>
     </row>
     <row r="840">
-      <c r="L840" s="10"/>
-      <c r="M840" s="10"/>
+      <c r="G840" s="14"/>
+      <c r="H840" s="14"/>
+      <c r="L840" s="15"/>
+      <c r="M840" s="15"/>
     </row>
     <row r="841">
-      <c r="L841" s="10"/>
-      <c r="M841" s="10"/>
+      <c r="G841" s="14"/>
+      <c r="H841" s="14"/>
+      <c r="L841" s="15"/>
+      <c r="M841" s="15"/>
     </row>
     <row r="842">
-      <c r="L842" s="10"/>
-      <c r="M842" s="10"/>
+      <c r="G842" s="14"/>
+      <c r="H842" s="14"/>
+      <c r="L842" s="15"/>
+      <c r="M842" s="15"/>
     </row>
     <row r="843">
-      <c r="L843" s="10"/>
-      <c r="M843" s="10"/>
+      <c r="G843" s="14"/>
+      <c r="H843" s="14"/>
+      <c r="L843" s="15"/>
+      <c r="M843" s="15"/>
     </row>
     <row r="844">
-      <c r="L844" s="10"/>
-      <c r="M844" s="10"/>
+      <c r="G844" s="14"/>
+      <c r="H844" s="14"/>
+      <c r="L844" s="15"/>
+      <c r="M844" s="15"/>
     </row>
     <row r="845">
-      <c r="L845" s="10"/>
-      <c r="M845" s="10"/>
+      <c r="G845" s="14"/>
+      <c r="H845" s="14"/>
+      <c r="L845" s="15"/>
+      <c r="M845" s="15"/>
     </row>
     <row r="846">
-      <c r="L846" s="10"/>
-      <c r="M846" s="10"/>
+      <c r="G846" s="14"/>
+      <c r="H846" s="14"/>
+      <c r="L846" s="15"/>
+      <c r="M846" s="15"/>
     </row>
     <row r="847">
-      <c r="L847" s="10"/>
-      <c r="M847" s="10"/>
+      <c r="G847" s="14"/>
+      <c r="H847" s="14"/>
+      <c r="L847" s="15"/>
+      <c r="M847" s="15"/>
     </row>
     <row r="848">
-      <c r="L848" s="10"/>
-      <c r="M848" s="10"/>
+      <c r="G848" s="14"/>
+      <c r="H848" s="14"/>
+      <c r="L848" s="15"/>
+      <c r="M848" s="15"/>
     </row>
     <row r="849">
-      <c r="L849" s="10"/>
-      <c r="M849" s="10"/>
+      <c r="G849" s="14"/>
+      <c r="H849" s="14"/>
+      <c r="L849" s="15"/>
+      <c r="M849" s="15"/>
     </row>
     <row r="850">
-      <c r="L850" s="10"/>
-      <c r="M850" s="10"/>
+      <c r="G850" s="14"/>
+      <c r="H850" s="14"/>
+      <c r="L850" s="15"/>
+      <c r="M850" s="15"/>
     </row>
     <row r="851">
-      <c r="L851" s="10"/>
-      <c r="M851" s="10"/>
+      <c r="G851" s="14"/>
+      <c r="H851" s="14"/>
+      <c r="L851" s="15"/>
+      <c r="M851" s="15"/>
     </row>
     <row r="852">
-      <c r="L852" s="10"/>
-      <c r="M852" s="10"/>
+      <c r="G852" s="14"/>
+      <c r="H852" s="14"/>
+      <c r="L852" s="15"/>
+      <c r="M852" s="15"/>
     </row>
     <row r="853">
-      <c r="L853" s="10"/>
-      <c r="M853" s="10"/>
+      <c r="G853" s="14"/>
+      <c r="H853" s="14"/>
+      <c r="L853" s="15"/>
+      <c r="M853" s="15"/>
     </row>
     <row r="854">
-      <c r="L854" s="10"/>
-      <c r="M854" s="10"/>
+      <c r="G854" s="14"/>
+      <c r="H854" s="14"/>
+      <c r="L854" s="15"/>
+      <c r="M854" s="15"/>
     </row>
     <row r="855">
-      <c r="L855" s="10"/>
-      <c r="M855" s="10"/>
+      <c r="G855" s="14"/>
+      <c r="H855" s="14"/>
+      <c r="L855" s="15"/>
+      <c r="M855" s="15"/>
     </row>
     <row r="856">
-      <c r="L856" s="10"/>
-      <c r="M856" s="10"/>
+      <c r="G856" s="14"/>
+      <c r="H856" s="14"/>
+      <c r="L856" s="15"/>
+      <c r="M856" s="15"/>
     </row>
     <row r="857">
-      <c r="L857" s="10"/>
-      <c r="M857" s="10"/>
+      <c r="G857" s="14"/>
+      <c r="H857" s="14"/>
+      <c r="L857" s="15"/>
+      <c r="M857" s="15"/>
     </row>
     <row r="858">
-      <c r="L858" s="10"/>
-      <c r="M858" s="10"/>
+      <c r="G858" s="14"/>
+      <c r="H858" s="14"/>
+      <c r="L858" s="15"/>
+      <c r="M858" s="15"/>
     </row>
     <row r="859">
-      <c r="L859" s="10"/>
-      <c r="M859" s="10"/>
+      <c r="G859" s="14"/>
+      <c r="H859" s="14"/>
+      <c r="L859" s="15"/>
+      <c r="M859" s="15"/>
     </row>
     <row r="860">
-      <c r="L860" s="10"/>
-      <c r="M860" s="10"/>
+      <c r="G860" s="14"/>
+      <c r="H860" s="14"/>
+      <c r="L860" s="15"/>
+      <c r="M860" s="15"/>
     </row>
     <row r="861">
-      <c r="L861" s="10"/>
-      <c r="M861" s="10"/>
+      <c r="G861" s="14"/>
+      <c r="H861" s="14"/>
+      <c r="L861" s="15"/>
+      <c r="M861" s="15"/>
     </row>
     <row r="862">
-      <c r="L862" s="10"/>
-      <c r="M862" s="10"/>
+      <c r="G862" s="14"/>
+      <c r="H862" s="14"/>
+      <c r="L862" s="15"/>
+      <c r="M862" s="15"/>
     </row>
     <row r="863">
-      <c r="L863" s="10"/>
-      <c r="M863" s="10"/>
+      <c r="G863" s="14"/>
+      <c r="H863" s="14"/>
+      <c r="L863" s="15"/>
+      <c r="M863" s="15"/>
     </row>
     <row r="864">
-      <c r="L864" s="10"/>
-      <c r="M864" s="10"/>
+      <c r="G864" s="14"/>
+      <c r="H864" s="14"/>
+      <c r="L864" s="15"/>
+      <c r="M864" s="15"/>
     </row>
     <row r="865">
-      <c r="L865" s="10"/>
-      <c r="M865" s="10"/>
+      <c r="G865" s="14"/>
+      <c r="H865" s="14"/>
+      <c r="L865" s="15"/>
+      <c r="M865" s="15"/>
     </row>
     <row r="866">
-      <c r="L866" s="10"/>
-      <c r="M866" s="10"/>
+      <c r="G866" s="14"/>
+      <c r="H866" s="14"/>
+      <c r="L866" s="15"/>
+      <c r="M866" s="15"/>
     </row>
     <row r="867">
-      <c r="L867" s="10"/>
-      <c r="M867" s="10"/>
+      <c r="G867" s="14"/>
+      <c r="H867" s="14"/>
+      <c r="L867" s="15"/>
+      <c r="M867" s="15"/>
     </row>
     <row r="868">
-      <c r="L868" s="10"/>
-      <c r="M868" s="10"/>
+      <c r="G868" s="14"/>
+      <c r="H868" s="14"/>
+      <c r="L868" s="15"/>
+      <c r="M868" s="15"/>
     </row>
     <row r="869">
-      <c r="L869" s="10"/>
-      <c r="M869" s="10"/>
+      <c r="G869" s="14"/>
+      <c r="H869" s="14"/>
+      <c r="L869" s="15"/>
+      <c r="M869" s="15"/>
     </row>
     <row r="870">
-      <c r="L870" s="10"/>
-      <c r="M870" s="10"/>
+      <c r="G870" s="14"/>
+      <c r="H870" s="14"/>
+      <c r="L870" s="15"/>
+      <c r="M870" s="15"/>
     </row>
     <row r="871">
-      <c r="L871" s="10"/>
-      <c r="M871" s="10"/>
+      <c r="G871" s="14"/>
+      <c r="H871" s="14"/>
+      <c r="L871" s="15"/>
+      <c r="M871" s="15"/>
     </row>
     <row r="872">
-      <c r="L872" s="10"/>
-      <c r="M872" s="10"/>
+      <c r="G872" s="14"/>
+      <c r="H872" s="14"/>
+      <c r="L872" s="15"/>
+      <c r="M872" s="15"/>
     </row>
     <row r="873">
-      <c r="L873" s="10"/>
-      <c r="M873" s="10"/>
+      <c r="G873" s="14"/>
+      <c r="H873" s="14"/>
+      <c r="L873" s="15"/>
+      <c r="M873" s="15"/>
     </row>
     <row r="874">
-      <c r="L874" s="10"/>
-      <c r="M874" s="10"/>
+      <c r="G874" s="14"/>
+      <c r="H874" s="14"/>
+      <c r="L874" s="15"/>
+      <c r="M874" s="15"/>
     </row>
     <row r="875">
-      <c r="L875" s="10"/>
-      <c r="M875" s="10"/>
+      <c r="G875" s="14"/>
+      <c r="H875" s="14"/>
+      <c r="L875" s="15"/>
+      <c r="M875" s="15"/>
     </row>
     <row r="876">
-      <c r="L876" s="10"/>
-      <c r="M876" s="10"/>
+      <c r="G876" s="14"/>
+      <c r="H876" s="14"/>
+      <c r="L876" s="15"/>
+      <c r="M876" s="15"/>
     </row>
     <row r="877">
-      <c r="L877" s="10"/>
-      <c r="M877" s="10"/>
+      <c r="G877" s="14"/>
+      <c r="H877" s="14"/>
+      <c r="L877" s="15"/>
+      <c r="M877" s="15"/>
     </row>
     <row r="878">
-      <c r="L878" s="10"/>
-      <c r="M878" s="10"/>
+      <c r="G878" s="14"/>
+      <c r="H878" s="14"/>
+      <c r="L878" s="15"/>
+      <c r="M878" s="15"/>
     </row>
     <row r="879">
-      <c r="L879" s="10"/>
-      <c r="M879" s="10"/>
+      <c r="G879" s="14"/>
+      <c r="H879" s="14"/>
+      <c r="L879" s="15"/>
+      <c r="M879" s="15"/>
     </row>
     <row r="880">
-      <c r="L880" s="10"/>
-      <c r="M880" s="10"/>
+      <c r="G880" s="14"/>
+      <c r="H880" s="14"/>
+      <c r="L880" s="15"/>
+      <c r="M880" s="15"/>
     </row>
     <row r="881">
-      <c r="L881" s="10"/>
-      <c r="M881" s="10"/>
+      <c r="G881" s="14"/>
+      <c r="H881" s="14"/>
+      <c r="L881" s="15"/>
+      <c r="M881" s="15"/>
     </row>
     <row r="882">
-      <c r="L882" s="10"/>
-      <c r="M882" s="10"/>
+      <c r="G882" s="14"/>
+      <c r="H882" s="14"/>
+      <c r="L882" s="15"/>
+      <c r="M882" s="15"/>
     </row>
     <row r="883">
-      <c r="L883" s="10"/>
-      <c r="M883" s="10"/>
+      <c r="G883" s="14"/>
+      <c r="H883" s="14"/>
+      <c r="L883" s="15"/>
+      <c r="M883" s="15"/>
     </row>
     <row r="884">
-      <c r="L884" s="10"/>
-      <c r="M884" s="10"/>
+      <c r="G884" s="14"/>
+      <c r="H884" s="14"/>
+      <c r="L884" s="15"/>
+      <c r="M884" s="15"/>
     </row>
     <row r="885">
-      <c r="L885" s="10"/>
-      <c r="M885" s="10"/>
+      <c r="G885" s="14"/>
+      <c r="H885" s="14"/>
+      <c r="L885" s="15"/>
+      <c r="M885" s="15"/>
     </row>
     <row r="886">
-      <c r="L886" s="10"/>
-      <c r="M886" s="10"/>
+      <c r="G886" s="14"/>
+      <c r="H886" s="14"/>
+      <c r="L886" s="15"/>
+      <c r="M886" s="15"/>
     </row>
     <row r="887">
-      <c r="L887" s="10"/>
-      <c r="M887" s="10"/>
+      <c r="G887" s="14"/>
+      <c r="H887" s="14"/>
+      <c r="L887" s="15"/>
+      <c r="M887" s="15"/>
     </row>
     <row r="888">
-      <c r="L888" s="10"/>
-      <c r="M888" s="10"/>
+      <c r="G888" s="14"/>
+      <c r="H888" s="14"/>
+      <c r="L888" s="15"/>
+      <c r="M888" s="15"/>
     </row>
     <row r="889">
-      <c r="L889" s="10"/>
-      <c r="M889" s="10"/>
+      <c r="G889" s="14"/>
+      <c r="H889" s="14"/>
+      <c r="L889" s="15"/>
+      <c r="M889" s="15"/>
     </row>
     <row r="890">
-      <c r="L890" s="10"/>
-      <c r="M890" s="10"/>
+      <c r="G890" s="14"/>
+      <c r="H890" s="14"/>
+      <c r="L890" s="15"/>
+      <c r="M890" s="15"/>
     </row>
     <row r="891">
-      <c r="L891" s="10"/>
-      <c r="M891" s="10"/>
+      <c r="G891" s="14"/>
+      <c r="H891" s="14"/>
+      <c r="L891" s="15"/>
+      <c r="M891" s="15"/>
     </row>
     <row r="892">
-      <c r="L892" s="10"/>
-      <c r="M892" s="10"/>
+      <c r="G892" s="14"/>
+      <c r="H892" s="14"/>
+      <c r="L892" s="15"/>
+      <c r="M892" s="15"/>
     </row>
     <row r="893">
-      <c r="L893" s="10"/>
-      <c r="M893" s="10"/>
+      <c r="G893" s="14"/>
+      <c r="H893" s="14"/>
+      <c r="L893" s="15"/>
+      <c r="M893" s="15"/>
     </row>
     <row r="894">
-      <c r="L894" s="10"/>
-      <c r="M894" s="10"/>
+      <c r="G894" s="14"/>
+      <c r="H894" s="14"/>
+      <c r="L894" s="15"/>
+      <c r="M894" s="15"/>
     </row>
     <row r="895">
-      <c r="L895" s="10"/>
-      <c r="M895" s="10"/>
+      <c r="G895" s="14"/>
+      <c r="H895" s="14"/>
+      <c r="L895" s="15"/>
+      <c r="M895" s="15"/>
     </row>
     <row r="896">
-      <c r="L896" s="10"/>
-      <c r="M896" s="10"/>
+      <c r="G896" s="14"/>
+      <c r="H896" s="14"/>
+      <c r="L896" s="15"/>
+      <c r="M896" s="15"/>
     </row>
     <row r="897">
-      <c r="L897" s="10"/>
-      <c r="M897" s="10"/>
+      <c r="G897" s="14"/>
+      <c r="H897" s="14"/>
+      <c r="L897" s="15"/>
+      <c r="M897" s="15"/>
     </row>
     <row r="898">
-      <c r="L898" s="10"/>
-      <c r="M898" s="10"/>
+      <c r="G898" s="14"/>
+      <c r="H898" s="14"/>
+      <c r="L898" s="15"/>
+      <c r="M898" s="15"/>
     </row>
     <row r="899">
-      <c r="L899" s="10"/>
-      <c r="M899" s="10"/>
+      <c r="G899" s="14"/>
+      <c r="H899" s="14"/>
+      <c r="L899" s="15"/>
+      <c r="M899" s="15"/>
     </row>
     <row r="900">
-      <c r="L900" s="10"/>
-      <c r="M900" s="10"/>
+      <c r="G900" s="14"/>
+      <c r="H900" s="14"/>
+      <c r="L900" s="15"/>
+      <c r="M900" s="15"/>
     </row>
     <row r="901">
-      <c r="L901" s="10"/>
-      <c r="M901" s="10"/>
+      <c r="G901" s="14"/>
+      <c r="H901" s="14"/>
+      <c r="L901" s="15"/>
+      <c r="M901" s="15"/>
     </row>
     <row r="902">
-      <c r="L902" s="10"/>
-      <c r="M902" s="10"/>
+      <c r="G902" s="14"/>
+      <c r="H902" s="14"/>
+      <c r="L902" s="15"/>
+      <c r="M902" s="15"/>
     </row>
     <row r="903">
-      <c r="L903" s="10"/>
-      <c r="M903" s="10"/>
+      <c r="G903" s="14"/>
+      <c r="H903" s="14"/>
+      <c r="L903" s="15"/>
+      <c r="M903" s="15"/>
     </row>
     <row r="904">
-      <c r="L904" s="10"/>
-      <c r="M904" s="10"/>
+      <c r="G904" s="14"/>
+      <c r="H904" s="14"/>
+      <c r="L904" s="15"/>
+      <c r="M904" s="15"/>
     </row>
     <row r="905">
-      <c r="L905" s="10"/>
-      <c r="M905" s="10"/>
+      <c r="G905" s="14"/>
+      <c r="H905" s="14"/>
+      <c r="L905" s="15"/>
+      <c r="M905" s="15"/>
     </row>
     <row r="906">
-      <c r="L906" s="10"/>
-      <c r="M906" s="10"/>
+      <c r="G906" s="14"/>
+      <c r="H906" s="14"/>
+      <c r="L906" s="15"/>
+      <c r="M906" s="15"/>
     </row>
     <row r="907">
-      <c r="L907" s="10"/>
-      <c r="M907" s="10"/>
+      <c r="G907" s="14"/>
+      <c r="H907" s="14"/>
+      <c r="L907" s="15"/>
+      <c r="M907" s="15"/>
     </row>
     <row r="908">
-      <c r="L908" s="10"/>
-      <c r="M908" s="10"/>
+      <c r="G908" s="14"/>
+      <c r="H908" s="14"/>
+      <c r="L908" s="15"/>
+      <c r="M908" s="15"/>
     </row>
     <row r="909">
-      <c r="L909" s="10"/>
-      <c r="M909" s="10"/>
+      <c r="G909" s="14"/>
+      <c r="H909" s="14"/>
+      <c r="L909" s="15"/>
+      <c r="M909" s="15"/>
     </row>
     <row r="910">
-      <c r="L910" s="10"/>
-      <c r="M910" s="10"/>
+      <c r="G910" s="14"/>
+      <c r="H910" s="14"/>
+      <c r="L910" s="15"/>
+      <c r="M910" s="15"/>
     </row>
     <row r="911">
-      <c r="L911" s="10"/>
-      <c r="M911" s="10"/>
+      <c r="G911" s="14"/>
+      <c r="H911" s="14"/>
+      <c r="L911" s="15"/>
+      <c r="M911" s="15"/>
     </row>
     <row r="912">
-      <c r="L912" s="10"/>
-      <c r="M912" s="10"/>
+      <c r="G912" s="14"/>
+      <c r="H912" s="14"/>
+      <c r="L912" s="15"/>
+      <c r="M912" s="15"/>
     </row>
     <row r="913">
-      <c r="L913" s="10"/>
-      <c r="M913" s="10"/>
+      <c r="G913" s="14"/>
+      <c r="H913" s="14"/>
+      <c r="L913" s="15"/>
+      <c r="M913" s="15"/>
     </row>
     <row r="914">
-      <c r="L914" s="10"/>
-      <c r="M914" s="10"/>
+      <c r="G914" s="14"/>
+      <c r="H914" s="14"/>
+      <c r="L914" s="15"/>
+      <c r="M914" s="15"/>
     </row>
     <row r="915">
-      <c r="L915" s="10"/>
-      <c r="M915" s="10"/>
+      <c r="G915" s="14"/>
+      <c r="H915" s="14"/>
+      <c r="L915" s="15"/>
+      <c r="M915" s="15"/>
     </row>
     <row r="916">
-      <c r="L916" s="10"/>
-      <c r="M916" s="10"/>
+      <c r="G916" s="14"/>
+      <c r="H916" s="14"/>
+      <c r="L916" s="15"/>
+      <c r="M916" s="15"/>
     </row>
     <row r="917">
-      <c r="L917" s="10"/>
-      <c r="M917" s="10"/>
+      <c r="G917" s="14"/>
+      <c r="H917" s="14"/>
+      <c r="L917" s="15"/>
+      <c r="M917" s="15"/>
     </row>
     <row r="918">
-      <c r="L918" s="10"/>
-      <c r="M918" s="10"/>
+      <c r="G918" s="14"/>
+      <c r="H918" s="14"/>
+      <c r="L918" s="15"/>
+      <c r="M918" s="15"/>
     </row>
     <row r="919">
-      <c r="L919" s="10"/>
-      <c r="M919" s="10"/>
+      <c r="G919" s="14"/>
+      <c r="H919" s="14"/>
+      <c r="L919" s="15"/>
+      <c r="M919" s="15"/>
     </row>
     <row r="920">
-      <c r="L920" s="10"/>
-      <c r="M920" s="10"/>
+      <c r="G920" s="14"/>
+      <c r="H920" s="14"/>
+      <c r="L920" s="15"/>
+      <c r="M920" s="15"/>
     </row>
     <row r="921">
-      <c r="L921" s="10"/>
-      <c r="M921" s="10"/>
+      <c r="G921" s="14"/>
+      <c r="H921" s="14"/>
+      <c r="L921" s="15"/>
+      <c r="M921" s="15"/>
     </row>
     <row r="922">
-      <c r="L922" s="10"/>
-      <c r="M922" s="10"/>
+      <c r="G922" s="14"/>
+      <c r="H922" s="14"/>
+      <c r="L922" s="15"/>
+      <c r="M922" s="15"/>
     </row>
     <row r="923">
-      <c r="L923" s="10"/>
-      <c r="M923" s="10"/>
+      <c r="G923" s="14"/>
+      <c r="H923" s="14"/>
+      <c r="L923" s="15"/>
+      <c r="M923" s="15"/>
     </row>
     <row r="924">
-      <c r="L924" s="10"/>
-      <c r="M924" s="10"/>
+      <c r="G924" s="14"/>
+      <c r="H924" s="14"/>
+      <c r="L924" s="15"/>
+      <c r="M924" s="15"/>
     </row>
     <row r="925">
-      <c r="L925" s="10"/>
-      <c r="M925" s="10"/>
+      <c r="G925" s="14"/>
+      <c r="H925" s="14"/>
+      <c r="L925" s="15"/>
+      <c r="M925" s="15"/>
     </row>
     <row r="926">
-      <c r="L926" s="10"/>
-      <c r="M926" s="10"/>
+      <c r="G926" s="14"/>
+      <c r="H926" s="14"/>
+      <c r="L926" s="15"/>
+      <c r="M926" s="15"/>
     </row>
     <row r="927">
-      <c r="L927" s="10"/>
-      <c r="M927" s="10"/>
+      <c r="G927" s="14"/>
+      <c r="H927" s="14"/>
+      <c r="L927" s="15"/>
+      <c r="M927" s="15"/>
     </row>
     <row r="928">
-      <c r="L928" s="10"/>
-      <c r="M928" s="10"/>
+      <c r="G928" s="14"/>
+      <c r="H928" s="14"/>
+      <c r="L928" s="15"/>
+      <c r="M928" s="15"/>
     </row>
     <row r="929">
-      <c r="L929" s="10"/>
-      <c r="M929" s="10"/>
+      <c r="G929" s="14"/>
+      <c r="H929" s="14"/>
+      <c r="L929" s="15"/>
+      <c r="M929" s="15"/>
     </row>
     <row r="930">
-      <c r="L930" s="10"/>
-      <c r="M930" s="10"/>
+      <c r="G930" s="14"/>
+      <c r="H930" s="14"/>
+      <c r="L930" s="15"/>
+      <c r="M930" s="15"/>
     </row>
     <row r="931">
-      <c r="L931" s="10"/>
-      <c r="M931" s="10"/>
+      <c r="G931" s="14"/>
+      <c r="H931" s="14"/>
+      <c r="L931" s="15"/>
+      <c r="M931" s="15"/>
     </row>
     <row r="932">
-      <c r="L932" s="10"/>
-      <c r="M932" s="10"/>
+      <c r="G932" s="14"/>
+      <c r="H932" s="14"/>
+      <c r="L932" s="15"/>
+      <c r="M932" s="15"/>
     </row>
     <row r="933">
-      <c r="L933" s="10"/>
-      <c r="M933" s="10"/>
+      <c r="G933" s="14"/>
+      <c r="H933" s="14"/>
+      <c r="L933" s="15"/>
+      <c r="M933" s="15"/>
     </row>
     <row r="934">
-      <c r="L934" s="10"/>
-      <c r="M934" s="10"/>
+      <c r="G934" s="14"/>
+      <c r="H934" s="14"/>
+      <c r="L934" s="15"/>
+      <c r="M934" s="15"/>
     </row>
     <row r="935">
-      <c r="L935" s="10"/>
-      <c r="M935" s="10"/>
+      <c r="G935" s="14"/>
+      <c r="H935" s="14"/>
+      <c r="L935" s="15"/>
+      <c r="M935" s="15"/>
     </row>
     <row r="936">
-      <c r="L936" s="10"/>
-      <c r="M936" s="10"/>
+      <c r="G936" s="14"/>
+      <c r="H936" s="14"/>
+      <c r="L936" s="15"/>
+      <c r="M936" s="15"/>
     </row>
     <row r="937">
-      <c r="L937" s="10"/>
-      <c r="M937" s="10"/>
+      <c r="G937" s="14"/>
+      <c r="H937" s="14"/>
+      <c r="L937" s="15"/>
+      <c r="M937" s="15"/>
     </row>
     <row r="938">
-      <c r="L938" s="10"/>
-      <c r="M938" s="10"/>
+      <c r="G938" s="14"/>
+      <c r="H938" s="14"/>
+      <c r="L938" s="15"/>
+      <c r="M938" s="15"/>
     </row>
     <row r="939">
-      <c r="L939" s="10"/>
-      <c r="M939" s="10"/>
+      <c r="G939" s="14"/>
+      <c r="H939" s="14"/>
+      <c r="L939" s="15"/>
+      <c r="M939" s="15"/>
     </row>
     <row r="940">
-      <c r="L940" s="10"/>
-      <c r="M940" s="10"/>
+      <c r="G940" s="14"/>
+      <c r="H940" s="14"/>
+      <c r="L940" s="15"/>
+      <c r="M940" s="15"/>
     </row>
     <row r="941">
-      <c r="L941" s="10"/>
-      <c r="M941" s="10"/>
+      <c r="G941" s="14"/>
+      <c r="H941" s="14"/>
+      <c r="L941" s="15"/>
+      <c r="M941" s="15"/>
     </row>
     <row r="942">
-      <c r="L942" s="10"/>
-      <c r="M942" s="10"/>
+      <c r="G942" s="14"/>
+      <c r="H942" s="14"/>
+      <c r="L942" s="15"/>
+      <c r="M942" s="15"/>
     </row>
     <row r="943">
-      <c r="L943" s="10"/>
-      <c r="M943" s="10"/>
+      <c r="G943" s="14"/>
+      <c r="H943" s="14"/>
+      <c r="L943" s="15"/>
+      <c r="M943" s="15"/>
     </row>
     <row r="944">
-      <c r="L944" s="10"/>
-      <c r="M944" s="10"/>
+      <c r="G944" s="14"/>
+      <c r="H944" s="14"/>
+      <c r="L944" s="15"/>
+      <c r="M944" s="15"/>
     </row>
     <row r="945">
-      <c r="L945" s="10"/>
-      <c r="M945" s="10"/>
+      <c r="G945" s="14"/>
+      <c r="H945" s="14"/>
+      <c r="L945" s="15"/>
+      <c r="M945" s="15"/>
     </row>
     <row r="946">
-      <c r="L946" s="10"/>
-      <c r="M946" s="10"/>
+      <c r="G946" s="14"/>
+      <c r="H946" s="14"/>
+      <c r="L946" s="15"/>
+      <c r="M946" s="15"/>
     </row>
     <row r="947">
-      <c r="L947" s="10"/>
-      <c r="M947" s="10"/>
+      <c r="G947" s="14"/>
+      <c r="H947" s="14"/>
+      <c r="L947" s="15"/>
+      <c r="M947" s="15"/>
     </row>
     <row r="948">
-      <c r="L948" s="10"/>
-      <c r="M948" s="10"/>
+      <c r="G948" s="14"/>
+      <c r="H948" s="14"/>
+      <c r="L948" s="15"/>
+      <c r="M948" s="15"/>
     </row>
     <row r="949">
-      <c r="L949" s="10"/>
-      <c r="M949" s="10"/>
+      <c r="G949" s="14"/>
+      <c r="H949" s="14"/>
+      <c r="L949" s="15"/>
+      <c r="M949" s="15"/>
     </row>
     <row r="950">
-      <c r="L950" s="10"/>
-      <c r="M950" s="10"/>
+      <c r="G950" s="14"/>
+      <c r="H950" s="14"/>
+      <c r="L950" s="15"/>
+      <c r="M950" s="15"/>
     </row>
     <row r="951">
-      <c r="L951" s="10"/>
-      <c r="M951" s="10"/>
+      <c r="G951" s="14"/>
+      <c r="H951" s="14"/>
+      <c r="L951" s="15"/>
+      <c r="M951" s="15"/>
     </row>
     <row r="952">
-      <c r="L952" s="10"/>
-      <c r="M952" s="10"/>
+      <c r="G952" s="14"/>
+      <c r="H952" s="14"/>
+      <c r="L952" s="15"/>
+      <c r="M952" s="15"/>
     </row>
     <row r="953">
-      <c r="L953" s="10"/>
-      <c r="M953" s="10"/>
+      <c r="G953" s="14"/>
+      <c r="H953" s="14"/>
+      <c r="L953" s="15"/>
+      <c r="M953" s="15"/>
     </row>
     <row r="954">
-      <c r="L954" s="10"/>
-      <c r="M954" s="10"/>
+      <c r="G954" s="14"/>
+      <c r="H954" s="14"/>
+      <c r="L954" s="15"/>
+      <c r="M954" s="15"/>
     </row>
     <row r="955">
-      <c r="L955" s="10"/>
-      <c r="M955" s="10"/>
+      <c r="G955" s="14"/>
+      <c r="H955" s="14"/>
+      <c r="L955" s="15"/>
+      <c r="M955" s="15"/>
     </row>
     <row r="956">
-      <c r="L956" s="10"/>
-      <c r="M956" s="10"/>
+      <c r="G956" s="14"/>
+      <c r="H956" s="14"/>
+      <c r="L956" s="15"/>
+      <c r="M956" s="15"/>
     </row>
     <row r="957">
-      <c r="L957" s="10"/>
-      <c r="M957" s="10"/>
+      <c r="G957" s="14"/>
+      <c r="H957" s="14"/>
+      <c r="L957" s="15"/>
+      <c r="M957" s="15"/>
     </row>
     <row r="958">
-      <c r="L958" s="10"/>
-      <c r="M958" s="10"/>
+      <c r="G958" s="14"/>
+      <c r="H958" s="14"/>
+      <c r="L958" s="15"/>
+      <c r="M958" s="15"/>
     </row>
     <row r="959">
-      <c r="L959" s="10"/>
-      <c r="M959" s="10"/>
+      <c r="G959" s="14"/>
+      <c r="H959" s="14"/>
+      <c r="L959" s="15"/>
+      <c r="M959" s="15"/>
     </row>
     <row r="960">
-      <c r="L960" s="10"/>
-      <c r="M960" s="10"/>
+      <c r="G960" s="14"/>
+      <c r="H960" s="14"/>
+      <c r="L960" s="15"/>
+      <c r="M960" s="15"/>
     </row>
     <row r="961">
-      <c r="L961" s="10"/>
-      <c r="M961" s="10"/>
+      <c r="G961" s="14"/>
+      <c r="H961" s="14"/>
+      <c r="L961" s="15"/>
+      <c r="M961" s="15"/>
     </row>
     <row r="962">
-      <c r="L962" s="10"/>
-      <c r="M962" s="10"/>
+      <c r="G962" s="14"/>
+      <c r="H962" s="14"/>
+      <c r="L962" s="15"/>
+      <c r="M962" s="15"/>
     </row>
     <row r="963">
-      <c r="L963" s="10"/>
-      <c r="M963" s="10"/>
+      <c r="G963" s="14"/>
+      <c r="H963" s="14"/>
+      <c r="L963" s="15"/>
+      <c r="M963" s="15"/>
     </row>
     <row r="964">
-      <c r="L964" s="10"/>
-      <c r="M964" s="10"/>
+      <c r="G964" s="14"/>
+      <c r="H964" s="14"/>
+      <c r="L964" s="15"/>
+      <c r="M964" s="15"/>
     </row>
     <row r="965">
-      <c r="L965" s="10"/>
-      <c r="M965" s="10"/>
+      <c r="G965" s="14"/>
+      <c r="H965" s="14"/>
+      <c r="L965" s="15"/>
+      <c r="M965" s="15"/>
     </row>
     <row r="966">
-      <c r="L966" s="10"/>
-      <c r="M966" s="10"/>
+      <c r="G966" s="14"/>
+      <c r="H966" s="14"/>
+      <c r="L966" s="15"/>
+      <c r="M966" s="15"/>
     </row>
     <row r="967">
-      <c r="L967" s="10"/>
-      <c r="M967" s="10"/>
+      <c r="G967" s="14"/>
+      <c r="H967" s="14"/>
+      <c r="L967" s="15"/>
+      <c r="M967" s="15"/>
     </row>
     <row r="968">
-      <c r="L968" s="10"/>
-      <c r="M968" s="10"/>
+      <c r="G968" s="14"/>
+      <c r="H968" s="14"/>
+      <c r="L968" s="15"/>
+      <c r="M968" s="15"/>
     </row>
     <row r="969">
-      <c r="L969" s="10"/>
-      <c r="M969" s="10"/>
+      <c r="G969" s="14"/>
+      <c r="H969" s="14"/>
+      <c r="L969" s="15"/>
+      <c r="M969" s="15"/>
     </row>
     <row r="970">
-      <c r="L970" s="10"/>
-      <c r="M970" s="10"/>
+      <c r="G970" s="14"/>
+      <c r="H970" s="14"/>
+      <c r="L970" s="15"/>
+      <c r="M970" s="15"/>
     </row>
     <row r="971">
-      <c r="L971" s="10"/>
-      <c r="M971" s="10"/>
+      <c r="G971" s="14"/>
+      <c r="H971" s="14"/>
+      <c r="L971" s="15"/>
+      <c r="M971" s="15"/>
     </row>
     <row r="972">
-      <c r="L972" s="10"/>
-      <c r="M972" s="10"/>
+      <c r="G972" s="14"/>
+      <c r="H972" s="14"/>
+      <c r="L972" s="15"/>
+      <c r="M972" s="15"/>
     </row>
     <row r="973">
-      <c r="L973" s="10"/>
-      <c r="M973" s="10"/>
+      <c r="G973" s="14"/>
+      <c r="H973" s="14"/>
+      <c r="L973" s="15"/>
+      <c r="M973" s="15"/>
     </row>
     <row r="974">
-      <c r="L974" s="10"/>
-      <c r="M974" s="10"/>
+      <c r="G974" s="14"/>
+      <c r="H974" s="14"/>
+      <c r="L974" s="15"/>
+      <c r="M974" s="15"/>
     </row>
     <row r="975">
-      <c r="L975" s="10"/>
-      <c r="M975" s="10"/>
+      <c r="G975" s="14"/>
+      <c r="H975" s="14"/>
+      <c r="L975" s="15"/>
+      <c r="M975" s="15"/>
     </row>
     <row r="976">
-      <c r="L976" s="10"/>
-      <c r="M976" s="10"/>
+      <c r="G976" s="14"/>
+      <c r="H976" s="14"/>
+      <c r="L976" s="15"/>
+      <c r="M976" s="15"/>
     </row>
     <row r="977">
-      <c r="L977" s="10"/>
-      <c r="M977" s="10"/>
+      <c r="G977" s="14"/>
+      <c r="H977" s="14"/>
+      <c r="L977" s="15"/>
+      <c r="M977" s="15"/>
     </row>
     <row r="978">
-      <c r="L978" s="10"/>
-      <c r="M978" s="10"/>
+      <c r="G978" s="14"/>
+      <c r="H978" s="14"/>
+      <c r="L978" s="15"/>
+      <c r="M978" s="15"/>
     </row>
     <row r="979">
-      <c r="L979" s="10"/>
-      <c r="M979" s="10"/>
+      <c r="G979" s="14"/>
+      <c r="H979" s="14"/>
+      <c r="L979" s="15"/>
+      <c r="M979" s="15"/>
     </row>
     <row r="980">
-      <c r="L980" s="10"/>
-      <c r="M980" s="10"/>
+      <c r="G980" s="14"/>
+      <c r="H980" s="14"/>
+      <c r="L980" s="15"/>
+      <c r="M980" s="15"/>
     </row>
     <row r="981">
-      <c r="L981" s="10"/>
-      <c r="M981" s="10"/>
+      <c r="G981" s="14"/>
+      <c r="H981" s="14"/>
+      <c r="L981" s="15"/>
+      <c r="M981" s="15"/>
     </row>
     <row r="982">
-      <c r="L982" s="10"/>
-      <c r="M982" s="10"/>
+      <c r="G982" s="14"/>
+      <c r="H982" s="14"/>
+      <c r="L982" s="15"/>
+      <c r="M982" s="15"/>
     </row>
     <row r="983">
-      <c r="L983" s="10"/>
-      <c r="M983" s="10"/>
+      <c r="G983" s="14"/>
+      <c r="H983" s="14"/>
+      <c r="L983" s="15"/>
+      <c r="M983" s="15"/>
     </row>
     <row r="984">
-      <c r="L984" s="10"/>
-      <c r="M984" s="10"/>
+      <c r="G984" s="14"/>
+      <c r="H984" s="14"/>
+      <c r="L984" s="15"/>
+      <c r="M984" s="15"/>
     </row>
     <row r="985">
-      <c r="L985" s="10"/>
-      <c r="M985" s="10"/>
+      <c r="G985" s="14"/>
+      <c r="H985" s="14"/>
+      <c r="L985" s="15"/>
+      <c r="M985" s="15"/>
     </row>
     <row r="986">
-      <c r="L986" s="10"/>
-      <c r="M986" s="10"/>
+      <c r="G986" s="14"/>
+      <c r="H986" s="14"/>
+      <c r="L986" s="15"/>
+      <c r="M986" s="15"/>
     </row>
     <row r="987">
-      <c r="L987" s="10"/>
-      <c r="M987" s="10"/>
+      <c r="G987" s="14"/>
+      <c r="H987" s="14"/>
+      <c r="L987" s="15"/>
+      <c r="M987" s="15"/>
     </row>
     <row r="988">
-      <c r="L988" s="10"/>
-      <c r="M988" s="10"/>
+      <c r="G988" s="14"/>
+      <c r="H988" s="14"/>
+      <c r="L988" s="15"/>
+      <c r="M988" s="15"/>
     </row>
     <row r="989">
-      <c r="L989" s="10"/>
-      <c r="M989" s="10"/>
+      <c r="G989" s="14"/>
+      <c r="H989" s="14"/>
+      <c r="L989" s="15"/>
+      <c r="M989" s="15"/>
     </row>
     <row r="990">
-      <c r="L990" s="10"/>
-      <c r="M990" s="10"/>
+      <c r="G990" s="14"/>
+      <c r="H990" s="14"/>
+      <c r="L990" s="15"/>
+      <c r="M990" s="15"/>
     </row>
     <row r="991">
-      <c r="L991" s="10"/>
-      <c r="M991" s="10"/>
+      <c r="G991" s="14"/>
+      <c r="H991" s="14"/>
+      <c r="L991" s="15"/>
+      <c r="M991" s="15"/>
     </row>
     <row r="992">
-      <c r="L992" s="10"/>
-      <c r="M992" s="10"/>
+      <c r="G992" s="14"/>
+      <c r="H992" s="14"/>
+      <c r="L992" s="15"/>
+      <c r="M992" s="15"/>
     </row>
     <row r="993">
-      <c r="L993" s="10"/>
-      <c r="M993" s="10"/>
+      <c r="G993" s="14"/>
+      <c r="H993" s="14"/>
+      <c r="L993" s="15"/>
+      <c r="M993" s="15"/>
     </row>
     <row r="994">
-      <c r="L994" s="10"/>
-      <c r="M994" s="10"/>
+      <c r="G994" s="14"/>
+      <c r="H994" s="14"/>
+      <c r="L994" s="15"/>
+      <c r="M994" s="15"/>
     </row>
     <row r="995">
-      <c r="L995" s="10"/>
-      <c r="M995" s="10"/>
+      <c r="G995" s="14"/>
+      <c r="H995" s="14"/>
+      <c r="L995" s="15"/>
+      <c r="M995" s="15"/>
     </row>
     <row r="996">
-      <c r="L996" s="10"/>
-      <c r="M996" s="10"/>
+      <c r="G996" s="14"/>
+      <c r="H996" s="14"/>
+      <c r="L996" s="15"/>
+      <c r="M996" s="15"/>
     </row>
     <row r="997">
-      <c r="L997" s="10"/>
-      <c r="M997" s="10"/>
+      <c r="G997" s="14"/>
+      <c r="H997" s="14"/>
+      <c r="L997" s="15"/>
+      <c r="M997" s="15"/>
     </row>
     <row r="998">
-      <c r="L998" s="10"/>
-      <c r="M998" s="10"/>
+      <c r="G998" s="14"/>
+      <c r="H998" s="14"/>
+      <c r="L998" s="15"/>
+      <c r="M998" s="15"/>
     </row>
     <row r="999">
-      <c r="L999" s="10"/>
-      <c r="M999" s="10"/>
+      <c r="G999" s="14"/>
+      <c r="H999" s="14"/>
+      <c r="L999" s="15"/>
+      <c r="M999" s="15"/>
     </row>
     <row r="1000">
-      <c r="L1000" s="10"/>
-      <c r="M1000" s="10"/>
+      <c r="G1000" s="14"/>
+      <c r="H1000" s="14"/>
+      <c r="L1000" s="15"/>
+      <c r="M1000" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
